--- a/sample-data/PODS.xlsx
+++ b/sample-data/PODS.xlsx
@@ -12,21 +12,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
   <si>
-    <t xml:space="preserve">Completion Percentage </t>
+    <t>Completion Percentage - 01/09/2026</t>
   </si>
   <si>
-    <t>Completion Percentage - 01/09/2026</t>
+    <t>Completion Percentage (Fast API)</t>
+  </si>
+  <si>
+    <t>Completion Percentage - 02/09/2026</t>
+  </si>
+  <si>
+    <t>Completion Percentage (Node)</t>
+  </si>
+  <si>
+    <t>Completion Percentage - 03/09/2026</t>
+  </si>
+  <si>
+    <t>Completion Percentage (.NET Core)</t>
   </si>
   <si>
     <t xml:space="preserve">POD Name </t>
   </si>
   <si>
+    <t xml:space="preserve">FE </t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>FE + BE integrations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Status </t>
+  </si>
+  <si>
+    <t>Branch</t>
   </si>
   <si>
     <t xml:space="preserve">Start Date </t>
@@ -41,18 +65,6 @@
     <t xml:space="preserve">Machine aligned to project </t>
   </si>
   <si>
-    <t xml:space="preserve">FE </t>
-  </si>
-  <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>FE + BE integrations</t>
-  </si>
-  <si>
-    <t>Completion Percentage - 02/09/2026</t>
-  </si>
-  <si>
     <t>TeleHealth</t>
   </si>
   <si>
@@ -62,7 +74,7 @@
     <t>In Progress</t>
   </si>
   <si>
-    <t>Completion Percentage - 03/09/2026</t>
+    <t>SDD</t>
   </si>
   <si>
     <t xml:space="preserve">Abhishek Jeena </t>
@@ -71,19 +83,22 @@
     <t>Abhishek Jeena</t>
   </si>
   <si>
-    <t>Demo SDD</t>
+    <t>WMS Pick</t>
   </si>
   <si>
-    <t xml:space="preserve">        ~88%</t>
+    <t>/</t>
   </si>
   <si>
-    <t>WMS Pick</t>
+    <t>CLM</t>
   </si>
   <si>
     <t>The POD WMS (WMS Pick_Pack_Ship) is an end-to-end Warehouse Management System designed to handle full inventory lifecycle management, procurement, fulfillment logistics, and analytics.</t>
   </si>
   <si>
-    <t>in progress</t>
+    <t>SDM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field Service Dispatch </t>
   </si>
   <si>
     <t>Prachi Pathak</t>
@@ -95,7 +110,10 @@
     <t>LMS</t>
   </si>
   <si>
-    <t>CLM</t>
+    <t>Workflow &amp; Approvals</t>
+  </si>
+  <si>
+    <t>Support/ Ticket</t>
   </si>
   <si>
     <t>The POD CLM (Contract Lifecycle Management) is an end-to-end Contract Management System designed to handle full contract lifecycle management, from request and authoring through review, approval, execution, and post-signature obligation tracking, renewal, and archival</t>
@@ -110,7 +128,7 @@
     <t>kondaro</t>
   </si>
   <si>
-    <t xml:space="preserve">Field Service Dispatch </t>
+    <t xml:space="preserve">smartFetch </t>
   </si>
   <si>
     <t>A comprehensive Field Service Management (FSM) platform that manages the complete service lifecycle—from work order creation, intelligent technician scheduling, route optimization, and real-time tracking to mobile task execution, customer communication, inventory, payments, compliance, feedback, and analytics.</t>
@@ -125,9 +143,6 @@
     <t>Deltera Health Design System prototype</t>
   </si>
   <si>
-    <t>Workflow &amp; Approvals</t>
-  </si>
-  <si>
     <t xml:space="preserve">The POD Workflow and Approvals is an end to end expense, procurement and leave management system </t>
   </si>
   <si>
@@ -140,9 +155,6 @@
     <t>Valture</t>
   </si>
   <si>
-    <t>Support/ Ticket</t>
-  </si>
-  <si>
     <t>A comprehensive IT service management and support platform that manages tickets from intake to resolution, with SLA tracking, multi-channel communication, collaboration, analytics, security, mobile access, and AI-powered virtual assistance.</t>
   </si>
   <si>
@@ -153,9 +165,6 @@
   </si>
   <si>
     <t>Palzar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smartFetch </t>
   </si>
   <si>
     <t>smartFetch is an internal developer tool for mapping and reusing connected features across codebases. Teams upload full-stack projects as pods into parent folders (Python, .NET, React).</t>
@@ -173,7 +182,7 @@
     <t>Dental Genie</t>
   </si>
   <si>
-    <t>Healthcare Procurement</t>
+    <t>Procure to Pay</t>
   </si>
   <si>
     <t>A healthcare medical procurement and supply chain management platform covering the full lifecycle from requisition and approval through sourcing, purchase orders, goods receipt, inventory, 3-way matching, invoicing and payment.</t>
@@ -186,6 +195,9 @@
   </si>
   <si>
     <t>Lab Order &amp; Results (Pod 3.0) is a centralized system for managing laboratory test orders, tracking results, and supporting healthcare workflows. The project scope is defined in the Lab Orders.xlsx sheet and includes features mapped to various consuming applications. It aims to streamline lab order processing, result management, and integration across connected systems. The document serves as an orientation guide for developers and stakeholders working on the pod. It focuses on intended functionality and business scope rather than implementation status. Any additional details beyond the spreadsheet are clearly identified as domain context or open questions.</t>
+  </si>
+  <si>
+    <t>Demo</t>
   </si>
 </sst>
 </file>
@@ -279,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -287,7 +299,7 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -295,9 +307,6 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -309,6 +318,9 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -316,16 +328,7 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -563,18 +566,22 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="2" t="s">
-        <v>0</v>
+      <c r="H1" s="1"/>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="3"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="4"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
@@ -585,45 +592,60 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
       <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>11</v>
+      <c r="L2" s="6" t="s">
+        <v>7</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
+      <c r="M2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>10</v>
+      </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5"/>
       <c r="T2" s="5"/>
@@ -634,25 +656,26 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
@@ -663,45 +686,60 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
       <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>13</v>
+      <c r="A4" s="9" t="s">
+        <v>17</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>14</v>
+      <c r="B4" s="9" t="s">
+        <v>18</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>15</v>
+      <c r="C4" s="9" t="s">
+        <v>19</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="11">
         <v>46243.0</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>18</v>
+      <c r="I4" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>19</v>
+      <c r="J4" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="H4" s="10" t="s">
-        <v>20</v>
+      <c r="K4" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="I4" s="12">
-        <v>0.85</v>
+      <c r="L4" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="J4" s="12">
-        <v>0.86</v>
+      <c r="M4" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
+      <c r="N4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
@@ -712,25 +750,26 @@
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
       <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
@@ -741,45 +780,60 @@
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
       <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="11">
+      <c r="B6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="11">
         <v>46254.0</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>25</v>
+      <c r="J6" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>26</v>
+      <c r="K6" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="H6" s="12">
-        <v>0.29</v>
+      <c r="L6" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="I6" s="12">
-        <v>0.74</v>
+      <c r="M6" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="J6" s="12">
-        <v>0.66</v>
+      <c r="N6" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
+      <c r="O6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
@@ -790,25 +844,26 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
       <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
@@ -819,45 +874,60 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
       <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="11">
+      <c r="E8" s="11">
         <v>46254.0</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>29</v>
+      <c r="F8" s="9" t="s">
+        <v>35</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>30</v>
+      <c r="G8" s="9" t="s">
+        <v>36</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>31</v>
+      <c r="H8" s="9" t="s">
+        <v>37</v>
       </c>
-      <c r="H8" s="12">
-        <v>0.58</v>
+      <c r="I8" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="I8" s="12">
-        <v>0.7</v>
+      <c r="J8" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="J8" s="12">
-        <v>0.65</v>
+      <c r="K8" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
+      <c r="L8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
@@ -868,25 +938,26 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
       <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
     </row>
     <row r="9">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
@@ -897,45 +968,60 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="s">
-        <v>32</v>
+      <c r="A10" s="9" t="s">
+        <v>28</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>33</v>
+      <c r="B10" s="13" t="s">
+        <v>39</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>23</v>
+      <c r="C10" s="9" t="s">
+        <v>19</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="11">
         <v>46257.0</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>34</v>
+      <c r="F10" s="9" t="s">
+        <v>40</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>35</v>
+      <c r="G10" s="9" t="s">
+        <v>41</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>36</v>
+      <c r="H10" s="9" t="s">
+        <v>42</v>
       </c>
-      <c r="H10" s="10">
-        <v>80.0</v>
+      <c r="I10" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="I10" s="10">
-        <v>60.0</v>
+      <c r="J10" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="J10" s="10">
-        <v>70.0</v>
+      <c r="K10" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="K10" s="13"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
+      <c r="L10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
@@ -946,25 +1032,26 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
       <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
@@ -975,45 +1062,60 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
       <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="s">
-        <v>37</v>
+      <c r="A12" s="9" t="s">
+        <v>32</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>38</v>
+      <c r="B12" s="9" t="s">
+        <v>43</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>23</v>
+      <c r="C12" s="9" t="s">
+        <v>19</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="11">
         <v>46254.0</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>39</v>
+      <c r="F12" s="9" t="s">
+        <v>44</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>40</v>
+      <c r="G12" s="9" t="s">
+        <v>45</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>41</v>
+      <c r="H12" s="9" t="s">
+        <v>46</v>
       </c>
-      <c r="H12" s="10">
-        <v>60.0</v>
+      <c r="I12" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="I12" s="10">
-        <v>70.0</v>
+      <c r="J12" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="J12" s="10">
-        <v>65.0</v>
+      <c r="K12" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="K12" s="13"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
+      <c r="L12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
@@ -1024,25 +1126,26 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
       <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
@@ -1053,45 +1156,60 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
       <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="s">
-        <v>42</v>
+      <c r="A14" s="9" t="s">
+        <v>33</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>43</v>
+      <c r="B14" s="13" t="s">
+        <v>47</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>23</v>
+      <c r="C14" s="9" t="s">
+        <v>19</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="11">
         <v>46254.0</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>44</v>
+      <c r="F14" s="9" t="s">
+        <v>48</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>45</v>
+      <c r="G14" s="9" t="s">
+        <v>49</v>
       </c>
-      <c r="G14" s="10" t="s">
-        <v>46</v>
+      <c r="H14" s="9" t="s">
+        <v>50</v>
       </c>
-      <c r="H14" s="10">
-        <v>6.0</v>
+      <c r="I14" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="I14" s="10">
-        <v>12.0</v>
+      <c r="J14" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="J14" s="10">
-        <v>5.0</v>
+      <c r="K14" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
+      <c r="L14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
@@ -1102,25 +1220,60 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
       <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
     </row>
     <row r="15">
-      <c r="A15" s="13"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
+      <c r="A15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="11">
+        <v>46237.0</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
@@ -1131,45 +1284,60 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
       <c r="AA15" s="5"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="s">
-        <v>47</v>
+      <c r="AB15" s="5"/>
+    </row>
+    <row r="16" ht="81.0" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>56</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>48</v>
+      <c r="B16" s="9" t="s">
+        <v>57</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>49</v>
+      <c r="C16" s="9" t="s">
+        <v>19</v>
       </c>
-      <c r="D16" s="11">
-        <v>46237.0</v>
+      <c r="D16" s="9" t="s">
+        <v>20</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>50</v>
+      <c r="E16" s="11">
+        <v>46265.0</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>51</v>
+      <c r="F16" s="9" t="s">
+        <v>41</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>52</v>
+      <c r="G16" s="9" t="s">
+        <v>41</v>
       </c>
-      <c r="H16" s="10">
-        <v>80.0</v>
+      <c r="H16" s="9" t="s">
+        <v>58</v>
       </c>
-      <c r="I16" s="10">
-        <v>85.0</v>
+      <c r="I16" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="J16" s="10">
-        <v>82.0</v>
+      <c r="J16" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="K16" s="13"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
+      <c r="K16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
@@ -1180,39 +1348,60 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
       <c r="AA16" s="5"/>
-    </row>
-    <row r="17" ht="81.0" customHeight="1">
-      <c r="A17" s="10" t="s">
-        <v>53</v>
+      <c r="AB16" s="5"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="s">
+        <v>59</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>54</v>
+      <c r="B17" s="9" t="s">
+        <v>60</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>23</v>
+      <c r="C17" s="9" t="s">
+        <v>19</v>
       </c>
-      <c r="D17" s="11">
-        <v>46265.0</v>
+      <c r="D17" s="9" t="s">
+        <v>20</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>35</v>
+      <c r="E17" s="14">
+        <v>46266.0</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>35</v>
+      <c r="F17" s="9" t="s">
+        <v>21</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>55</v>
+      <c r="G17" s="9" t="s">
+        <v>21</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
+      <c r="H17" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
@@ -1223,42 +1412,23 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
       <c r="AA17" s="5"/>
+      <c r="AB17" s="5"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="17">
-        <v>46266.0</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="12">
-        <v>0.9</v>
-      </c>
-      <c r="I18" s="12">
-        <v>0.92</v>
-      </c>
-      <c r="J18" s="12">
-        <v>0.9</v>
-      </c>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
@@ -1272,6 +1442,7 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
     </row>
     <row r="19">
       <c r="A19" s="5"/>
@@ -1301,6 +1472,7 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
       <c r="AA19" s="5"/>
+      <c r="AB19" s="5"/>
     </row>
     <row r="20">
       <c r="A20" s="5"/>
@@ -1330,6 +1502,7 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
       <c r="AA20" s="5"/>
+      <c r="AB20" s="5"/>
     </row>
     <row r="21">
       <c r="A21" s="5"/>
@@ -1359,6 +1532,7 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
       <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
     </row>
     <row r="22">
       <c r="A22" s="5"/>
@@ -1388,6 +1562,7 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
       <c r="AA22" s="5"/>
+      <c r="AB22" s="5"/>
     </row>
     <row r="23">
       <c r="A23" s="5"/>
@@ -1417,6 +1592,7 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
       <c r="AA23" s="5"/>
+      <c r="AB23" s="5"/>
     </row>
     <row r="24">
       <c r="A24" s="5"/>
@@ -1446,6 +1622,7 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
       <c r="AA24" s="5"/>
+      <c r="AB24" s="5"/>
     </row>
     <row r="25">
       <c r="A25" s="5"/>
@@ -1475,6 +1652,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
       <c r="AA25" s="5"/>
+      <c r="AB25" s="5"/>
     </row>
     <row r="26">
       <c r="A26" s="5"/>
@@ -1504,6 +1682,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
       <c r="AA26" s="5"/>
+      <c r="AB26" s="5"/>
     </row>
     <row r="27">
       <c r="A27" s="5"/>
@@ -1533,6 +1712,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
       <c r="AA27" s="5"/>
+      <c r="AB27" s="5"/>
     </row>
     <row r="28">
       <c r="A28" s="5"/>
@@ -1562,6 +1742,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
       <c r="AA28" s="5"/>
+      <c r="AB28" s="5"/>
     </row>
     <row r="29">
       <c r="A29" s="5"/>
@@ -1591,6 +1772,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
       <c r="AA29" s="5"/>
+      <c r="AB29" s="5"/>
     </row>
     <row r="30">
       <c r="A30" s="5"/>
@@ -1620,6 +1802,7 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
       <c r="AA30" s="5"/>
+      <c r="AB30" s="5"/>
     </row>
     <row r="31">
       <c r="A31" s="5"/>
@@ -1649,6 +1832,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
       <c r="AA31" s="5"/>
+      <c r="AB31" s="5"/>
     </row>
     <row r="32">
       <c r="A32" s="5"/>
@@ -1678,6 +1862,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
       <c r="AA32" s="5"/>
+      <c r="AB32" s="5"/>
     </row>
     <row r="33">
       <c r="A33" s="5"/>
@@ -1707,6 +1892,7 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
       <c r="AA33" s="5"/>
+      <c r="AB33" s="5"/>
     </row>
     <row r="34">
       <c r="A34" s="5"/>
@@ -1736,6 +1922,7 @@
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
       <c r="AA34" s="5"/>
+      <c r="AB34" s="5"/>
     </row>
     <row r="35">
       <c r="A35" s="5"/>
@@ -1765,6 +1952,7 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
       <c r="AA35" s="5"/>
+      <c r="AB35" s="5"/>
     </row>
     <row r="36">
       <c r="A36" s="5"/>
@@ -1794,6 +1982,7 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
       <c r="AA36" s="5"/>
+      <c r="AB36" s="5"/>
     </row>
     <row r="37">
       <c r="A37" s="5"/>
@@ -1823,6 +2012,7 @@
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
       <c r="AA37" s="5"/>
+      <c r="AB37" s="5"/>
     </row>
     <row r="38">
       <c r="A38" s="5"/>
@@ -1852,6 +2042,7 @@
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
       <c r="AA38" s="5"/>
+      <c r="AB38" s="5"/>
     </row>
     <row r="39">
       <c r="A39" s="5"/>
@@ -1881,6 +2072,7 @@
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
       <c r="AA39" s="5"/>
+      <c r="AB39" s="5"/>
     </row>
     <row r="40">
       <c r="A40" s="5"/>
@@ -1910,6 +2102,7 @@
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
       <c r="AA40" s="5"/>
+      <c r="AB40" s="5"/>
     </row>
     <row r="41">
       <c r="A41" s="5"/>
@@ -1939,6 +2132,7 @@
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
       <c r="AA41" s="5"/>
+      <c r="AB41" s="5"/>
     </row>
     <row r="42">
       <c r="A42" s="5"/>
@@ -1968,6 +2162,7 @@
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
       <c r="AA42" s="5"/>
+      <c r="AB42" s="5"/>
     </row>
     <row r="43">
       <c r="A43" s="5"/>
@@ -1997,6 +2192,7 @@
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
       <c r="AA43" s="5"/>
+      <c r="AB43" s="5"/>
     </row>
     <row r="44">
       <c r="A44" s="5"/>
@@ -2026,6 +2222,7 @@
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
       <c r="AA44" s="5"/>
+      <c r="AB44" s="5"/>
     </row>
     <row r="45">
       <c r="A45" s="5"/>
@@ -2055,6 +2252,7 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
       <c r="AA45" s="5"/>
+      <c r="AB45" s="5"/>
     </row>
     <row r="46">
       <c r="A46" s="5"/>
@@ -2084,6 +2282,7 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
       <c r="AA46" s="5"/>
+      <c r="AB46" s="5"/>
     </row>
     <row r="47">
       <c r="A47" s="5"/>
@@ -2113,6 +2312,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
       <c r="AA47" s="5"/>
+      <c r="AB47" s="5"/>
     </row>
     <row r="48">
       <c r="A48" s="5"/>
@@ -2142,6 +2342,7 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
       <c r="AA48" s="5"/>
+      <c r="AB48" s="5"/>
     </row>
     <row r="49">
       <c r="A49" s="5"/>
@@ -2171,6 +2372,7 @@
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
       <c r="AA49" s="5"/>
+      <c r="AB49" s="5"/>
     </row>
     <row r="50">
       <c r="A50" s="5"/>
@@ -2200,6 +2402,7 @@
       <c r="Y50" s="5"/>
       <c r="Z50" s="5"/>
       <c r="AA50" s="5"/>
+      <c r="AB50" s="5"/>
     </row>
     <row r="51">
       <c r="A51" s="5"/>
@@ -2229,6 +2432,7 @@
       <c r="Y51" s="5"/>
       <c r="Z51" s="5"/>
       <c r="AA51" s="5"/>
+      <c r="AB51" s="5"/>
     </row>
     <row r="52">
       <c r="A52" s="5"/>
@@ -2258,6 +2462,7 @@
       <c r="Y52" s="5"/>
       <c r="Z52" s="5"/>
       <c r="AA52" s="5"/>
+      <c r="AB52" s="5"/>
     </row>
     <row r="53">
       <c r="A53" s="5"/>
@@ -2287,6 +2492,7 @@
       <c r="Y53" s="5"/>
       <c r="Z53" s="5"/>
       <c r="AA53" s="5"/>
+      <c r="AB53" s="5"/>
     </row>
     <row r="54">
       <c r="A54" s="5"/>
@@ -2316,6 +2522,7 @@
       <c r="Y54" s="5"/>
       <c r="Z54" s="5"/>
       <c r="AA54" s="5"/>
+      <c r="AB54" s="5"/>
     </row>
     <row r="55">
       <c r="A55" s="5"/>
@@ -2345,6 +2552,7 @@
       <c r="Y55" s="5"/>
       <c r="Z55" s="5"/>
       <c r="AA55" s="5"/>
+      <c r="AB55" s="5"/>
     </row>
     <row r="56">
       <c r="A56" s="5"/>
@@ -2374,6 +2582,7 @@
       <c r="Y56" s="5"/>
       <c r="Z56" s="5"/>
       <c r="AA56" s="5"/>
+      <c r="AB56" s="5"/>
     </row>
     <row r="57">
       <c r="A57" s="5"/>
@@ -2403,6 +2612,7 @@
       <c r="Y57" s="5"/>
       <c r="Z57" s="5"/>
       <c r="AA57" s="5"/>
+      <c r="AB57" s="5"/>
     </row>
     <row r="58">
       <c r="A58" s="5"/>
@@ -2432,6 +2642,7 @@
       <c r="Y58" s="5"/>
       <c r="Z58" s="5"/>
       <c r="AA58" s="5"/>
+      <c r="AB58" s="5"/>
     </row>
     <row r="59">
       <c r="A59" s="5"/>
@@ -2461,6 +2672,7 @@
       <c r="Y59" s="5"/>
       <c r="Z59" s="5"/>
       <c r="AA59" s="5"/>
+      <c r="AB59" s="5"/>
     </row>
     <row r="60">
       <c r="A60" s="5"/>
@@ -2490,6 +2702,7 @@
       <c r="Y60" s="5"/>
       <c r="Z60" s="5"/>
       <c r="AA60" s="5"/>
+      <c r="AB60" s="5"/>
     </row>
     <row r="61">
       <c r="A61" s="5"/>
@@ -2519,6 +2732,7 @@
       <c r="Y61" s="5"/>
       <c r="Z61" s="5"/>
       <c r="AA61" s="5"/>
+      <c r="AB61" s="5"/>
     </row>
     <row r="62">
       <c r="A62" s="5"/>
@@ -2548,6 +2762,7 @@
       <c r="Y62" s="5"/>
       <c r="Z62" s="5"/>
       <c r="AA62" s="5"/>
+      <c r="AB62" s="5"/>
     </row>
     <row r="63">
       <c r="A63" s="5"/>
@@ -2577,6 +2792,7 @@
       <c r="Y63" s="5"/>
       <c r="Z63" s="5"/>
       <c r="AA63" s="5"/>
+      <c r="AB63" s="5"/>
     </row>
     <row r="64">
       <c r="A64" s="5"/>
@@ -2606,6 +2822,7 @@
       <c r="Y64" s="5"/>
       <c r="Z64" s="5"/>
       <c r="AA64" s="5"/>
+      <c r="AB64" s="5"/>
     </row>
     <row r="65">
       <c r="A65" s="5"/>
@@ -2635,6 +2852,7 @@
       <c r="Y65" s="5"/>
       <c r="Z65" s="5"/>
       <c r="AA65" s="5"/>
+      <c r="AB65" s="5"/>
     </row>
     <row r="66">
       <c r="A66" s="5"/>
@@ -2664,6 +2882,7 @@
       <c r="Y66" s="5"/>
       <c r="Z66" s="5"/>
       <c r="AA66" s="5"/>
+      <c r="AB66" s="5"/>
     </row>
     <row r="67">
       <c r="A67" s="5"/>
@@ -2693,6 +2912,7 @@
       <c r="Y67" s="5"/>
       <c r="Z67" s="5"/>
       <c r="AA67" s="5"/>
+      <c r="AB67" s="5"/>
     </row>
     <row r="68">
       <c r="A68" s="5"/>
@@ -2722,6 +2942,7 @@
       <c r="Y68" s="5"/>
       <c r="Z68" s="5"/>
       <c r="AA68" s="5"/>
+      <c r="AB68" s="5"/>
     </row>
     <row r="69">
       <c r="A69" s="5"/>
@@ -2751,6 +2972,7 @@
       <c r="Y69" s="5"/>
       <c r="Z69" s="5"/>
       <c r="AA69" s="5"/>
+      <c r="AB69" s="5"/>
     </row>
     <row r="70">
       <c r="A70" s="5"/>
@@ -2780,6 +3002,7 @@
       <c r="Y70" s="5"/>
       <c r="Z70" s="5"/>
       <c r="AA70" s="5"/>
+      <c r="AB70" s="5"/>
     </row>
     <row r="71">
       <c r="A71" s="5"/>
@@ -2809,6 +3032,7 @@
       <c r="Y71" s="5"/>
       <c r="Z71" s="5"/>
       <c r="AA71" s="5"/>
+      <c r="AB71" s="5"/>
     </row>
     <row r="72">
       <c r="A72" s="5"/>
@@ -2838,6 +3062,7 @@
       <c r="Y72" s="5"/>
       <c r="Z72" s="5"/>
       <c r="AA72" s="5"/>
+      <c r="AB72" s="5"/>
     </row>
     <row r="73">
       <c r="A73" s="5"/>
@@ -2867,6 +3092,7 @@
       <c r="Y73" s="5"/>
       <c r="Z73" s="5"/>
       <c r="AA73" s="5"/>
+      <c r="AB73" s="5"/>
     </row>
     <row r="74">
       <c r="A74" s="5"/>
@@ -2896,6 +3122,7 @@
       <c r="Y74" s="5"/>
       <c r="Z74" s="5"/>
       <c r="AA74" s="5"/>
+      <c r="AB74" s="5"/>
     </row>
     <row r="75">
       <c r="A75" s="5"/>
@@ -2925,6 +3152,7 @@
       <c r="Y75" s="5"/>
       <c r="Z75" s="5"/>
       <c r="AA75" s="5"/>
+      <c r="AB75" s="5"/>
     </row>
     <row r="76">
       <c r="A76" s="5"/>
@@ -2954,6 +3182,7 @@
       <c r="Y76" s="5"/>
       <c r="Z76" s="5"/>
       <c r="AA76" s="5"/>
+      <c r="AB76" s="5"/>
     </row>
     <row r="77">
       <c r="A77" s="5"/>
@@ -2983,6 +3212,7 @@
       <c r="Y77" s="5"/>
       <c r="Z77" s="5"/>
       <c r="AA77" s="5"/>
+      <c r="AB77" s="5"/>
     </row>
     <row r="78">
       <c r="A78" s="5"/>
@@ -3012,6 +3242,7 @@
       <c r="Y78" s="5"/>
       <c r="Z78" s="5"/>
       <c r="AA78" s="5"/>
+      <c r="AB78" s="5"/>
     </row>
     <row r="79">
       <c r="A79" s="5"/>
@@ -3041,6 +3272,7 @@
       <c r="Y79" s="5"/>
       <c r="Z79" s="5"/>
       <c r="AA79" s="5"/>
+      <c r="AB79" s="5"/>
     </row>
     <row r="80">
       <c r="A80" s="5"/>
@@ -3070,6 +3302,7 @@
       <c r="Y80" s="5"/>
       <c r="Z80" s="5"/>
       <c r="AA80" s="5"/>
+      <c r="AB80" s="5"/>
     </row>
     <row r="81">
       <c r="A81" s="5"/>
@@ -3099,6 +3332,7 @@
       <c r="Y81" s="5"/>
       <c r="Z81" s="5"/>
       <c r="AA81" s="5"/>
+      <c r="AB81" s="5"/>
     </row>
     <row r="82">
       <c r="A82" s="5"/>
@@ -3128,6 +3362,7 @@
       <c r="Y82" s="5"/>
       <c r="Z82" s="5"/>
       <c r="AA82" s="5"/>
+      <c r="AB82" s="5"/>
     </row>
     <row r="83">
       <c r="A83" s="5"/>
@@ -3157,6 +3392,7 @@
       <c r="Y83" s="5"/>
       <c r="Z83" s="5"/>
       <c r="AA83" s="5"/>
+      <c r="AB83" s="5"/>
     </row>
     <row r="84">
       <c r="A84" s="5"/>
@@ -3186,6 +3422,7 @@
       <c r="Y84" s="5"/>
       <c r="Z84" s="5"/>
       <c r="AA84" s="5"/>
+      <c r="AB84" s="5"/>
     </row>
     <row r="85">
       <c r="A85" s="5"/>
@@ -3215,6 +3452,7 @@
       <c r="Y85" s="5"/>
       <c r="Z85" s="5"/>
       <c r="AA85" s="5"/>
+      <c r="AB85" s="5"/>
     </row>
     <row r="86">
       <c r="A86" s="5"/>
@@ -3244,6 +3482,7 @@
       <c r="Y86" s="5"/>
       <c r="Z86" s="5"/>
       <c r="AA86" s="5"/>
+      <c r="AB86" s="5"/>
     </row>
     <row r="87">
       <c r="A87" s="5"/>
@@ -3273,6 +3512,7 @@
       <c r="Y87" s="5"/>
       <c r="Z87" s="5"/>
       <c r="AA87" s="5"/>
+      <c r="AB87" s="5"/>
     </row>
     <row r="88">
       <c r="A88" s="5"/>
@@ -3302,6 +3542,7 @@
       <c r="Y88" s="5"/>
       <c r="Z88" s="5"/>
       <c r="AA88" s="5"/>
+      <c r="AB88" s="5"/>
     </row>
     <row r="89">
       <c r="A89" s="5"/>
@@ -3331,6 +3572,7 @@
       <c r="Y89" s="5"/>
       <c r="Z89" s="5"/>
       <c r="AA89" s="5"/>
+      <c r="AB89" s="5"/>
     </row>
     <row r="90">
       <c r="A90" s="5"/>
@@ -3360,6 +3602,7 @@
       <c r="Y90" s="5"/>
       <c r="Z90" s="5"/>
       <c r="AA90" s="5"/>
+      <c r="AB90" s="5"/>
     </row>
     <row r="91">
       <c r="A91" s="5"/>
@@ -3389,6 +3632,7 @@
       <c r="Y91" s="5"/>
       <c r="Z91" s="5"/>
       <c r="AA91" s="5"/>
+      <c r="AB91" s="5"/>
     </row>
     <row r="92">
       <c r="A92" s="5"/>
@@ -3418,6 +3662,7 @@
       <c r="Y92" s="5"/>
       <c r="Z92" s="5"/>
       <c r="AA92" s="5"/>
+      <c r="AB92" s="5"/>
     </row>
     <row r="93">
       <c r="A93" s="5"/>
@@ -3447,6 +3692,7 @@
       <c r="Y93" s="5"/>
       <c r="Z93" s="5"/>
       <c r="AA93" s="5"/>
+      <c r="AB93" s="5"/>
     </row>
     <row r="94">
       <c r="A94" s="5"/>
@@ -3476,6 +3722,7 @@
       <c r="Y94" s="5"/>
       <c r="Z94" s="5"/>
       <c r="AA94" s="5"/>
+      <c r="AB94" s="5"/>
     </row>
     <row r="95">
       <c r="A95" s="5"/>
@@ -3505,6 +3752,7 @@
       <c r="Y95" s="5"/>
       <c r="Z95" s="5"/>
       <c r="AA95" s="5"/>
+      <c r="AB95" s="5"/>
     </row>
     <row r="96">
       <c r="A96" s="5"/>
@@ -3534,6 +3782,7 @@
       <c r="Y96" s="5"/>
       <c r="Z96" s="5"/>
       <c r="AA96" s="5"/>
+      <c r="AB96" s="5"/>
     </row>
     <row r="97">
       <c r="A97" s="5"/>
@@ -3563,6 +3812,7 @@
       <c r="Y97" s="5"/>
       <c r="Z97" s="5"/>
       <c r="AA97" s="5"/>
+      <c r="AB97" s="5"/>
     </row>
     <row r="98">
       <c r="A98" s="5"/>
@@ -3592,6 +3842,7 @@
       <c r="Y98" s="5"/>
       <c r="Z98" s="5"/>
       <c r="AA98" s="5"/>
+      <c r="AB98" s="5"/>
     </row>
     <row r="99">
       <c r="A99" s="5"/>
@@ -3621,6 +3872,7 @@
       <c r="Y99" s="5"/>
       <c r="Z99" s="5"/>
       <c r="AA99" s="5"/>
+      <c r="AB99" s="5"/>
     </row>
     <row r="100">
       <c r="A100" s="5"/>
@@ -3650,6 +3902,7 @@
       <c r="Y100" s="5"/>
       <c r="Z100" s="5"/>
       <c r="AA100" s="5"/>
+      <c r="AB100" s="5"/>
     </row>
     <row r="101">
       <c r="A101" s="5"/>
@@ -3679,6 +3932,7 @@
       <c r="Y101" s="5"/>
       <c r="Z101" s="5"/>
       <c r="AA101" s="5"/>
+      <c r="AB101" s="5"/>
     </row>
     <row r="102">
       <c r="A102" s="5"/>
@@ -3708,6 +3962,7 @@
       <c r="Y102" s="5"/>
       <c r="Z102" s="5"/>
       <c r="AA102" s="5"/>
+      <c r="AB102" s="5"/>
     </row>
     <row r="103">
       <c r="A103" s="5"/>
@@ -3737,6 +3992,7 @@
       <c r="Y103" s="5"/>
       <c r="Z103" s="5"/>
       <c r="AA103" s="5"/>
+      <c r="AB103" s="5"/>
     </row>
     <row r="104">
       <c r="A104" s="5"/>
@@ -3766,6 +4022,7 @@
       <c r="Y104" s="5"/>
       <c r="Z104" s="5"/>
       <c r="AA104" s="5"/>
+      <c r="AB104" s="5"/>
     </row>
     <row r="105">
       <c r="A105" s="5"/>
@@ -3795,6 +4052,7 @@
       <c r="Y105" s="5"/>
       <c r="Z105" s="5"/>
       <c r="AA105" s="5"/>
+      <c r="AB105" s="5"/>
     </row>
     <row r="106">
       <c r="A106" s="5"/>
@@ -3824,6 +4082,7 @@
       <c r="Y106" s="5"/>
       <c r="Z106" s="5"/>
       <c r="AA106" s="5"/>
+      <c r="AB106" s="5"/>
     </row>
     <row r="107">
       <c r="A107" s="5"/>
@@ -3853,6 +4112,7 @@
       <c r="Y107" s="5"/>
       <c r="Z107" s="5"/>
       <c r="AA107" s="5"/>
+      <c r="AB107" s="5"/>
     </row>
     <row r="108">
       <c r="A108" s="5"/>
@@ -3882,6 +4142,7 @@
       <c r="Y108" s="5"/>
       <c r="Z108" s="5"/>
       <c r="AA108" s="5"/>
+      <c r="AB108" s="5"/>
     </row>
     <row r="109">
       <c r="A109" s="5"/>
@@ -3911,6 +4172,7 @@
       <c r="Y109" s="5"/>
       <c r="Z109" s="5"/>
       <c r="AA109" s="5"/>
+      <c r="AB109" s="5"/>
     </row>
     <row r="110">
       <c r="A110" s="5"/>
@@ -3940,6 +4202,7 @@
       <c r="Y110" s="5"/>
       <c r="Z110" s="5"/>
       <c r="AA110" s="5"/>
+      <c r="AB110" s="5"/>
     </row>
     <row r="111">
       <c r="A111" s="5"/>
@@ -3969,6 +4232,7 @@
       <c r="Y111" s="5"/>
       <c r="Z111" s="5"/>
       <c r="AA111" s="5"/>
+      <c r="AB111" s="5"/>
     </row>
     <row r="112">
       <c r="A112" s="5"/>
@@ -3998,6 +4262,7 @@
       <c r="Y112" s="5"/>
       <c r="Z112" s="5"/>
       <c r="AA112" s="5"/>
+      <c r="AB112" s="5"/>
     </row>
     <row r="113">
       <c r="A113" s="5"/>
@@ -4027,6 +4292,7 @@
       <c r="Y113" s="5"/>
       <c r="Z113" s="5"/>
       <c r="AA113" s="5"/>
+      <c r="AB113" s="5"/>
     </row>
     <row r="114">
       <c r="A114" s="5"/>
@@ -4056,6 +4322,7 @@
       <c r="Y114" s="5"/>
       <c r="Z114" s="5"/>
       <c r="AA114" s="5"/>
+      <c r="AB114" s="5"/>
     </row>
     <row r="115">
       <c r="A115" s="5"/>
@@ -4085,6 +4352,7 @@
       <c r="Y115" s="5"/>
       <c r="Z115" s="5"/>
       <c r="AA115" s="5"/>
+      <c r="AB115" s="5"/>
     </row>
     <row r="116">
       <c r="A116" s="5"/>
@@ -4114,6 +4382,7 @@
       <c r="Y116" s="5"/>
       <c r="Z116" s="5"/>
       <c r="AA116" s="5"/>
+      <c r="AB116" s="5"/>
     </row>
     <row r="117">
       <c r="A117" s="5"/>
@@ -4143,6 +4412,7 @@
       <c r="Y117" s="5"/>
       <c r="Z117" s="5"/>
       <c r="AA117" s="5"/>
+      <c r="AB117" s="5"/>
     </row>
     <row r="118">
       <c r="A118" s="5"/>
@@ -4172,6 +4442,7 @@
       <c r="Y118" s="5"/>
       <c r="Z118" s="5"/>
       <c r="AA118" s="5"/>
+      <c r="AB118" s="5"/>
     </row>
     <row r="119">
       <c r="A119" s="5"/>
@@ -4201,6 +4472,7 @@
       <c r="Y119" s="5"/>
       <c r="Z119" s="5"/>
       <c r="AA119" s="5"/>
+      <c r="AB119" s="5"/>
     </row>
     <row r="120">
       <c r="A120" s="5"/>
@@ -4230,6 +4502,7 @@
       <c r="Y120" s="5"/>
       <c r="Z120" s="5"/>
       <c r="AA120" s="5"/>
+      <c r="AB120" s="5"/>
     </row>
     <row r="121">
       <c r="A121" s="5"/>
@@ -4259,6 +4532,7 @@
       <c r="Y121" s="5"/>
       <c r="Z121" s="5"/>
       <c r="AA121" s="5"/>
+      <c r="AB121" s="5"/>
     </row>
     <row r="122">
       <c r="A122" s="5"/>
@@ -4288,6 +4562,7 @@
       <c r="Y122" s="5"/>
       <c r="Z122" s="5"/>
       <c r="AA122" s="5"/>
+      <c r="AB122" s="5"/>
     </row>
     <row r="123">
       <c r="A123" s="5"/>
@@ -4317,6 +4592,7 @@
       <c r="Y123" s="5"/>
       <c r="Z123" s="5"/>
       <c r="AA123" s="5"/>
+      <c r="AB123" s="5"/>
     </row>
     <row r="124">
       <c r="A124" s="5"/>
@@ -4346,6 +4622,7 @@
       <c r="Y124" s="5"/>
       <c r="Z124" s="5"/>
       <c r="AA124" s="5"/>
+      <c r="AB124" s="5"/>
     </row>
     <row r="125">
       <c r="A125" s="5"/>
@@ -4375,6 +4652,7 @@
       <c r="Y125" s="5"/>
       <c r="Z125" s="5"/>
       <c r="AA125" s="5"/>
+      <c r="AB125" s="5"/>
     </row>
     <row r="126">
       <c r="A126" s="5"/>
@@ -4404,6 +4682,7 @@
       <c r="Y126" s="5"/>
       <c r="Z126" s="5"/>
       <c r="AA126" s="5"/>
+      <c r="AB126" s="5"/>
     </row>
     <row r="127">
       <c r="A127" s="5"/>
@@ -4433,6 +4712,7 @@
       <c r="Y127" s="5"/>
       <c r="Z127" s="5"/>
       <c r="AA127" s="5"/>
+      <c r="AB127" s="5"/>
     </row>
     <row r="128">
       <c r="A128" s="5"/>
@@ -4462,6 +4742,7 @@
       <c r="Y128" s="5"/>
       <c r="Z128" s="5"/>
       <c r="AA128" s="5"/>
+      <c r="AB128" s="5"/>
     </row>
     <row r="129">
       <c r="A129" s="5"/>
@@ -4491,6 +4772,7 @@
       <c r="Y129" s="5"/>
       <c r="Z129" s="5"/>
       <c r="AA129" s="5"/>
+      <c r="AB129" s="5"/>
     </row>
     <row r="130">
       <c r="A130" s="5"/>
@@ -4520,6 +4802,7 @@
       <c r="Y130" s="5"/>
       <c r="Z130" s="5"/>
       <c r="AA130" s="5"/>
+      <c r="AB130" s="5"/>
     </row>
     <row r="131">
       <c r="A131" s="5"/>
@@ -4549,6 +4832,7 @@
       <c r="Y131" s="5"/>
       <c r="Z131" s="5"/>
       <c r="AA131" s="5"/>
+      <c r="AB131" s="5"/>
     </row>
     <row r="132">
       <c r="A132" s="5"/>
@@ -4578,6 +4862,7 @@
       <c r="Y132" s="5"/>
       <c r="Z132" s="5"/>
       <c r="AA132" s="5"/>
+      <c r="AB132" s="5"/>
     </row>
     <row r="133">
       <c r="A133" s="5"/>
@@ -4607,6 +4892,7 @@
       <c r="Y133" s="5"/>
       <c r="Z133" s="5"/>
       <c r="AA133" s="5"/>
+      <c r="AB133" s="5"/>
     </row>
     <row r="134">
       <c r="A134" s="5"/>
@@ -4636,6 +4922,7 @@
       <c r="Y134" s="5"/>
       <c r="Z134" s="5"/>
       <c r="AA134" s="5"/>
+      <c r="AB134" s="5"/>
     </row>
     <row r="135">
       <c r="A135" s="5"/>
@@ -4665,6 +4952,7 @@
       <c r="Y135" s="5"/>
       <c r="Z135" s="5"/>
       <c r="AA135" s="5"/>
+      <c r="AB135" s="5"/>
     </row>
     <row r="136">
       <c r="A136" s="5"/>
@@ -4694,6 +4982,7 @@
       <c r="Y136" s="5"/>
       <c r="Z136" s="5"/>
       <c r="AA136" s="5"/>
+      <c r="AB136" s="5"/>
     </row>
     <row r="137">
       <c r="A137" s="5"/>
@@ -4723,6 +5012,7 @@
       <c r="Y137" s="5"/>
       <c r="Z137" s="5"/>
       <c r="AA137" s="5"/>
+      <c r="AB137" s="5"/>
     </row>
     <row r="138">
       <c r="A138" s="5"/>
@@ -4752,6 +5042,7 @@
       <c r="Y138" s="5"/>
       <c r="Z138" s="5"/>
       <c r="AA138" s="5"/>
+      <c r="AB138" s="5"/>
     </row>
     <row r="139">
       <c r="A139" s="5"/>
@@ -4781,6 +5072,7 @@
       <c r="Y139" s="5"/>
       <c r="Z139" s="5"/>
       <c r="AA139" s="5"/>
+      <c r="AB139" s="5"/>
     </row>
     <row r="140">
       <c r="A140" s="5"/>
@@ -4810,6 +5102,7 @@
       <c r="Y140" s="5"/>
       <c r="Z140" s="5"/>
       <c r="AA140" s="5"/>
+      <c r="AB140" s="5"/>
     </row>
     <row r="141">
       <c r="A141" s="5"/>
@@ -4839,6 +5132,7 @@
       <c r="Y141" s="5"/>
       <c r="Z141" s="5"/>
       <c r="AA141" s="5"/>
+      <c r="AB141" s="5"/>
     </row>
     <row r="142">
       <c r="A142" s="5"/>
@@ -4868,6 +5162,7 @@
       <c r="Y142" s="5"/>
       <c r="Z142" s="5"/>
       <c r="AA142" s="5"/>
+      <c r="AB142" s="5"/>
     </row>
     <row r="143">
       <c r="A143" s="5"/>
@@ -4897,6 +5192,7 @@
       <c r="Y143" s="5"/>
       <c r="Z143" s="5"/>
       <c r="AA143" s="5"/>
+      <c r="AB143" s="5"/>
     </row>
     <row r="144">
       <c r="A144" s="5"/>
@@ -4926,6 +5222,7 @@
       <c r="Y144" s="5"/>
       <c r="Z144" s="5"/>
       <c r="AA144" s="5"/>
+      <c r="AB144" s="5"/>
     </row>
     <row r="145">
       <c r="A145" s="5"/>
@@ -4955,6 +5252,7 @@
       <c r="Y145" s="5"/>
       <c r="Z145" s="5"/>
       <c r="AA145" s="5"/>
+      <c r="AB145" s="5"/>
     </row>
     <row r="146">
       <c r="A146" s="5"/>
@@ -4984,6 +5282,7 @@
       <c r="Y146" s="5"/>
       <c r="Z146" s="5"/>
       <c r="AA146" s="5"/>
+      <c r="AB146" s="5"/>
     </row>
     <row r="147">
       <c r="A147" s="5"/>
@@ -5013,6 +5312,7 @@
       <c r="Y147" s="5"/>
       <c r="Z147" s="5"/>
       <c r="AA147" s="5"/>
+      <c r="AB147" s="5"/>
     </row>
     <row r="148">
       <c r="A148" s="5"/>
@@ -5042,6 +5342,7 @@
       <c r="Y148" s="5"/>
       <c r="Z148" s="5"/>
       <c r="AA148" s="5"/>
+      <c r="AB148" s="5"/>
     </row>
     <row r="149">
       <c r="A149" s="5"/>
@@ -5071,6 +5372,7 @@
       <c r="Y149" s="5"/>
       <c r="Z149" s="5"/>
       <c r="AA149" s="5"/>
+      <c r="AB149" s="5"/>
     </row>
     <row r="150">
       <c r="A150" s="5"/>
@@ -5100,6 +5402,7 @@
       <c r="Y150" s="5"/>
       <c r="Z150" s="5"/>
       <c r="AA150" s="5"/>
+      <c r="AB150" s="5"/>
     </row>
     <row r="151">
       <c r="A151" s="5"/>
@@ -5129,6 +5432,7 @@
       <c r="Y151" s="5"/>
       <c r="Z151" s="5"/>
       <c r="AA151" s="5"/>
+      <c r="AB151" s="5"/>
     </row>
     <row r="152">
       <c r="A152" s="5"/>
@@ -5158,6 +5462,7 @@
       <c r="Y152" s="5"/>
       <c r="Z152" s="5"/>
       <c r="AA152" s="5"/>
+      <c r="AB152" s="5"/>
     </row>
     <row r="153">
       <c r="A153" s="5"/>
@@ -5187,6 +5492,7 @@
       <c r="Y153" s="5"/>
       <c r="Z153" s="5"/>
       <c r="AA153" s="5"/>
+      <c r="AB153" s="5"/>
     </row>
     <row r="154">
       <c r="A154" s="5"/>
@@ -5216,6 +5522,7 @@
       <c r="Y154" s="5"/>
       <c r="Z154" s="5"/>
       <c r="AA154" s="5"/>
+      <c r="AB154" s="5"/>
     </row>
     <row r="155">
       <c r="A155" s="5"/>
@@ -5245,6 +5552,7 @@
       <c r="Y155" s="5"/>
       <c r="Z155" s="5"/>
       <c r="AA155" s="5"/>
+      <c r="AB155" s="5"/>
     </row>
     <row r="156">
       <c r="A156" s="5"/>
@@ -5274,6 +5582,7 @@
       <c r="Y156" s="5"/>
       <c r="Z156" s="5"/>
       <c r="AA156" s="5"/>
+      <c r="AB156" s="5"/>
     </row>
     <row r="157">
       <c r="A157" s="5"/>
@@ -5303,6 +5612,7 @@
       <c r="Y157" s="5"/>
       <c r="Z157" s="5"/>
       <c r="AA157" s="5"/>
+      <c r="AB157" s="5"/>
     </row>
     <row r="158">
       <c r="A158" s="5"/>
@@ -5332,6 +5642,7 @@
       <c r="Y158" s="5"/>
       <c r="Z158" s="5"/>
       <c r="AA158" s="5"/>
+      <c r="AB158" s="5"/>
     </row>
     <row r="159">
       <c r="A159" s="5"/>
@@ -5361,6 +5672,7 @@
       <c r="Y159" s="5"/>
       <c r="Z159" s="5"/>
       <c r="AA159" s="5"/>
+      <c r="AB159" s="5"/>
     </row>
     <row r="160">
       <c r="A160" s="5"/>
@@ -5390,6 +5702,7 @@
       <c r="Y160" s="5"/>
       <c r="Z160" s="5"/>
       <c r="AA160" s="5"/>
+      <c r="AB160" s="5"/>
     </row>
     <row r="161">
       <c r="A161" s="5"/>
@@ -5419,6 +5732,7 @@
       <c r="Y161" s="5"/>
       <c r="Z161" s="5"/>
       <c r="AA161" s="5"/>
+      <c r="AB161" s="5"/>
     </row>
     <row r="162">
       <c r="A162" s="5"/>
@@ -5448,6 +5762,7 @@
       <c r="Y162" s="5"/>
       <c r="Z162" s="5"/>
       <c r="AA162" s="5"/>
+      <c r="AB162" s="5"/>
     </row>
     <row r="163">
       <c r="A163" s="5"/>
@@ -5477,6 +5792,7 @@
       <c r="Y163" s="5"/>
       <c r="Z163" s="5"/>
       <c r="AA163" s="5"/>
+      <c r="AB163" s="5"/>
     </row>
     <row r="164">
       <c r="A164" s="5"/>
@@ -5506,6 +5822,7 @@
       <c r="Y164" s="5"/>
       <c r="Z164" s="5"/>
       <c r="AA164" s="5"/>
+      <c r="AB164" s="5"/>
     </row>
     <row r="165">
       <c r="A165" s="5"/>
@@ -5535,6 +5852,7 @@
       <c r="Y165" s="5"/>
       <c r="Z165" s="5"/>
       <c r="AA165" s="5"/>
+      <c r="AB165" s="5"/>
     </row>
     <row r="166">
       <c r="A166" s="5"/>
@@ -5564,6 +5882,7 @@
       <c r="Y166" s="5"/>
       <c r="Z166" s="5"/>
       <c r="AA166" s="5"/>
+      <c r="AB166" s="5"/>
     </row>
     <row r="167">
       <c r="A167" s="5"/>
@@ -5593,6 +5912,7 @@
       <c r="Y167" s="5"/>
       <c r="Z167" s="5"/>
       <c r="AA167" s="5"/>
+      <c r="AB167" s="5"/>
     </row>
     <row r="168">
       <c r="A168" s="5"/>
@@ -5622,6 +5942,7 @@
       <c r="Y168" s="5"/>
       <c r="Z168" s="5"/>
       <c r="AA168" s="5"/>
+      <c r="AB168" s="5"/>
     </row>
     <row r="169">
       <c r="A169" s="5"/>
@@ -5651,6 +5972,7 @@
       <c r="Y169" s="5"/>
       <c r="Z169" s="5"/>
       <c r="AA169" s="5"/>
+      <c r="AB169" s="5"/>
     </row>
     <row r="170">
       <c r="A170" s="5"/>
@@ -5680,6 +6002,7 @@
       <c r="Y170" s="5"/>
       <c r="Z170" s="5"/>
       <c r="AA170" s="5"/>
+      <c r="AB170" s="5"/>
     </row>
     <row r="171">
       <c r="A171" s="5"/>
@@ -5709,6 +6032,7 @@
       <c r="Y171" s="5"/>
       <c r="Z171" s="5"/>
       <c r="AA171" s="5"/>
+      <c r="AB171" s="5"/>
     </row>
     <row r="172">
       <c r="A172" s="5"/>
@@ -5738,6 +6062,7 @@
       <c r="Y172" s="5"/>
       <c r="Z172" s="5"/>
       <c r="AA172" s="5"/>
+      <c r="AB172" s="5"/>
     </row>
     <row r="173">
       <c r="A173" s="5"/>
@@ -5767,6 +6092,7 @@
       <c r="Y173" s="5"/>
       <c r="Z173" s="5"/>
       <c r="AA173" s="5"/>
+      <c r="AB173" s="5"/>
     </row>
     <row r="174">
       <c r="A174" s="5"/>
@@ -5796,6 +6122,7 @@
       <c r="Y174" s="5"/>
       <c r="Z174" s="5"/>
       <c r="AA174" s="5"/>
+      <c r="AB174" s="5"/>
     </row>
     <row r="175">
       <c r="A175" s="5"/>
@@ -5825,6 +6152,7 @@
       <c r="Y175" s="5"/>
       <c r="Z175" s="5"/>
       <c r="AA175" s="5"/>
+      <c r="AB175" s="5"/>
     </row>
     <row r="176">
       <c r="A176" s="5"/>
@@ -5854,6 +6182,7 @@
       <c r="Y176" s="5"/>
       <c r="Z176" s="5"/>
       <c r="AA176" s="5"/>
+      <c r="AB176" s="5"/>
     </row>
     <row r="177">
       <c r="A177" s="5"/>
@@ -5883,6 +6212,7 @@
       <c r="Y177" s="5"/>
       <c r="Z177" s="5"/>
       <c r="AA177" s="5"/>
+      <c r="AB177" s="5"/>
     </row>
     <row r="178">
       <c r="A178" s="5"/>
@@ -5912,6 +6242,7 @@
       <c r="Y178" s="5"/>
       <c r="Z178" s="5"/>
       <c r="AA178" s="5"/>
+      <c r="AB178" s="5"/>
     </row>
     <row r="179">
       <c r="A179" s="5"/>
@@ -5941,6 +6272,7 @@
       <c r="Y179" s="5"/>
       <c r="Z179" s="5"/>
       <c r="AA179" s="5"/>
+      <c r="AB179" s="5"/>
     </row>
     <row r="180">
       <c r="A180" s="5"/>
@@ -5970,6 +6302,7 @@
       <c r="Y180" s="5"/>
       <c r="Z180" s="5"/>
       <c r="AA180" s="5"/>
+      <c r="AB180" s="5"/>
     </row>
     <row r="181">
       <c r="A181" s="5"/>
@@ -5999,6 +6332,7 @@
       <c r="Y181" s="5"/>
       <c r="Z181" s="5"/>
       <c r="AA181" s="5"/>
+      <c r="AB181" s="5"/>
     </row>
     <row r="182">
       <c r="A182" s="5"/>
@@ -6028,6 +6362,7 @@
       <c r="Y182" s="5"/>
       <c r="Z182" s="5"/>
       <c r="AA182" s="5"/>
+      <c r="AB182" s="5"/>
     </row>
     <row r="183">
       <c r="A183" s="5"/>
@@ -6057,6 +6392,7 @@
       <c r="Y183" s="5"/>
       <c r="Z183" s="5"/>
       <c r="AA183" s="5"/>
+      <c r="AB183" s="5"/>
     </row>
     <row r="184">
       <c r="A184" s="5"/>
@@ -6086,6 +6422,7 @@
       <c r="Y184" s="5"/>
       <c r="Z184" s="5"/>
       <c r="AA184" s="5"/>
+      <c r="AB184" s="5"/>
     </row>
     <row r="185">
       <c r="A185" s="5"/>
@@ -6115,6 +6452,7 @@
       <c r="Y185" s="5"/>
       <c r="Z185" s="5"/>
       <c r="AA185" s="5"/>
+      <c r="AB185" s="5"/>
     </row>
     <row r="186">
       <c r="A186" s="5"/>
@@ -6144,6 +6482,7 @@
       <c r="Y186" s="5"/>
       <c r="Z186" s="5"/>
       <c r="AA186" s="5"/>
+      <c r="AB186" s="5"/>
     </row>
     <row r="187">
       <c r="A187" s="5"/>
@@ -6173,6 +6512,7 @@
       <c r="Y187" s="5"/>
       <c r="Z187" s="5"/>
       <c r="AA187" s="5"/>
+      <c r="AB187" s="5"/>
     </row>
     <row r="188">
       <c r="A188" s="5"/>
@@ -6202,6 +6542,7 @@
       <c r="Y188" s="5"/>
       <c r="Z188" s="5"/>
       <c r="AA188" s="5"/>
+      <c r="AB188" s="5"/>
     </row>
     <row r="189">
       <c r="A189" s="5"/>
@@ -6231,6 +6572,7 @@
       <c r="Y189" s="5"/>
       <c r="Z189" s="5"/>
       <c r="AA189" s="5"/>
+      <c r="AB189" s="5"/>
     </row>
     <row r="190">
       <c r="A190" s="5"/>
@@ -6260,6 +6602,7 @@
       <c r="Y190" s="5"/>
       <c r="Z190" s="5"/>
       <c r="AA190" s="5"/>
+      <c r="AB190" s="5"/>
     </row>
     <row r="191">
       <c r="A191" s="5"/>
@@ -6289,6 +6632,7 @@
       <c r="Y191" s="5"/>
       <c r="Z191" s="5"/>
       <c r="AA191" s="5"/>
+      <c r="AB191" s="5"/>
     </row>
     <row r="192">
       <c r="A192" s="5"/>
@@ -6318,6 +6662,7 @@
       <c r="Y192" s="5"/>
       <c r="Z192" s="5"/>
       <c r="AA192" s="5"/>
+      <c r="AB192" s="5"/>
     </row>
     <row r="193">
       <c r="A193" s="5"/>
@@ -6347,6 +6692,7 @@
       <c r="Y193" s="5"/>
       <c r="Z193" s="5"/>
       <c r="AA193" s="5"/>
+      <c r="AB193" s="5"/>
     </row>
     <row r="194">
       <c r="A194" s="5"/>
@@ -6376,6 +6722,7 @@
       <c r="Y194" s="5"/>
       <c r="Z194" s="5"/>
       <c r="AA194" s="5"/>
+      <c r="AB194" s="5"/>
     </row>
     <row r="195">
       <c r="A195" s="5"/>
@@ -6405,6 +6752,7 @@
       <c r="Y195" s="5"/>
       <c r="Z195" s="5"/>
       <c r="AA195" s="5"/>
+      <c r="AB195" s="5"/>
     </row>
     <row r="196">
       <c r="A196" s="5"/>
@@ -6434,6 +6782,7 @@
       <c r="Y196" s="5"/>
       <c r="Z196" s="5"/>
       <c r="AA196" s="5"/>
+      <c r="AB196" s="5"/>
     </row>
     <row r="197">
       <c r="A197" s="5"/>
@@ -6463,6 +6812,7 @@
       <c r="Y197" s="5"/>
       <c r="Z197" s="5"/>
       <c r="AA197" s="5"/>
+      <c r="AB197" s="5"/>
     </row>
     <row r="198">
       <c r="A198" s="5"/>
@@ -6492,6 +6842,7 @@
       <c r="Y198" s="5"/>
       <c r="Z198" s="5"/>
       <c r="AA198" s="5"/>
+      <c r="AB198" s="5"/>
     </row>
     <row r="199">
       <c r="A199" s="5"/>
@@ -6521,6 +6872,7 @@
       <c r="Y199" s="5"/>
       <c r="Z199" s="5"/>
       <c r="AA199" s="5"/>
+      <c r="AB199" s="5"/>
     </row>
     <row r="200">
       <c r="A200" s="5"/>
@@ -6550,6 +6902,7 @@
       <c r="Y200" s="5"/>
       <c r="Z200" s="5"/>
       <c r="AA200" s="5"/>
+      <c r="AB200" s="5"/>
     </row>
     <row r="201">
       <c r="A201" s="5"/>
@@ -6579,6 +6932,7 @@
       <c r="Y201" s="5"/>
       <c r="Z201" s="5"/>
       <c r="AA201" s="5"/>
+      <c r="AB201" s="5"/>
     </row>
     <row r="202">
       <c r="A202" s="5"/>
@@ -6608,6 +6962,7 @@
       <c r="Y202" s="5"/>
       <c r="Z202" s="5"/>
       <c r="AA202" s="5"/>
+      <c r="AB202" s="5"/>
     </row>
     <row r="203">
       <c r="A203" s="5"/>
@@ -6637,6 +6992,7 @@
       <c r="Y203" s="5"/>
       <c r="Z203" s="5"/>
       <c r="AA203" s="5"/>
+      <c r="AB203" s="5"/>
     </row>
     <row r="204">
       <c r="A204" s="5"/>
@@ -6666,6 +7022,7 @@
       <c r="Y204" s="5"/>
       <c r="Z204" s="5"/>
       <c r="AA204" s="5"/>
+      <c r="AB204" s="5"/>
     </row>
     <row r="205">
       <c r="A205" s="5"/>
@@ -6695,6 +7052,7 @@
       <c r="Y205" s="5"/>
       <c r="Z205" s="5"/>
       <c r="AA205" s="5"/>
+      <c r="AB205" s="5"/>
     </row>
     <row r="206">
       <c r="A206" s="5"/>
@@ -6724,6 +7082,7 @@
       <c r="Y206" s="5"/>
       <c r="Z206" s="5"/>
       <c r="AA206" s="5"/>
+      <c r="AB206" s="5"/>
     </row>
     <row r="207">
       <c r="A207" s="5"/>
@@ -6753,6 +7112,7 @@
       <c r="Y207" s="5"/>
       <c r="Z207" s="5"/>
       <c r="AA207" s="5"/>
+      <c r="AB207" s="5"/>
     </row>
     <row r="208">
       <c r="A208" s="5"/>
@@ -6782,6 +7142,7 @@
       <c r="Y208" s="5"/>
       <c r="Z208" s="5"/>
       <c r="AA208" s="5"/>
+      <c r="AB208" s="5"/>
     </row>
     <row r="209">
       <c r="A209" s="5"/>
@@ -6811,6 +7172,7 @@
       <c r="Y209" s="5"/>
       <c r="Z209" s="5"/>
       <c r="AA209" s="5"/>
+      <c r="AB209" s="5"/>
     </row>
     <row r="210">
       <c r="A210" s="5"/>
@@ -6840,6 +7202,7 @@
       <c r="Y210" s="5"/>
       <c r="Z210" s="5"/>
       <c r="AA210" s="5"/>
+      <c r="AB210" s="5"/>
     </row>
     <row r="211">
       <c r="A211" s="5"/>
@@ -6869,6 +7232,7 @@
       <c r="Y211" s="5"/>
       <c r="Z211" s="5"/>
       <c r="AA211" s="5"/>
+      <c r="AB211" s="5"/>
     </row>
     <row r="212">
       <c r="A212" s="5"/>
@@ -6898,6 +7262,7 @@
       <c r="Y212" s="5"/>
       <c r="Z212" s="5"/>
       <c r="AA212" s="5"/>
+      <c r="AB212" s="5"/>
     </row>
     <row r="213">
       <c r="A213" s="5"/>
@@ -6927,6 +7292,7 @@
       <c r="Y213" s="5"/>
       <c r="Z213" s="5"/>
       <c r="AA213" s="5"/>
+      <c r="AB213" s="5"/>
     </row>
     <row r="214">
       <c r="A214" s="5"/>
@@ -6956,6 +7322,7 @@
       <c r="Y214" s="5"/>
       <c r="Z214" s="5"/>
       <c r="AA214" s="5"/>
+      <c r="AB214" s="5"/>
     </row>
     <row r="215">
       <c r="A215" s="5"/>
@@ -6985,6 +7352,7 @@
       <c r="Y215" s="5"/>
       <c r="Z215" s="5"/>
       <c r="AA215" s="5"/>
+      <c r="AB215" s="5"/>
     </row>
     <row r="216">
       <c r="A216" s="5"/>
@@ -7014,6 +7382,7 @@
       <c r="Y216" s="5"/>
       <c r="Z216" s="5"/>
       <c r="AA216" s="5"/>
+      <c r="AB216" s="5"/>
     </row>
     <row r="217">
       <c r="A217" s="5"/>
@@ -7043,6 +7412,7 @@
       <c r="Y217" s="5"/>
       <c r="Z217" s="5"/>
       <c r="AA217" s="5"/>
+      <c r="AB217" s="5"/>
     </row>
     <row r="218">
       <c r="A218" s="5"/>
@@ -7072,6 +7442,7 @@
       <c r="Y218" s="5"/>
       <c r="Z218" s="5"/>
       <c r="AA218" s="5"/>
+      <c r="AB218" s="5"/>
     </row>
     <row r="219">
       <c r="A219" s="5"/>
@@ -7101,6 +7472,7 @@
       <c r="Y219" s="5"/>
       <c r="Z219" s="5"/>
       <c r="AA219" s="5"/>
+      <c r="AB219" s="5"/>
     </row>
     <row r="220">
       <c r="A220" s="5"/>
@@ -7130,6 +7502,7 @@
       <c r="Y220" s="5"/>
       <c r="Z220" s="5"/>
       <c r="AA220" s="5"/>
+      <c r="AB220" s="5"/>
     </row>
     <row r="221">
       <c r="A221" s="5"/>
@@ -7159,6 +7532,7 @@
       <c r="Y221" s="5"/>
       <c r="Z221" s="5"/>
       <c r="AA221" s="5"/>
+      <c r="AB221" s="5"/>
     </row>
     <row r="222">
       <c r="A222" s="5"/>
@@ -7188,6 +7562,7 @@
       <c r="Y222" s="5"/>
       <c r="Z222" s="5"/>
       <c r="AA222" s="5"/>
+      <c r="AB222" s="5"/>
     </row>
     <row r="223">
       <c r="A223" s="5"/>
@@ -7217,6 +7592,7 @@
       <c r="Y223" s="5"/>
       <c r="Z223" s="5"/>
       <c r="AA223" s="5"/>
+      <c r="AB223" s="5"/>
     </row>
     <row r="224">
       <c r="A224" s="5"/>
@@ -7246,6 +7622,7 @@
       <c r="Y224" s="5"/>
       <c r="Z224" s="5"/>
       <c r="AA224" s="5"/>
+      <c r="AB224" s="5"/>
     </row>
     <row r="225">
       <c r="A225" s="5"/>
@@ -7275,6 +7652,7 @@
       <c r="Y225" s="5"/>
       <c r="Z225" s="5"/>
       <c r="AA225" s="5"/>
+      <c r="AB225" s="5"/>
     </row>
     <row r="226">
       <c r="A226" s="5"/>
@@ -7304,6 +7682,7 @@
       <c r="Y226" s="5"/>
       <c r="Z226" s="5"/>
       <c r="AA226" s="5"/>
+      <c r="AB226" s="5"/>
     </row>
     <row r="227">
       <c r="A227" s="5"/>
@@ -7333,6 +7712,7 @@
       <c r="Y227" s="5"/>
       <c r="Z227" s="5"/>
       <c r="AA227" s="5"/>
+      <c r="AB227" s="5"/>
     </row>
     <row r="228">
       <c r="A228" s="5"/>
@@ -7362,6 +7742,7 @@
       <c r="Y228" s="5"/>
       <c r="Z228" s="5"/>
       <c r="AA228" s="5"/>
+      <c r="AB228" s="5"/>
     </row>
     <row r="229">
       <c r="A229" s="5"/>
@@ -7391,6 +7772,7 @@
       <c r="Y229" s="5"/>
       <c r="Z229" s="5"/>
       <c r="AA229" s="5"/>
+      <c r="AB229" s="5"/>
     </row>
     <row r="230">
       <c r="A230" s="5"/>
@@ -7420,6 +7802,7 @@
       <c r="Y230" s="5"/>
       <c r="Z230" s="5"/>
       <c r="AA230" s="5"/>
+      <c r="AB230" s="5"/>
     </row>
     <row r="231">
       <c r="A231" s="5"/>
@@ -7449,6 +7832,7 @@
       <c r="Y231" s="5"/>
       <c r="Z231" s="5"/>
       <c r="AA231" s="5"/>
+      <c r="AB231" s="5"/>
     </row>
     <row r="232">
       <c r="A232" s="5"/>
@@ -7478,6 +7862,7 @@
       <c r="Y232" s="5"/>
       <c r="Z232" s="5"/>
       <c r="AA232" s="5"/>
+      <c r="AB232" s="5"/>
     </row>
     <row r="233">
       <c r="A233" s="5"/>
@@ -7507,6 +7892,7 @@
       <c r="Y233" s="5"/>
       <c r="Z233" s="5"/>
       <c r="AA233" s="5"/>
+      <c r="AB233" s="5"/>
     </row>
     <row r="234">
       <c r="A234" s="5"/>
@@ -7536,6 +7922,7 @@
       <c r="Y234" s="5"/>
       <c r="Z234" s="5"/>
       <c r="AA234" s="5"/>
+      <c r="AB234" s="5"/>
     </row>
     <row r="235">
       <c r="A235" s="5"/>
@@ -7565,6 +7952,7 @@
       <c r="Y235" s="5"/>
       <c r="Z235" s="5"/>
       <c r="AA235" s="5"/>
+      <c r="AB235" s="5"/>
     </row>
     <row r="236">
       <c r="A236" s="5"/>
@@ -7594,6 +7982,7 @@
       <c r="Y236" s="5"/>
       <c r="Z236" s="5"/>
       <c r="AA236" s="5"/>
+      <c r="AB236" s="5"/>
     </row>
     <row r="237">
       <c r="A237" s="5"/>
@@ -7623,6 +8012,7 @@
       <c r="Y237" s="5"/>
       <c r="Z237" s="5"/>
       <c r="AA237" s="5"/>
+      <c r="AB237" s="5"/>
     </row>
     <row r="238">
       <c r="A238" s="5"/>
@@ -7652,6 +8042,7 @@
       <c r="Y238" s="5"/>
       <c r="Z238" s="5"/>
       <c r="AA238" s="5"/>
+      <c r="AB238" s="5"/>
     </row>
     <row r="239">
       <c r="A239" s="5"/>
@@ -7681,6 +8072,7 @@
       <c r="Y239" s="5"/>
       <c r="Z239" s="5"/>
       <c r="AA239" s="5"/>
+      <c r="AB239" s="5"/>
     </row>
     <row r="240">
       <c r="A240" s="5"/>
@@ -7710,6 +8102,7 @@
       <c r="Y240" s="5"/>
       <c r="Z240" s="5"/>
       <c r="AA240" s="5"/>
+      <c r="AB240" s="5"/>
     </row>
     <row r="241">
       <c r="A241" s="5"/>
@@ -7739,6 +8132,7 @@
       <c r="Y241" s="5"/>
       <c r="Z241" s="5"/>
       <c r="AA241" s="5"/>
+      <c r="AB241" s="5"/>
     </row>
     <row r="242">
       <c r="A242" s="5"/>
@@ -7768,6 +8162,7 @@
       <c r="Y242" s="5"/>
       <c r="Z242" s="5"/>
       <c r="AA242" s="5"/>
+      <c r="AB242" s="5"/>
     </row>
     <row r="243">
       <c r="A243" s="5"/>
@@ -7797,6 +8192,7 @@
       <c r="Y243" s="5"/>
       <c r="Z243" s="5"/>
       <c r="AA243" s="5"/>
+      <c r="AB243" s="5"/>
     </row>
     <row r="244">
       <c r="A244" s="5"/>
@@ -7826,6 +8222,7 @@
       <c r="Y244" s="5"/>
       <c r="Z244" s="5"/>
       <c r="AA244" s="5"/>
+      <c r="AB244" s="5"/>
     </row>
     <row r="245">
       <c r="A245" s="5"/>
@@ -7855,6 +8252,7 @@
       <c r="Y245" s="5"/>
       <c r="Z245" s="5"/>
       <c r="AA245" s="5"/>
+      <c r="AB245" s="5"/>
     </row>
     <row r="246">
       <c r="A246" s="5"/>
@@ -7884,6 +8282,7 @@
       <c r="Y246" s="5"/>
       <c r="Z246" s="5"/>
       <c r="AA246" s="5"/>
+      <c r="AB246" s="5"/>
     </row>
     <row r="247">
       <c r="A247" s="5"/>
@@ -7913,6 +8312,7 @@
       <c r="Y247" s="5"/>
       <c r="Z247" s="5"/>
       <c r="AA247" s="5"/>
+      <c r="AB247" s="5"/>
     </row>
     <row r="248">
       <c r="A248" s="5"/>
@@ -7942,6 +8342,7 @@
       <c r="Y248" s="5"/>
       <c r="Z248" s="5"/>
       <c r="AA248" s="5"/>
+      <c r="AB248" s="5"/>
     </row>
     <row r="249">
       <c r="A249" s="5"/>
@@ -7971,6 +8372,7 @@
       <c r="Y249" s="5"/>
       <c r="Z249" s="5"/>
       <c r="AA249" s="5"/>
+      <c r="AB249" s="5"/>
     </row>
     <row r="250">
       <c r="A250" s="5"/>
@@ -8000,6 +8402,7 @@
       <c r="Y250" s="5"/>
       <c r="Z250" s="5"/>
       <c r="AA250" s="5"/>
+      <c r="AB250" s="5"/>
     </row>
     <row r="251">
       <c r="A251" s="5"/>
@@ -8029,6 +8432,7 @@
       <c r="Y251" s="5"/>
       <c r="Z251" s="5"/>
       <c r="AA251" s="5"/>
+      <c r="AB251" s="5"/>
     </row>
     <row r="252">
       <c r="A252" s="5"/>
@@ -8058,6 +8462,7 @@
       <c r="Y252" s="5"/>
       <c r="Z252" s="5"/>
       <c r="AA252" s="5"/>
+      <c r="AB252" s="5"/>
     </row>
     <row r="253">
       <c r="A253" s="5"/>
@@ -8087,6 +8492,7 @@
       <c r="Y253" s="5"/>
       <c r="Z253" s="5"/>
       <c r="AA253" s="5"/>
+      <c r="AB253" s="5"/>
     </row>
     <row r="254">
       <c r="A254" s="5"/>
@@ -8116,6 +8522,7 @@
       <c r="Y254" s="5"/>
       <c r="Z254" s="5"/>
       <c r="AA254" s="5"/>
+      <c r="AB254" s="5"/>
     </row>
     <row r="255">
       <c r="A255" s="5"/>
@@ -8145,6 +8552,7 @@
       <c r="Y255" s="5"/>
       <c r="Z255" s="5"/>
       <c r="AA255" s="5"/>
+      <c r="AB255" s="5"/>
     </row>
     <row r="256">
       <c r="A256" s="5"/>
@@ -8174,6 +8582,7 @@
       <c r="Y256" s="5"/>
       <c r="Z256" s="5"/>
       <c r="AA256" s="5"/>
+      <c r="AB256" s="5"/>
     </row>
     <row r="257">
       <c r="A257" s="5"/>
@@ -8203,6 +8612,7 @@
       <c r="Y257" s="5"/>
       <c r="Z257" s="5"/>
       <c r="AA257" s="5"/>
+      <c r="AB257" s="5"/>
     </row>
     <row r="258">
       <c r="A258" s="5"/>
@@ -8232,6 +8642,7 @@
       <c r="Y258" s="5"/>
       <c r="Z258" s="5"/>
       <c r="AA258" s="5"/>
+      <c r="AB258" s="5"/>
     </row>
     <row r="259">
       <c r="A259" s="5"/>
@@ -8261,6 +8672,7 @@
       <c r="Y259" s="5"/>
       <c r="Z259" s="5"/>
       <c r="AA259" s="5"/>
+      <c r="AB259" s="5"/>
     </row>
     <row r="260">
       <c r="A260" s="5"/>
@@ -8290,6 +8702,7 @@
       <c r="Y260" s="5"/>
       <c r="Z260" s="5"/>
       <c r="AA260" s="5"/>
+      <c r="AB260" s="5"/>
     </row>
     <row r="261">
       <c r="A261" s="5"/>
@@ -8319,6 +8732,7 @@
       <c r="Y261" s="5"/>
       <c r="Z261" s="5"/>
       <c r="AA261" s="5"/>
+      <c r="AB261" s="5"/>
     </row>
     <row r="262">
       <c r="A262" s="5"/>
@@ -8348,6 +8762,7 @@
       <c r="Y262" s="5"/>
       <c r="Z262" s="5"/>
       <c r="AA262" s="5"/>
+      <c r="AB262" s="5"/>
     </row>
     <row r="263">
       <c r="A263" s="5"/>
@@ -8377,6 +8792,7 @@
       <c r="Y263" s="5"/>
       <c r="Z263" s="5"/>
       <c r="AA263" s="5"/>
+      <c r="AB263" s="5"/>
     </row>
     <row r="264">
       <c r="A264" s="5"/>
@@ -8406,6 +8822,7 @@
       <c r="Y264" s="5"/>
       <c r="Z264" s="5"/>
       <c r="AA264" s="5"/>
+      <c r="AB264" s="5"/>
     </row>
     <row r="265">
       <c r="A265" s="5"/>
@@ -8435,6 +8852,7 @@
       <c r="Y265" s="5"/>
       <c r="Z265" s="5"/>
       <c r="AA265" s="5"/>
+      <c r="AB265" s="5"/>
     </row>
     <row r="266">
       <c r="A266" s="5"/>
@@ -8464,6 +8882,7 @@
       <c r="Y266" s="5"/>
       <c r="Z266" s="5"/>
       <c r="AA266" s="5"/>
+      <c r="AB266" s="5"/>
     </row>
     <row r="267">
       <c r="A267" s="5"/>
@@ -8493,6 +8912,7 @@
       <c r="Y267" s="5"/>
       <c r="Z267" s="5"/>
       <c r="AA267" s="5"/>
+      <c r="AB267" s="5"/>
     </row>
     <row r="268">
       <c r="A268" s="5"/>
@@ -8522,6 +8942,7 @@
       <c r="Y268" s="5"/>
       <c r="Z268" s="5"/>
       <c r="AA268" s="5"/>
+      <c r="AB268" s="5"/>
     </row>
     <row r="269">
       <c r="A269" s="5"/>
@@ -8551,6 +8972,7 @@
       <c r="Y269" s="5"/>
       <c r="Z269" s="5"/>
       <c r="AA269" s="5"/>
+      <c r="AB269" s="5"/>
     </row>
     <row r="270">
       <c r="A270" s="5"/>
@@ -8580,6 +9002,7 @@
       <c r="Y270" s="5"/>
       <c r="Z270" s="5"/>
       <c r="AA270" s="5"/>
+      <c r="AB270" s="5"/>
     </row>
     <row r="271">
       <c r="A271" s="5"/>
@@ -8609,6 +9032,7 @@
       <c r="Y271" s="5"/>
       <c r="Z271" s="5"/>
       <c r="AA271" s="5"/>
+      <c r="AB271" s="5"/>
     </row>
     <row r="272">
       <c r="A272" s="5"/>
@@ -8638,6 +9062,7 @@
       <c r="Y272" s="5"/>
       <c r="Z272" s="5"/>
       <c r="AA272" s="5"/>
+      <c r="AB272" s="5"/>
     </row>
     <row r="273">
       <c r="A273" s="5"/>
@@ -8667,6 +9092,7 @@
       <c r="Y273" s="5"/>
       <c r="Z273" s="5"/>
       <c r="AA273" s="5"/>
+      <c r="AB273" s="5"/>
     </row>
     <row r="274">
       <c r="A274" s="5"/>
@@ -8696,6 +9122,7 @@
       <c r="Y274" s="5"/>
       <c r="Z274" s="5"/>
       <c r="AA274" s="5"/>
+      <c r="AB274" s="5"/>
     </row>
     <row r="275">
       <c r="A275" s="5"/>
@@ -8725,6 +9152,7 @@
       <c r="Y275" s="5"/>
       <c r="Z275" s="5"/>
       <c r="AA275" s="5"/>
+      <c r="AB275" s="5"/>
     </row>
     <row r="276">
       <c r="A276" s="5"/>
@@ -8754,6 +9182,7 @@
       <c r="Y276" s="5"/>
       <c r="Z276" s="5"/>
       <c r="AA276" s="5"/>
+      <c r="AB276" s="5"/>
     </row>
     <row r="277">
       <c r="A277" s="5"/>
@@ -8783,6 +9212,7 @@
       <c r="Y277" s="5"/>
       <c r="Z277" s="5"/>
       <c r="AA277" s="5"/>
+      <c r="AB277" s="5"/>
     </row>
     <row r="278">
       <c r="A278" s="5"/>
@@ -8812,6 +9242,7 @@
       <c r="Y278" s="5"/>
       <c r="Z278" s="5"/>
       <c r="AA278" s="5"/>
+      <c r="AB278" s="5"/>
     </row>
     <row r="279">
       <c r="A279" s="5"/>
@@ -8841,6 +9272,7 @@
       <c r="Y279" s="5"/>
       <c r="Z279" s="5"/>
       <c r="AA279" s="5"/>
+      <c r="AB279" s="5"/>
     </row>
     <row r="280">
       <c r="A280" s="5"/>
@@ -8870,6 +9302,7 @@
       <c r="Y280" s="5"/>
       <c r="Z280" s="5"/>
       <c r="AA280" s="5"/>
+      <c r="AB280" s="5"/>
     </row>
     <row r="281">
       <c r="A281" s="5"/>
@@ -8899,6 +9332,7 @@
       <c r="Y281" s="5"/>
       <c r="Z281" s="5"/>
       <c r="AA281" s="5"/>
+      <c r="AB281" s="5"/>
     </row>
     <row r="282">
       <c r="A282" s="5"/>
@@ -8928,6 +9362,7 @@
       <c r="Y282" s="5"/>
       <c r="Z282" s="5"/>
       <c r="AA282" s="5"/>
+      <c r="AB282" s="5"/>
     </row>
     <row r="283">
       <c r="A283" s="5"/>
@@ -8957,6 +9392,7 @@
       <c r="Y283" s="5"/>
       <c r="Z283" s="5"/>
       <c r="AA283" s="5"/>
+      <c r="AB283" s="5"/>
     </row>
     <row r="284">
       <c r="A284" s="5"/>
@@ -8986,6 +9422,7 @@
       <c r="Y284" s="5"/>
       <c r="Z284" s="5"/>
       <c r="AA284" s="5"/>
+      <c r="AB284" s="5"/>
     </row>
     <row r="285">
       <c r="A285" s="5"/>
@@ -9015,6 +9452,7 @@
       <c r="Y285" s="5"/>
       <c r="Z285" s="5"/>
       <c r="AA285" s="5"/>
+      <c r="AB285" s="5"/>
     </row>
     <row r="286">
       <c r="A286" s="5"/>
@@ -9044,6 +9482,7 @@
       <c r="Y286" s="5"/>
       <c r="Z286" s="5"/>
       <c r="AA286" s="5"/>
+      <c r="AB286" s="5"/>
     </row>
     <row r="287">
       <c r="A287" s="5"/>
@@ -9073,6 +9512,7 @@
       <c r="Y287" s="5"/>
       <c r="Z287" s="5"/>
       <c r="AA287" s="5"/>
+      <c r="AB287" s="5"/>
     </row>
     <row r="288">
       <c r="A288" s="5"/>
@@ -9102,6 +9542,7 @@
       <c r="Y288" s="5"/>
       <c r="Z288" s="5"/>
       <c r="AA288" s="5"/>
+      <c r="AB288" s="5"/>
     </row>
     <row r="289">
       <c r="A289" s="5"/>
@@ -9131,6 +9572,7 @@
       <c r="Y289" s="5"/>
       <c r="Z289" s="5"/>
       <c r="AA289" s="5"/>
+      <c r="AB289" s="5"/>
     </row>
     <row r="290">
       <c r="A290" s="5"/>
@@ -9160,6 +9602,7 @@
       <c r="Y290" s="5"/>
       <c r="Z290" s="5"/>
       <c r="AA290" s="5"/>
+      <c r="AB290" s="5"/>
     </row>
     <row r="291">
       <c r="A291" s="5"/>
@@ -9189,6 +9632,7 @@
       <c r="Y291" s="5"/>
       <c r="Z291" s="5"/>
       <c r="AA291" s="5"/>
+      <c r="AB291" s="5"/>
     </row>
     <row r="292">
       <c r="A292" s="5"/>
@@ -9218,6 +9662,7 @@
       <c r="Y292" s="5"/>
       <c r="Z292" s="5"/>
       <c r="AA292" s="5"/>
+      <c r="AB292" s="5"/>
     </row>
     <row r="293">
       <c r="A293" s="5"/>
@@ -9247,6 +9692,7 @@
       <c r="Y293" s="5"/>
       <c r="Z293" s="5"/>
       <c r="AA293" s="5"/>
+      <c r="AB293" s="5"/>
     </row>
     <row r="294">
       <c r="A294" s="5"/>
@@ -9276,6 +9722,7 @@
       <c r="Y294" s="5"/>
       <c r="Z294" s="5"/>
       <c r="AA294" s="5"/>
+      <c r="AB294" s="5"/>
     </row>
     <row r="295">
       <c r="A295" s="5"/>
@@ -9305,6 +9752,7 @@
       <c r="Y295" s="5"/>
       <c r="Z295" s="5"/>
       <c r="AA295" s="5"/>
+      <c r="AB295" s="5"/>
     </row>
     <row r="296">
       <c r="A296" s="5"/>
@@ -9334,6 +9782,7 @@
       <c r="Y296" s="5"/>
       <c r="Z296" s="5"/>
       <c r="AA296" s="5"/>
+      <c r="AB296" s="5"/>
     </row>
     <row r="297">
       <c r="A297" s="5"/>
@@ -9363,6 +9812,7 @@
       <c r="Y297" s="5"/>
       <c r="Z297" s="5"/>
       <c r="AA297" s="5"/>
+      <c r="AB297" s="5"/>
     </row>
     <row r="298">
       <c r="A298" s="5"/>
@@ -9392,6 +9842,7 @@
       <c r="Y298" s="5"/>
       <c r="Z298" s="5"/>
       <c r="AA298" s="5"/>
+      <c r="AB298" s="5"/>
     </row>
     <row r="299">
       <c r="A299" s="5"/>
@@ -9421,6 +9872,7 @@
       <c r="Y299" s="5"/>
       <c r="Z299" s="5"/>
       <c r="AA299" s="5"/>
+      <c r="AB299" s="5"/>
     </row>
     <row r="300">
       <c r="A300" s="5"/>
@@ -9450,6 +9902,7 @@
       <c r="Y300" s="5"/>
       <c r="Z300" s="5"/>
       <c r="AA300" s="5"/>
+      <c r="AB300" s="5"/>
     </row>
     <row r="301">
       <c r="A301" s="5"/>
@@ -9479,6 +9932,7 @@
       <c r="Y301" s="5"/>
       <c r="Z301" s="5"/>
       <c r="AA301" s="5"/>
+      <c r="AB301" s="5"/>
     </row>
     <row r="302">
       <c r="A302" s="5"/>
@@ -9508,6 +9962,7 @@
       <c r="Y302" s="5"/>
       <c r="Z302" s="5"/>
       <c r="AA302" s="5"/>
+      <c r="AB302" s="5"/>
     </row>
     <row r="303">
       <c r="A303" s="5"/>
@@ -9537,6 +9992,7 @@
       <c r="Y303" s="5"/>
       <c r="Z303" s="5"/>
       <c r="AA303" s="5"/>
+      <c r="AB303" s="5"/>
     </row>
     <row r="304">
       <c r="A304" s="5"/>
@@ -9566,6 +10022,7 @@
       <c r="Y304" s="5"/>
       <c r="Z304" s="5"/>
       <c r="AA304" s="5"/>
+      <c r="AB304" s="5"/>
     </row>
     <row r="305">
       <c r="A305" s="5"/>
@@ -9595,6 +10052,7 @@
       <c r="Y305" s="5"/>
       <c r="Z305" s="5"/>
       <c r="AA305" s="5"/>
+      <c r="AB305" s="5"/>
     </row>
     <row r="306">
       <c r="A306" s="5"/>
@@ -9624,6 +10082,7 @@
       <c r="Y306" s="5"/>
       <c r="Z306" s="5"/>
       <c r="AA306" s="5"/>
+      <c r="AB306" s="5"/>
     </row>
     <row r="307">
       <c r="A307" s="5"/>
@@ -9653,6 +10112,7 @@
       <c r="Y307" s="5"/>
       <c r="Z307" s="5"/>
       <c r="AA307" s="5"/>
+      <c r="AB307" s="5"/>
     </row>
     <row r="308">
       <c r="A308" s="5"/>
@@ -9682,6 +10142,7 @@
       <c r="Y308" s="5"/>
       <c r="Z308" s="5"/>
       <c r="AA308" s="5"/>
+      <c r="AB308" s="5"/>
     </row>
     <row r="309">
       <c r="A309" s="5"/>
@@ -9711,6 +10172,7 @@
       <c r="Y309" s="5"/>
       <c r="Z309" s="5"/>
       <c r="AA309" s="5"/>
+      <c r="AB309" s="5"/>
     </row>
     <row r="310">
       <c r="A310" s="5"/>
@@ -9740,6 +10202,7 @@
       <c r="Y310" s="5"/>
       <c r="Z310" s="5"/>
       <c r="AA310" s="5"/>
+      <c r="AB310" s="5"/>
     </row>
     <row r="311">
       <c r="A311" s="5"/>
@@ -9769,6 +10232,7 @@
       <c r="Y311" s="5"/>
       <c r="Z311" s="5"/>
       <c r="AA311" s="5"/>
+      <c r="AB311" s="5"/>
     </row>
     <row r="312">
       <c r="A312" s="5"/>
@@ -9798,6 +10262,7 @@
       <c r="Y312" s="5"/>
       <c r="Z312" s="5"/>
       <c r="AA312" s="5"/>
+      <c r="AB312" s="5"/>
     </row>
     <row r="313">
       <c r="A313" s="5"/>
@@ -9827,6 +10292,7 @@
       <c r="Y313" s="5"/>
       <c r="Z313" s="5"/>
       <c r="AA313" s="5"/>
+      <c r="AB313" s="5"/>
     </row>
     <row r="314">
       <c r="A314" s="5"/>
@@ -9856,6 +10322,7 @@
       <c r="Y314" s="5"/>
       <c r="Z314" s="5"/>
       <c r="AA314" s="5"/>
+      <c r="AB314" s="5"/>
     </row>
     <row r="315">
       <c r="A315" s="5"/>
@@ -9885,6 +10352,7 @@
       <c r="Y315" s="5"/>
       <c r="Z315" s="5"/>
       <c r="AA315" s="5"/>
+      <c r="AB315" s="5"/>
     </row>
     <row r="316">
       <c r="A316" s="5"/>
@@ -9914,6 +10382,7 @@
       <c r="Y316" s="5"/>
       <c r="Z316" s="5"/>
       <c r="AA316" s="5"/>
+      <c r="AB316" s="5"/>
     </row>
     <row r="317">
       <c r="A317" s="5"/>
@@ -9943,6 +10412,7 @@
       <c r="Y317" s="5"/>
       <c r="Z317" s="5"/>
       <c r="AA317" s="5"/>
+      <c r="AB317" s="5"/>
     </row>
     <row r="318">
       <c r="A318" s="5"/>
@@ -9972,6 +10442,7 @@
       <c r="Y318" s="5"/>
       <c r="Z318" s="5"/>
       <c r="AA318" s="5"/>
+      <c r="AB318" s="5"/>
     </row>
     <row r="319">
       <c r="A319" s="5"/>
@@ -10001,6 +10472,7 @@
       <c r="Y319" s="5"/>
       <c r="Z319" s="5"/>
       <c r="AA319" s="5"/>
+      <c r="AB319" s="5"/>
     </row>
     <row r="320">
       <c r="A320" s="5"/>
@@ -10030,6 +10502,7 @@
       <c r="Y320" s="5"/>
       <c r="Z320" s="5"/>
       <c r="AA320" s="5"/>
+      <c r="AB320" s="5"/>
     </row>
     <row r="321">
       <c r="A321" s="5"/>
@@ -10059,6 +10532,7 @@
       <c r="Y321" s="5"/>
       <c r="Z321" s="5"/>
       <c r="AA321" s="5"/>
+      <c r="AB321" s="5"/>
     </row>
     <row r="322">
       <c r="A322" s="5"/>
@@ -10088,6 +10562,7 @@
       <c r="Y322" s="5"/>
       <c r="Z322" s="5"/>
       <c r="AA322" s="5"/>
+      <c r="AB322" s="5"/>
     </row>
     <row r="323">
       <c r="A323" s="5"/>
@@ -10117,6 +10592,7 @@
       <c r="Y323" s="5"/>
       <c r="Z323" s="5"/>
       <c r="AA323" s="5"/>
+      <c r="AB323" s="5"/>
     </row>
     <row r="324">
       <c r="A324" s="5"/>
@@ -10146,6 +10622,7 @@
       <c r="Y324" s="5"/>
       <c r="Z324" s="5"/>
       <c r="AA324" s="5"/>
+      <c r="AB324" s="5"/>
     </row>
     <row r="325">
       <c r="A325" s="5"/>
@@ -10175,6 +10652,7 @@
       <c r="Y325" s="5"/>
       <c r="Z325" s="5"/>
       <c r="AA325" s="5"/>
+      <c r="AB325" s="5"/>
     </row>
     <row r="326">
       <c r="A326" s="5"/>
@@ -10204,6 +10682,7 @@
       <c r="Y326" s="5"/>
       <c r="Z326" s="5"/>
       <c r="AA326" s="5"/>
+      <c r="AB326" s="5"/>
     </row>
     <row r="327">
       <c r="A327" s="5"/>
@@ -10233,6 +10712,7 @@
       <c r="Y327" s="5"/>
       <c r="Z327" s="5"/>
       <c r="AA327" s="5"/>
+      <c r="AB327" s="5"/>
     </row>
     <row r="328">
       <c r="A328" s="5"/>
@@ -10262,6 +10742,7 @@
       <c r="Y328" s="5"/>
       <c r="Z328" s="5"/>
       <c r="AA328" s="5"/>
+      <c r="AB328" s="5"/>
     </row>
     <row r="329">
       <c r="A329" s="5"/>
@@ -10291,6 +10772,7 @@
       <c r="Y329" s="5"/>
       <c r="Z329" s="5"/>
       <c r="AA329" s="5"/>
+      <c r="AB329" s="5"/>
     </row>
     <row r="330">
       <c r="A330" s="5"/>
@@ -10320,6 +10802,7 @@
       <c r="Y330" s="5"/>
       <c r="Z330" s="5"/>
       <c r="AA330" s="5"/>
+      <c r="AB330" s="5"/>
     </row>
     <row r="331">
       <c r="A331" s="5"/>
@@ -10349,6 +10832,7 @@
       <c r="Y331" s="5"/>
       <c r="Z331" s="5"/>
       <c r="AA331" s="5"/>
+      <c r="AB331" s="5"/>
     </row>
     <row r="332">
       <c r="A332" s="5"/>
@@ -10378,6 +10862,7 @@
       <c r="Y332" s="5"/>
       <c r="Z332" s="5"/>
       <c r="AA332" s="5"/>
+      <c r="AB332" s="5"/>
     </row>
     <row r="333">
       <c r="A333" s="5"/>
@@ -10407,6 +10892,7 @@
       <c r="Y333" s="5"/>
       <c r="Z333" s="5"/>
       <c r="AA333" s="5"/>
+      <c r="AB333" s="5"/>
     </row>
     <row r="334">
       <c r="A334" s="5"/>
@@ -10436,6 +10922,7 @@
       <c r="Y334" s="5"/>
       <c r="Z334" s="5"/>
       <c r="AA334" s="5"/>
+      <c r="AB334" s="5"/>
     </row>
     <row r="335">
       <c r="A335" s="5"/>
@@ -10465,6 +10952,7 @@
       <c r="Y335" s="5"/>
       <c r="Z335" s="5"/>
       <c r="AA335" s="5"/>
+      <c r="AB335" s="5"/>
     </row>
     <row r="336">
       <c r="A336" s="5"/>
@@ -10494,6 +10982,7 @@
       <c r="Y336" s="5"/>
       <c r="Z336" s="5"/>
       <c r="AA336" s="5"/>
+      <c r="AB336" s="5"/>
     </row>
     <row r="337">
       <c r="A337" s="5"/>
@@ -10523,6 +11012,7 @@
       <c r="Y337" s="5"/>
       <c r="Z337" s="5"/>
       <c r="AA337" s="5"/>
+      <c r="AB337" s="5"/>
     </row>
     <row r="338">
       <c r="A338" s="5"/>
@@ -10552,6 +11042,7 @@
       <c r="Y338" s="5"/>
       <c r="Z338" s="5"/>
       <c r="AA338" s="5"/>
+      <c r="AB338" s="5"/>
     </row>
     <row r="339">
       <c r="A339" s="5"/>
@@ -10581,6 +11072,7 @@
       <c r="Y339" s="5"/>
       <c r="Z339" s="5"/>
       <c r="AA339" s="5"/>
+      <c r="AB339" s="5"/>
     </row>
     <row r="340">
       <c r="A340" s="5"/>
@@ -10610,6 +11102,7 @@
       <c r="Y340" s="5"/>
       <c r="Z340" s="5"/>
       <c r="AA340" s="5"/>
+      <c r="AB340" s="5"/>
     </row>
     <row r="341">
       <c r="A341" s="5"/>
@@ -10639,6 +11132,7 @@
       <c r="Y341" s="5"/>
       <c r="Z341" s="5"/>
       <c r="AA341" s="5"/>
+      <c r="AB341" s="5"/>
     </row>
     <row r="342">
       <c r="A342" s="5"/>
@@ -10668,6 +11162,7 @@
       <c r="Y342" s="5"/>
       <c r="Z342" s="5"/>
       <c r="AA342" s="5"/>
+      <c r="AB342" s="5"/>
     </row>
     <row r="343">
       <c r="A343" s="5"/>
@@ -10697,6 +11192,7 @@
       <c r="Y343" s="5"/>
       <c r="Z343" s="5"/>
       <c r="AA343" s="5"/>
+      <c r="AB343" s="5"/>
     </row>
     <row r="344">
       <c r="A344" s="5"/>
@@ -10726,6 +11222,7 @@
       <c r="Y344" s="5"/>
       <c r="Z344" s="5"/>
       <c r="AA344" s="5"/>
+      <c r="AB344" s="5"/>
     </row>
     <row r="345">
       <c r="A345" s="5"/>
@@ -10755,6 +11252,7 @@
       <c r="Y345" s="5"/>
       <c r="Z345" s="5"/>
       <c r="AA345" s="5"/>
+      <c r="AB345" s="5"/>
     </row>
     <row r="346">
       <c r="A346" s="5"/>
@@ -10784,6 +11282,7 @@
       <c r="Y346" s="5"/>
       <c r="Z346" s="5"/>
       <c r="AA346" s="5"/>
+      <c r="AB346" s="5"/>
     </row>
     <row r="347">
       <c r="A347" s="5"/>
@@ -10813,6 +11312,7 @@
       <c r="Y347" s="5"/>
       <c r="Z347" s="5"/>
       <c r="AA347" s="5"/>
+      <c r="AB347" s="5"/>
     </row>
     <row r="348">
       <c r="A348" s="5"/>
@@ -10842,6 +11342,7 @@
       <c r="Y348" s="5"/>
       <c r="Z348" s="5"/>
       <c r="AA348" s="5"/>
+      <c r="AB348" s="5"/>
     </row>
     <row r="349">
       <c r="A349" s="5"/>
@@ -10871,6 +11372,7 @@
       <c r="Y349" s="5"/>
       <c r="Z349" s="5"/>
       <c r="AA349" s="5"/>
+      <c r="AB349" s="5"/>
     </row>
     <row r="350">
       <c r="A350" s="5"/>
@@ -10900,6 +11402,7 @@
       <c r="Y350" s="5"/>
       <c r="Z350" s="5"/>
       <c r="AA350" s="5"/>
+      <c r="AB350" s="5"/>
     </row>
     <row r="351">
       <c r="A351" s="5"/>
@@ -10929,6 +11432,7 @@
       <c r="Y351" s="5"/>
       <c r="Z351" s="5"/>
       <c r="AA351" s="5"/>
+      <c r="AB351" s="5"/>
     </row>
     <row r="352">
       <c r="A352" s="5"/>
@@ -10958,6 +11462,7 @@
       <c r="Y352" s="5"/>
       <c r="Z352" s="5"/>
       <c r="AA352" s="5"/>
+      <c r="AB352" s="5"/>
     </row>
     <row r="353">
       <c r="A353" s="5"/>
@@ -10987,6 +11492,7 @@
       <c r="Y353" s="5"/>
       <c r="Z353" s="5"/>
       <c r="AA353" s="5"/>
+      <c r="AB353" s="5"/>
     </row>
     <row r="354">
       <c r="A354" s="5"/>
@@ -11016,6 +11522,7 @@
       <c r="Y354" s="5"/>
       <c r="Z354" s="5"/>
       <c r="AA354" s="5"/>
+      <c r="AB354" s="5"/>
     </row>
     <row r="355">
       <c r="A355" s="5"/>
@@ -11045,6 +11552,7 @@
       <c r="Y355" s="5"/>
       <c r="Z355" s="5"/>
       <c r="AA355" s="5"/>
+      <c r="AB355" s="5"/>
     </row>
     <row r="356">
       <c r="A356" s="5"/>
@@ -11074,6 +11582,7 @@
       <c r="Y356" s="5"/>
       <c r="Z356" s="5"/>
       <c r="AA356" s="5"/>
+      <c r="AB356" s="5"/>
     </row>
     <row r="357">
       <c r="A357" s="5"/>
@@ -11103,6 +11612,7 @@
       <c r="Y357" s="5"/>
       <c r="Z357" s="5"/>
       <c r="AA357" s="5"/>
+      <c r="AB357" s="5"/>
     </row>
     <row r="358">
       <c r="A358" s="5"/>
@@ -11132,6 +11642,7 @@
       <c r="Y358" s="5"/>
       <c r="Z358" s="5"/>
       <c r="AA358" s="5"/>
+      <c r="AB358" s="5"/>
     </row>
     <row r="359">
       <c r="A359" s="5"/>
@@ -11161,6 +11672,7 @@
       <c r="Y359" s="5"/>
       <c r="Z359" s="5"/>
       <c r="AA359" s="5"/>
+      <c r="AB359" s="5"/>
     </row>
     <row r="360">
       <c r="A360" s="5"/>
@@ -11190,6 +11702,7 @@
       <c r="Y360" s="5"/>
       <c r="Z360" s="5"/>
       <c r="AA360" s="5"/>
+      <c r="AB360" s="5"/>
     </row>
     <row r="361">
       <c r="A361" s="5"/>
@@ -11219,6 +11732,7 @@
       <c r="Y361" s="5"/>
       <c r="Z361" s="5"/>
       <c r="AA361" s="5"/>
+      <c r="AB361" s="5"/>
     </row>
     <row r="362">
       <c r="A362" s="5"/>
@@ -11248,6 +11762,7 @@
       <c r="Y362" s="5"/>
       <c r="Z362" s="5"/>
       <c r="AA362" s="5"/>
+      <c r="AB362" s="5"/>
     </row>
     <row r="363">
       <c r="A363" s="5"/>
@@ -11277,6 +11792,7 @@
       <c r="Y363" s="5"/>
       <c r="Z363" s="5"/>
       <c r="AA363" s="5"/>
+      <c r="AB363" s="5"/>
     </row>
     <row r="364">
       <c r="A364" s="5"/>
@@ -11306,6 +11822,7 @@
       <c r="Y364" s="5"/>
       <c r="Z364" s="5"/>
       <c r="AA364" s="5"/>
+      <c r="AB364" s="5"/>
     </row>
     <row r="365">
       <c r="A365" s="5"/>
@@ -11335,6 +11852,7 @@
       <c r="Y365" s="5"/>
       <c r="Z365" s="5"/>
       <c r="AA365" s="5"/>
+      <c r="AB365" s="5"/>
     </row>
     <row r="366">
       <c r="A366" s="5"/>
@@ -11364,6 +11882,7 @@
       <c r="Y366" s="5"/>
       <c r="Z366" s="5"/>
       <c r="AA366" s="5"/>
+      <c r="AB366" s="5"/>
     </row>
     <row r="367">
       <c r="A367" s="5"/>
@@ -11393,6 +11912,7 @@
       <c r="Y367" s="5"/>
       <c r="Z367" s="5"/>
       <c r="AA367" s="5"/>
+      <c r="AB367" s="5"/>
     </row>
     <row r="368">
       <c r="A368" s="5"/>
@@ -11422,6 +11942,7 @@
       <c r="Y368" s="5"/>
       <c r="Z368" s="5"/>
       <c r="AA368" s="5"/>
+      <c r="AB368" s="5"/>
     </row>
     <row r="369">
       <c r="A369" s="5"/>
@@ -11451,6 +11972,7 @@
       <c r="Y369" s="5"/>
       <c r="Z369" s="5"/>
       <c r="AA369" s="5"/>
+      <c r="AB369" s="5"/>
     </row>
     <row r="370">
       <c r="A370" s="5"/>
@@ -11480,6 +12002,7 @@
       <c r="Y370" s="5"/>
       <c r="Z370" s="5"/>
       <c r="AA370" s="5"/>
+      <c r="AB370" s="5"/>
     </row>
     <row r="371">
       <c r="A371" s="5"/>
@@ -11509,6 +12032,7 @@
       <c r="Y371" s="5"/>
       <c r="Z371" s="5"/>
       <c r="AA371" s="5"/>
+      <c r="AB371" s="5"/>
     </row>
     <row r="372">
       <c r="A372" s="5"/>
@@ -11538,6 +12062,7 @@
       <c r="Y372" s="5"/>
       <c r="Z372" s="5"/>
       <c r="AA372" s="5"/>
+      <c r="AB372" s="5"/>
     </row>
     <row r="373">
       <c r="A373" s="5"/>
@@ -11567,6 +12092,7 @@
       <c r="Y373" s="5"/>
       <c r="Z373" s="5"/>
       <c r="AA373" s="5"/>
+      <c r="AB373" s="5"/>
     </row>
     <row r="374">
       <c r="A374" s="5"/>
@@ -11596,6 +12122,7 @@
       <c r="Y374" s="5"/>
       <c r="Z374" s="5"/>
       <c r="AA374" s="5"/>
+      <c r="AB374" s="5"/>
     </row>
     <row r="375">
       <c r="A375" s="5"/>
@@ -11625,6 +12152,7 @@
       <c r="Y375" s="5"/>
       <c r="Z375" s="5"/>
       <c r="AA375" s="5"/>
+      <c r="AB375" s="5"/>
     </row>
     <row r="376">
       <c r="A376" s="5"/>
@@ -11654,6 +12182,7 @@
       <c r="Y376" s="5"/>
       <c r="Z376" s="5"/>
       <c r="AA376" s="5"/>
+      <c r="AB376" s="5"/>
     </row>
     <row r="377">
       <c r="A377" s="5"/>
@@ -11683,6 +12212,7 @@
       <c r="Y377" s="5"/>
       <c r="Z377" s="5"/>
       <c r="AA377" s="5"/>
+      <c r="AB377" s="5"/>
     </row>
     <row r="378">
       <c r="A378" s="5"/>
@@ -11712,6 +12242,7 @@
       <c r="Y378" s="5"/>
       <c r="Z378" s="5"/>
       <c r="AA378" s="5"/>
+      <c r="AB378" s="5"/>
     </row>
     <row r="379">
       <c r="A379" s="5"/>
@@ -11741,6 +12272,7 @@
       <c r="Y379" s="5"/>
       <c r="Z379" s="5"/>
       <c r="AA379" s="5"/>
+      <c r="AB379" s="5"/>
     </row>
     <row r="380">
       <c r="A380" s="5"/>
@@ -11770,6 +12302,7 @@
       <c r="Y380" s="5"/>
       <c r="Z380" s="5"/>
       <c r="AA380" s="5"/>
+      <c r="AB380" s="5"/>
     </row>
     <row r="381">
       <c r="A381" s="5"/>
@@ -11799,6 +12332,7 @@
       <c r="Y381" s="5"/>
       <c r="Z381" s="5"/>
       <c r="AA381" s="5"/>
+      <c r="AB381" s="5"/>
     </row>
     <row r="382">
       <c r="A382" s="5"/>
@@ -11828,6 +12362,7 @@
       <c r="Y382" s="5"/>
       <c r="Z382" s="5"/>
       <c r="AA382" s="5"/>
+      <c r="AB382" s="5"/>
     </row>
     <row r="383">
       <c r="A383" s="5"/>
@@ -11857,6 +12392,7 @@
       <c r="Y383" s="5"/>
       <c r="Z383" s="5"/>
       <c r="AA383" s="5"/>
+      <c r="AB383" s="5"/>
     </row>
     <row r="384">
       <c r="A384" s="5"/>
@@ -11886,6 +12422,7 @@
       <c r="Y384" s="5"/>
       <c r="Z384" s="5"/>
       <c r="AA384" s="5"/>
+      <c r="AB384" s="5"/>
     </row>
     <row r="385">
       <c r="A385" s="5"/>
@@ -11915,6 +12452,7 @@
       <c r="Y385" s="5"/>
       <c r="Z385" s="5"/>
       <c r="AA385" s="5"/>
+      <c r="AB385" s="5"/>
     </row>
     <row r="386">
       <c r="A386" s="5"/>
@@ -11944,6 +12482,7 @@
       <c r="Y386" s="5"/>
       <c r="Z386" s="5"/>
       <c r="AA386" s="5"/>
+      <c r="AB386" s="5"/>
     </row>
     <row r="387">
       <c r="A387" s="5"/>
@@ -11973,6 +12512,7 @@
       <c r="Y387" s="5"/>
       <c r="Z387" s="5"/>
       <c r="AA387" s="5"/>
+      <c r="AB387" s="5"/>
     </row>
     <row r="388">
       <c r="A388" s="5"/>
@@ -12002,6 +12542,7 @@
       <c r="Y388" s="5"/>
       <c r="Z388" s="5"/>
       <c r="AA388" s="5"/>
+      <c r="AB388" s="5"/>
     </row>
     <row r="389">
       <c r="A389" s="5"/>
@@ -12031,6 +12572,7 @@
       <c r="Y389" s="5"/>
       <c r="Z389" s="5"/>
       <c r="AA389" s="5"/>
+      <c r="AB389" s="5"/>
     </row>
     <row r="390">
       <c r="A390" s="5"/>
@@ -12060,6 +12602,7 @@
       <c r="Y390" s="5"/>
       <c r="Z390" s="5"/>
       <c r="AA390" s="5"/>
+      <c r="AB390" s="5"/>
     </row>
     <row r="391">
       <c r="A391" s="5"/>
@@ -12089,6 +12632,7 @@
       <c r="Y391" s="5"/>
       <c r="Z391" s="5"/>
       <c r="AA391" s="5"/>
+      <c r="AB391" s="5"/>
     </row>
     <row r="392">
       <c r="A392" s="5"/>
@@ -12118,6 +12662,7 @@
       <c r="Y392" s="5"/>
       <c r="Z392" s="5"/>
       <c r="AA392" s="5"/>
+      <c r="AB392" s="5"/>
     </row>
     <row r="393">
       <c r="A393" s="5"/>
@@ -12147,6 +12692,7 @@
       <c r="Y393" s="5"/>
       <c r="Z393" s="5"/>
       <c r="AA393" s="5"/>
+      <c r="AB393" s="5"/>
     </row>
     <row r="394">
       <c r="A394" s="5"/>
@@ -12176,6 +12722,7 @@
       <c r="Y394" s="5"/>
       <c r="Z394" s="5"/>
       <c r="AA394" s="5"/>
+      <c r="AB394" s="5"/>
     </row>
     <row r="395">
       <c r="A395" s="5"/>
@@ -12205,6 +12752,7 @@
       <c r="Y395" s="5"/>
       <c r="Z395" s="5"/>
       <c r="AA395" s="5"/>
+      <c r="AB395" s="5"/>
     </row>
     <row r="396">
       <c r="A396" s="5"/>
@@ -12234,6 +12782,7 @@
       <c r="Y396" s="5"/>
       <c r="Z396" s="5"/>
       <c r="AA396" s="5"/>
+      <c r="AB396" s="5"/>
     </row>
     <row r="397">
       <c r="A397" s="5"/>
@@ -12263,6 +12812,7 @@
       <c r="Y397" s="5"/>
       <c r="Z397" s="5"/>
       <c r="AA397" s="5"/>
+      <c r="AB397" s="5"/>
     </row>
     <row r="398">
       <c r="A398" s="5"/>
@@ -12292,6 +12842,7 @@
       <c r="Y398" s="5"/>
       <c r="Z398" s="5"/>
       <c r="AA398" s="5"/>
+      <c r="AB398" s="5"/>
     </row>
     <row r="399">
       <c r="A399" s="5"/>
@@ -12321,6 +12872,7 @@
       <c r="Y399" s="5"/>
       <c r="Z399" s="5"/>
       <c r="AA399" s="5"/>
+      <c r="AB399" s="5"/>
     </row>
     <row r="400">
       <c r="A400" s="5"/>
@@ -12350,6 +12902,7 @@
       <c r="Y400" s="5"/>
       <c r="Z400" s="5"/>
       <c r="AA400" s="5"/>
+      <c r="AB400" s="5"/>
     </row>
     <row r="401">
       <c r="A401" s="5"/>
@@ -12379,6 +12932,7 @@
       <c r="Y401" s="5"/>
       <c r="Z401" s="5"/>
       <c r="AA401" s="5"/>
+      <c r="AB401" s="5"/>
     </row>
     <row r="402">
       <c r="A402" s="5"/>
@@ -12408,6 +12962,7 @@
       <c r="Y402" s="5"/>
       <c r="Z402" s="5"/>
       <c r="AA402" s="5"/>
+      <c r="AB402" s="5"/>
     </row>
     <row r="403">
       <c r="A403" s="5"/>
@@ -12437,6 +12992,7 @@
       <c r="Y403" s="5"/>
       <c r="Z403" s="5"/>
       <c r="AA403" s="5"/>
+      <c r="AB403" s="5"/>
     </row>
     <row r="404">
       <c r="A404" s="5"/>
@@ -12466,6 +13022,7 @@
       <c r="Y404" s="5"/>
       <c r="Z404" s="5"/>
       <c r="AA404" s="5"/>
+      <c r="AB404" s="5"/>
     </row>
     <row r="405">
       <c r="A405" s="5"/>
@@ -12495,6 +13052,7 @@
       <c r="Y405" s="5"/>
       <c r="Z405" s="5"/>
       <c r="AA405" s="5"/>
+      <c r="AB405" s="5"/>
     </row>
     <row r="406">
       <c r="A406" s="5"/>
@@ -12524,6 +13082,7 @@
       <c r="Y406" s="5"/>
       <c r="Z406" s="5"/>
       <c r="AA406" s="5"/>
+      <c r="AB406" s="5"/>
     </row>
     <row r="407">
       <c r="A407" s="5"/>
@@ -12553,6 +13112,7 @@
       <c r="Y407" s="5"/>
       <c r="Z407" s="5"/>
       <c r="AA407" s="5"/>
+      <c r="AB407" s="5"/>
     </row>
     <row r="408">
       <c r="A408" s="5"/>
@@ -12582,6 +13142,7 @@
       <c r="Y408" s="5"/>
       <c r="Z408" s="5"/>
       <c r="AA408" s="5"/>
+      <c r="AB408" s="5"/>
     </row>
     <row r="409">
       <c r="A409" s="5"/>
@@ -12611,6 +13172,7 @@
       <c r="Y409" s="5"/>
       <c r="Z409" s="5"/>
       <c r="AA409" s="5"/>
+      <c r="AB409" s="5"/>
     </row>
     <row r="410">
       <c r="A410" s="5"/>
@@ -12640,6 +13202,7 @@
       <c r="Y410" s="5"/>
       <c r="Z410" s="5"/>
       <c r="AA410" s="5"/>
+      <c r="AB410" s="5"/>
     </row>
     <row r="411">
       <c r="A411" s="5"/>
@@ -12669,6 +13232,7 @@
       <c r="Y411" s="5"/>
       <c r="Z411" s="5"/>
       <c r="AA411" s="5"/>
+      <c r="AB411" s="5"/>
     </row>
     <row r="412">
       <c r="A412" s="5"/>
@@ -12698,6 +13262,7 @@
       <c r="Y412" s="5"/>
       <c r="Z412" s="5"/>
       <c r="AA412" s="5"/>
+      <c r="AB412" s="5"/>
     </row>
     <row r="413">
       <c r="A413" s="5"/>
@@ -12727,6 +13292,7 @@
       <c r="Y413" s="5"/>
       <c r="Z413" s="5"/>
       <c r="AA413" s="5"/>
+      <c r="AB413" s="5"/>
     </row>
     <row r="414">
       <c r="A414" s="5"/>
@@ -12756,6 +13322,7 @@
       <c r="Y414" s="5"/>
       <c r="Z414" s="5"/>
       <c r="AA414" s="5"/>
+      <c r="AB414" s="5"/>
     </row>
     <row r="415">
       <c r="A415" s="5"/>
@@ -12785,6 +13352,7 @@
       <c r="Y415" s="5"/>
       <c r="Z415" s="5"/>
       <c r="AA415" s="5"/>
+      <c r="AB415" s="5"/>
     </row>
     <row r="416">
       <c r="A416" s="5"/>
@@ -12814,6 +13382,7 @@
       <c r="Y416" s="5"/>
       <c r="Z416" s="5"/>
       <c r="AA416" s="5"/>
+      <c r="AB416" s="5"/>
     </row>
     <row r="417">
       <c r="A417" s="5"/>
@@ -12843,6 +13412,7 @@
       <c r="Y417" s="5"/>
       <c r="Z417" s="5"/>
       <c r="AA417" s="5"/>
+      <c r="AB417" s="5"/>
     </row>
     <row r="418">
       <c r="A418" s="5"/>
@@ -12872,6 +13442,7 @@
       <c r="Y418" s="5"/>
       <c r="Z418" s="5"/>
       <c r="AA418" s="5"/>
+      <c r="AB418" s="5"/>
     </row>
     <row r="419">
       <c r="A419" s="5"/>
@@ -12901,6 +13472,7 @@
       <c r="Y419" s="5"/>
       <c r="Z419" s="5"/>
       <c r="AA419" s="5"/>
+      <c r="AB419" s="5"/>
     </row>
     <row r="420">
       <c r="A420" s="5"/>
@@ -12930,6 +13502,7 @@
       <c r="Y420" s="5"/>
       <c r="Z420" s="5"/>
       <c r="AA420" s="5"/>
+      <c r="AB420" s="5"/>
     </row>
     <row r="421">
       <c r="A421" s="5"/>
@@ -12959,6 +13532,7 @@
       <c r="Y421" s="5"/>
       <c r="Z421" s="5"/>
       <c r="AA421" s="5"/>
+      <c r="AB421" s="5"/>
     </row>
     <row r="422">
       <c r="A422" s="5"/>
@@ -12988,6 +13562,7 @@
       <c r="Y422" s="5"/>
       <c r="Z422" s="5"/>
       <c r="AA422" s="5"/>
+      <c r="AB422" s="5"/>
     </row>
     <row r="423">
       <c r="A423" s="5"/>
@@ -13017,6 +13592,7 @@
       <c r="Y423" s="5"/>
       <c r="Z423" s="5"/>
       <c r="AA423" s="5"/>
+      <c r="AB423" s="5"/>
     </row>
     <row r="424">
       <c r="A424" s="5"/>
@@ -13046,6 +13622,7 @@
       <c r="Y424" s="5"/>
       <c r="Z424" s="5"/>
       <c r="AA424" s="5"/>
+      <c r="AB424" s="5"/>
     </row>
     <row r="425">
       <c r="A425" s="5"/>
@@ -13075,6 +13652,7 @@
       <c r="Y425" s="5"/>
       <c r="Z425" s="5"/>
       <c r="AA425" s="5"/>
+      <c r="AB425" s="5"/>
     </row>
     <row r="426">
       <c r="A426" s="5"/>
@@ -13104,6 +13682,7 @@
       <c r="Y426" s="5"/>
       <c r="Z426" s="5"/>
       <c r="AA426" s="5"/>
+      <c r="AB426" s="5"/>
     </row>
     <row r="427">
       <c r="A427" s="5"/>
@@ -13133,6 +13712,7 @@
       <c r="Y427" s="5"/>
       <c r="Z427" s="5"/>
       <c r="AA427" s="5"/>
+      <c r="AB427" s="5"/>
     </row>
     <row r="428">
       <c r="A428" s="5"/>
@@ -13162,6 +13742,7 @@
       <c r="Y428" s="5"/>
       <c r="Z428" s="5"/>
       <c r="AA428" s="5"/>
+      <c r="AB428" s="5"/>
     </row>
     <row r="429">
       <c r="A429" s="5"/>
@@ -13191,6 +13772,7 @@
       <c r="Y429" s="5"/>
       <c r="Z429" s="5"/>
       <c r="AA429" s="5"/>
+      <c r="AB429" s="5"/>
     </row>
     <row r="430">
       <c r="A430" s="5"/>
@@ -13220,6 +13802,7 @@
       <c r="Y430" s="5"/>
       <c r="Z430" s="5"/>
       <c r="AA430" s="5"/>
+      <c r="AB430" s="5"/>
     </row>
     <row r="431">
       <c r="A431" s="5"/>
@@ -13249,6 +13832,7 @@
       <c r="Y431" s="5"/>
       <c r="Z431" s="5"/>
       <c r="AA431" s="5"/>
+      <c r="AB431" s="5"/>
     </row>
     <row r="432">
       <c r="A432" s="5"/>
@@ -13278,6 +13862,7 @@
       <c r="Y432" s="5"/>
       <c r="Z432" s="5"/>
       <c r="AA432" s="5"/>
+      <c r="AB432" s="5"/>
     </row>
     <row r="433">
       <c r="A433" s="5"/>
@@ -13307,6 +13892,7 @@
       <c r="Y433" s="5"/>
       <c r="Z433" s="5"/>
       <c r="AA433" s="5"/>
+      <c r="AB433" s="5"/>
     </row>
     <row r="434">
       <c r="A434" s="5"/>
@@ -13336,6 +13922,7 @@
       <c r="Y434" s="5"/>
       <c r="Z434" s="5"/>
       <c r="AA434" s="5"/>
+      <c r="AB434" s="5"/>
     </row>
     <row r="435">
       <c r="A435" s="5"/>
@@ -13365,6 +13952,7 @@
       <c r="Y435" s="5"/>
       <c r="Z435" s="5"/>
       <c r="AA435" s="5"/>
+      <c r="AB435" s="5"/>
     </row>
     <row r="436">
       <c r="A436" s="5"/>
@@ -13394,6 +13982,7 @@
       <c r="Y436" s="5"/>
       <c r="Z436" s="5"/>
       <c r="AA436" s="5"/>
+      <c r="AB436" s="5"/>
     </row>
     <row r="437">
       <c r="A437" s="5"/>
@@ -13423,6 +14012,7 @@
       <c r="Y437" s="5"/>
       <c r="Z437" s="5"/>
       <c r="AA437" s="5"/>
+      <c r="AB437" s="5"/>
     </row>
     <row r="438">
       <c r="A438" s="5"/>
@@ -13452,6 +14042,7 @@
       <c r="Y438" s="5"/>
       <c r="Z438" s="5"/>
       <c r="AA438" s="5"/>
+      <c r="AB438" s="5"/>
     </row>
     <row r="439">
       <c r="A439" s="5"/>
@@ -13481,6 +14072,7 @@
       <c r="Y439" s="5"/>
       <c r="Z439" s="5"/>
       <c r="AA439" s="5"/>
+      <c r="AB439" s="5"/>
     </row>
     <row r="440">
       <c r="A440" s="5"/>
@@ -13510,6 +14102,7 @@
       <c r="Y440" s="5"/>
       <c r="Z440" s="5"/>
       <c r="AA440" s="5"/>
+      <c r="AB440" s="5"/>
     </row>
     <row r="441">
       <c r="A441" s="5"/>
@@ -13539,6 +14132,7 @@
       <c r="Y441" s="5"/>
       <c r="Z441" s="5"/>
       <c r="AA441" s="5"/>
+      <c r="AB441" s="5"/>
     </row>
     <row r="442">
       <c r="A442" s="5"/>
@@ -13568,6 +14162,7 @@
       <c r="Y442" s="5"/>
       <c r="Z442" s="5"/>
       <c r="AA442" s="5"/>
+      <c r="AB442" s="5"/>
     </row>
     <row r="443">
       <c r="A443" s="5"/>
@@ -13597,6 +14192,7 @@
       <c r="Y443" s="5"/>
       <c r="Z443" s="5"/>
       <c r="AA443" s="5"/>
+      <c r="AB443" s="5"/>
     </row>
     <row r="444">
       <c r="A444" s="5"/>
@@ -13626,6 +14222,7 @@
       <c r="Y444" s="5"/>
       <c r="Z444" s="5"/>
       <c r="AA444" s="5"/>
+      <c r="AB444" s="5"/>
     </row>
     <row r="445">
       <c r="A445" s="5"/>
@@ -13655,6 +14252,7 @@
       <c r="Y445" s="5"/>
       <c r="Z445" s="5"/>
       <c r="AA445" s="5"/>
+      <c r="AB445" s="5"/>
     </row>
     <row r="446">
       <c r="A446" s="5"/>
@@ -13684,6 +14282,7 @@
       <c r="Y446" s="5"/>
       <c r="Z446" s="5"/>
       <c r="AA446" s="5"/>
+      <c r="AB446" s="5"/>
     </row>
     <row r="447">
       <c r="A447" s="5"/>
@@ -13713,6 +14312,7 @@
       <c r="Y447" s="5"/>
       <c r="Z447" s="5"/>
       <c r="AA447" s="5"/>
+      <c r="AB447" s="5"/>
     </row>
     <row r="448">
       <c r="A448" s="5"/>
@@ -13742,6 +14342,7 @@
       <c r="Y448" s="5"/>
       <c r="Z448" s="5"/>
       <c r="AA448" s="5"/>
+      <c r="AB448" s="5"/>
     </row>
     <row r="449">
       <c r="A449" s="5"/>
@@ -13771,6 +14372,7 @@
       <c r="Y449" s="5"/>
       <c r="Z449" s="5"/>
       <c r="AA449" s="5"/>
+      <c r="AB449" s="5"/>
     </row>
     <row r="450">
       <c r="A450" s="5"/>
@@ -13800,6 +14402,7 @@
       <c r="Y450" s="5"/>
       <c r="Z450" s="5"/>
       <c r="AA450" s="5"/>
+      <c r="AB450" s="5"/>
     </row>
     <row r="451">
       <c r="A451" s="5"/>
@@ -13829,6 +14432,7 @@
       <c r="Y451" s="5"/>
       <c r="Z451" s="5"/>
       <c r="AA451" s="5"/>
+      <c r="AB451" s="5"/>
     </row>
     <row r="452">
       <c r="A452" s="5"/>
@@ -13858,6 +14462,7 @@
       <c r="Y452" s="5"/>
       <c r="Z452" s="5"/>
       <c r="AA452" s="5"/>
+      <c r="AB452" s="5"/>
     </row>
     <row r="453">
       <c r="A453" s="5"/>
@@ -13887,6 +14492,7 @@
       <c r="Y453" s="5"/>
       <c r="Z453" s="5"/>
       <c r="AA453" s="5"/>
+      <c r="AB453" s="5"/>
     </row>
     <row r="454">
       <c r="A454" s="5"/>
@@ -13916,6 +14522,7 @@
       <c r="Y454" s="5"/>
       <c r="Z454" s="5"/>
       <c r="AA454" s="5"/>
+      <c r="AB454" s="5"/>
     </row>
     <row r="455">
       <c r="A455" s="5"/>
@@ -13945,6 +14552,7 @@
       <c r="Y455" s="5"/>
       <c r="Z455" s="5"/>
       <c r="AA455" s="5"/>
+      <c r="AB455" s="5"/>
     </row>
     <row r="456">
       <c r="A456" s="5"/>
@@ -13974,6 +14582,7 @@
       <c r="Y456" s="5"/>
       <c r="Z456" s="5"/>
       <c r="AA456" s="5"/>
+      <c r="AB456" s="5"/>
     </row>
     <row r="457">
       <c r="A457" s="5"/>
@@ -14003,6 +14612,7 @@
       <c r="Y457" s="5"/>
       <c r="Z457" s="5"/>
       <c r="AA457" s="5"/>
+      <c r="AB457" s="5"/>
     </row>
     <row r="458">
       <c r="A458" s="5"/>
@@ -14032,6 +14642,7 @@
       <c r="Y458" s="5"/>
       <c r="Z458" s="5"/>
       <c r="AA458" s="5"/>
+      <c r="AB458" s="5"/>
     </row>
     <row r="459">
       <c r="A459" s="5"/>
@@ -14061,6 +14672,7 @@
       <c r="Y459" s="5"/>
       <c r="Z459" s="5"/>
       <c r="AA459" s="5"/>
+      <c r="AB459" s="5"/>
     </row>
     <row r="460">
       <c r="A460" s="5"/>
@@ -14090,6 +14702,7 @@
       <c r="Y460" s="5"/>
       <c r="Z460" s="5"/>
       <c r="AA460" s="5"/>
+      <c r="AB460" s="5"/>
     </row>
     <row r="461">
       <c r="A461" s="5"/>
@@ -14119,6 +14732,7 @@
       <c r="Y461" s="5"/>
       <c r="Z461" s="5"/>
       <c r="AA461" s="5"/>
+      <c r="AB461" s="5"/>
     </row>
     <row r="462">
       <c r="A462" s="5"/>
@@ -14148,6 +14762,7 @@
       <c r="Y462" s="5"/>
       <c r="Z462" s="5"/>
       <c r="AA462" s="5"/>
+      <c r="AB462" s="5"/>
     </row>
     <row r="463">
       <c r="A463" s="5"/>
@@ -14177,6 +14792,7 @@
       <c r="Y463" s="5"/>
       <c r="Z463" s="5"/>
       <c r="AA463" s="5"/>
+      <c r="AB463" s="5"/>
     </row>
     <row r="464">
       <c r="A464" s="5"/>
@@ -14206,6 +14822,7 @@
       <c r="Y464" s="5"/>
       <c r="Z464" s="5"/>
       <c r="AA464" s="5"/>
+      <c r="AB464" s="5"/>
     </row>
     <row r="465">
       <c r="A465" s="5"/>
@@ -14235,6 +14852,7 @@
       <c r="Y465" s="5"/>
       <c r="Z465" s="5"/>
       <c r="AA465" s="5"/>
+      <c r="AB465" s="5"/>
     </row>
     <row r="466">
       <c r="A466" s="5"/>
@@ -14264,6 +14882,7 @@
       <c r="Y466" s="5"/>
       <c r="Z466" s="5"/>
       <c r="AA466" s="5"/>
+      <c r="AB466" s="5"/>
     </row>
     <row r="467">
       <c r="A467" s="5"/>
@@ -14293,6 +14912,7 @@
       <c r="Y467" s="5"/>
       <c r="Z467" s="5"/>
       <c r="AA467" s="5"/>
+      <c r="AB467" s="5"/>
     </row>
     <row r="468">
       <c r="A468" s="5"/>
@@ -14322,6 +14942,7 @@
       <c r="Y468" s="5"/>
       <c r="Z468" s="5"/>
       <c r="AA468" s="5"/>
+      <c r="AB468" s="5"/>
     </row>
     <row r="469">
       <c r="A469" s="5"/>
@@ -14351,6 +14972,7 @@
       <c r="Y469" s="5"/>
       <c r="Z469" s="5"/>
       <c r="AA469" s="5"/>
+      <c r="AB469" s="5"/>
     </row>
     <row r="470">
       <c r="A470" s="5"/>
@@ -14380,6 +15002,7 @@
       <c r="Y470" s="5"/>
       <c r="Z470" s="5"/>
       <c r="AA470" s="5"/>
+      <c r="AB470" s="5"/>
     </row>
     <row r="471">
       <c r="A471" s="5"/>
@@ -14409,6 +15032,7 @@
       <c r="Y471" s="5"/>
       <c r="Z471" s="5"/>
       <c r="AA471" s="5"/>
+      <c r="AB471" s="5"/>
     </row>
     <row r="472">
       <c r="A472" s="5"/>
@@ -14438,6 +15062,7 @@
       <c r="Y472" s="5"/>
       <c r="Z472" s="5"/>
       <c r="AA472" s="5"/>
+      <c r="AB472" s="5"/>
     </row>
     <row r="473">
       <c r="A473" s="5"/>
@@ -14467,6 +15092,7 @@
       <c r="Y473" s="5"/>
       <c r="Z473" s="5"/>
       <c r="AA473" s="5"/>
+      <c r="AB473" s="5"/>
     </row>
     <row r="474">
       <c r="A474" s="5"/>
@@ -14496,6 +15122,7 @@
       <c r="Y474" s="5"/>
       <c r="Z474" s="5"/>
       <c r="AA474" s="5"/>
+      <c r="AB474" s="5"/>
     </row>
     <row r="475">
       <c r="A475" s="5"/>
@@ -14525,6 +15152,7 @@
       <c r="Y475" s="5"/>
       <c r="Z475" s="5"/>
       <c r="AA475" s="5"/>
+      <c r="AB475" s="5"/>
     </row>
     <row r="476">
       <c r="A476" s="5"/>
@@ -14554,6 +15182,7 @@
       <c r="Y476" s="5"/>
       <c r="Z476" s="5"/>
       <c r="AA476" s="5"/>
+      <c r="AB476" s="5"/>
     </row>
     <row r="477">
       <c r="A477" s="5"/>
@@ -14583,6 +15212,7 @@
       <c r="Y477" s="5"/>
       <c r="Z477" s="5"/>
       <c r="AA477" s="5"/>
+      <c r="AB477" s="5"/>
     </row>
     <row r="478">
       <c r="A478" s="5"/>
@@ -14612,6 +15242,7 @@
       <c r="Y478" s="5"/>
       <c r="Z478" s="5"/>
       <c r="AA478" s="5"/>
+      <c r="AB478" s="5"/>
     </row>
     <row r="479">
       <c r="A479" s="5"/>
@@ -14641,6 +15272,7 @@
       <c r="Y479" s="5"/>
       <c r="Z479" s="5"/>
       <c r="AA479" s="5"/>
+      <c r="AB479" s="5"/>
     </row>
     <row r="480">
       <c r="A480" s="5"/>
@@ -14670,6 +15302,7 @@
       <c r="Y480" s="5"/>
       <c r="Z480" s="5"/>
       <c r="AA480" s="5"/>
+      <c r="AB480" s="5"/>
     </row>
     <row r="481">
       <c r="A481" s="5"/>
@@ -14699,6 +15332,7 @@
       <c r="Y481" s="5"/>
       <c r="Z481" s="5"/>
       <c r="AA481" s="5"/>
+      <c r="AB481" s="5"/>
     </row>
     <row r="482">
       <c r="A482" s="5"/>
@@ -14728,6 +15362,7 @@
       <c r="Y482" s="5"/>
       <c r="Z482" s="5"/>
       <c r="AA482" s="5"/>
+      <c r="AB482" s="5"/>
     </row>
     <row r="483">
       <c r="A483" s="5"/>
@@ -14757,6 +15392,7 @@
       <c r="Y483" s="5"/>
       <c r="Z483" s="5"/>
       <c r="AA483" s="5"/>
+      <c r="AB483" s="5"/>
     </row>
     <row r="484">
       <c r="A484" s="5"/>
@@ -14786,6 +15422,7 @@
       <c r="Y484" s="5"/>
       <c r="Z484" s="5"/>
       <c r="AA484" s="5"/>
+      <c r="AB484" s="5"/>
     </row>
     <row r="485">
       <c r="A485" s="5"/>
@@ -14815,6 +15452,7 @@
       <c r="Y485" s="5"/>
       <c r="Z485" s="5"/>
       <c r="AA485" s="5"/>
+      <c r="AB485" s="5"/>
     </row>
     <row r="486">
       <c r="A486" s="5"/>
@@ -14844,6 +15482,7 @@
       <c r="Y486" s="5"/>
       <c r="Z486" s="5"/>
       <c r="AA486" s="5"/>
+      <c r="AB486" s="5"/>
     </row>
     <row r="487">
       <c r="A487" s="5"/>
@@ -14873,6 +15512,7 @@
       <c r="Y487" s="5"/>
       <c r="Z487" s="5"/>
       <c r="AA487" s="5"/>
+      <c r="AB487" s="5"/>
     </row>
     <row r="488">
       <c r="A488" s="5"/>
@@ -14902,6 +15542,7 @@
       <c r="Y488" s="5"/>
       <c r="Z488" s="5"/>
       <c r="AA488" s="5"/>
+      <c r="AB488" s="5"/>
     </row>
     <row r="489">
       <c r="A489" s="5"/>
@@ -14931,6 +15572,7 @@
       <c r="Y489" s="5"/>
       <c r="Z489" s="5"/>
       <c r="AA489" s="5"/>
+      <c r="AB489" s="5"/>
     </row>
     <row r="490">
       <c r="A490" s="5"/>
@@ -14960,6 +15602,7 @@
       <c r="Y490" s="5"/>
       <c r="Z490" s="5"/>
       <c r="AA490" s="5"/>
+      <c r="AB490" s="5"/>
     </row>
     <row r="491">
       <c r="A491" s="5"/>
@@ -14989,6 +15632,7 @@
       <c r="Y491" s="5"/>
       <c r="Z491" s="5"/>
       <c r="AA491" s="5"/>
+      <c r="AB491" s="5"/>
     </row>
     <row r="492">
       <c r="A492" s="5"/>
@@ -15018,6 +15662,7 @@
       <c r="Y492" s="5"/>
       <c r="Z492" s="5"/>
       <c r="AA492" s="5"/>
+      <c r="AB492" s="5"/>
     </row>
     <row r="493">
       <c r="A493" s="5"/>
@@ -15047,6 +15692,7 @@
       <c r="Y493" s="5"/>
       <c r="Z493" s="5"/>
       <c r="AA493" s="5"/>
+      <c r="AB493" s="5"/>
     </row>
     <row r="494">
       <c r="A494" s="5"/>
@@ -15076,6 +15722,7 @@
       <c r="Y494" s="5"/>
       <c r="Z494" s="5"/>
       <c r="AA494" s="5"/>
+      <c r="AB494" s="5"/>
     </row>
     <row r="495">
       <c r="A495" s="5"/>
@@ -15105,6 +15752,7 @@
       <c r="Y495" s="5"/>
       <c r="Z495" s="5"/>
       <c r="AA495" s="5"/>
+      <c r="AB495" s="5"/>
     </row>
     <row r="496">
       <c r="A496" s="5"/>
@@ -15134,6 +15782,7 @@
       <c r="Y496" s="5"/>
       <c r="Z496" s="5"/>
       <c r="AA496" s="5"/>
+      <c r="AB496" s="5"/>
     </row>
     <row r="497">
       <c r="A497" s="5"/>
@@ -15163,6 +15812,7 @@
       <c r="Y497" s="5"/>
       <c r="Z497" s="5"/>
       <c r="AA497" s="5"/>
+      <c r="AB497" s="5"/>
     </row>
     <row r="498">
       <c r="A498" s="5"/>
@@ -15192,6 +15842,7 @@
       <c r="Y498" s="5"/>
       <c r="Z498" s="5"/>
       <c r="AA498" s="5"/>
+      <c r="AB498" s="5"/>
     </row>
     <row r="499">
       <c r="A499" s="5"/>
@@ -15221,6 +15872,7 @@
       <c r="Y499" s="5"/>
       <c r="Z499" s="5"/>
       <c r="AA499" s="5"/>
+      <c r="AB499" s="5"/>
     </row>
     <row r="500">
       <c r="A500" s="5"/>
@@ -15250,6 +15902,7 @@
       <c r="Y500" s="5"/>
       <c r="Z500" s="5"/>
       <c r="AA500" s="5"/>
+      <c r="AB500" s="5"/>
     </row>
     <row r="501">
       <c r="A501" s="5"/>
@@ -15279,6 +15932,7 @@
       <c r="Y501" s="5"/>
       <c r="Z501" s="5"/>
       <c r="AA501" s="5"/>
+      <c r="AB501" s="5"/>
     </row>
     <row r="502">
       <c r="A502" s="5"/>
@@ -15308,6 +15962,7 @@
       <c r="Y502" s="5"/>
       <c r="Z502" s="5"/>
       <c r="AA502" s="5"/>
+      <c r="AB502" s="5"/>
     </row>
     <row r="503">
       <c r="A503" s="5"/>
@@ -15337,6 +15992,7 @@
       <c r="Y503" s="5"/>
       <c r="Z503" s="5"/>
       <c r="AA503" s="5"/>
+      <c r="AB503" s="5"/>
     </row>
     <row r="504">
       <c r="A504" s="5"/>
@@ -15366,6 +16022,7 @@
       <c r="Y504" s="5"/>
       <c r="Z504" s="5"/>
       <c r="AA504" s="5"/>
+      <c r="AB504" s="5"/>
     </row>
     <row r="505">
       <c r="A505" s="5"/>
@@ -15395,6 +16052,7 @@
       <c r="Y505" s="5"/>
       <c r="Z505" s="5"/>
       <c r="AA505" s="5"/>
+      <c r="AB505" s="5"/>
     </row>
     <row r="506">
       <c r="A506" s="5"/>
@@ -15424,6 +16082,7 @@
       <c r="Y506" s="5"/>
       <c r="Z506" s="5"/>
       <c r="AA506" s="5"/>
+      <c r="AB506" s="5"/>
     </row>
     <row r="507">
       <c r="A507" s="5"/>
@@ -15453,6 +16112,7 @@
       <c r="Y507" s="5"/>
       <c r="Z507" s="5"/>
       <c r="AA507" s="5"/>
+      <c r="AB507" s="5"/>
     </row>
     <row r="508">
       <c r="A508" s="5"/>
@@ -15482,6 +16142,7 @@
       <c r="Y508" s="5"/>
       <c r="Z508" s="5"/>
       <c r="AA508" s="5"/>
+      <c r="AB508" s="5"/>
     </row>
     <row r="509">
       <c r="A509" s="5"/>
@@ -15511,6 +16172,7 @@
       <c r="Y509" s="5"/>
       <c r="Z509" s="5"/>
       <c r="AA509" s="5"/>
+      <c r="AB509" s="5"/>
     </row>
     <row r="510">
       <c r="A510" s="5"/>
@@ -15540,6 +16202,7 @@
       <c r="Y510" s="5"/>
       <c r="Z510" s="5"/>
       <c r="AA510" s="5"/>
+      <c r="AB510" s="5"/>
     </row>
     <row r="511">
       <c r="A511" s="5"/>
@@ -15569,6 +16232,7 @@
       <c r="Y511" s="5"/>
       <c r="Z511" s="5"/>
       <c r="AA511" s="5"/>
+      <c r="AB511" s="5"/>
     </row>
     <row r="512">
       <c r="A512" s="5"/>
@@ -15598,6 +16262,7 @@
       <c r="Y512" s="5"/>
       <c r="Z512" s="5"/>
       <c r="AA512" s="5"/>
+      <c r="AB512" s="5"/>
     </row>
     <row r="513">
       <c r="A513" s="5"/>
@@ -15627,6 +16292,7 @@
       <c r="Y513" s="5"/>
       <c r="Z513" s="5"/>
       <c r="AA513" s="5"/>
+      <c r="AB513" s="5"/>
     </row>
     <row r="514">
       <c r="A514" s="5"/>
@@ -15656,6 +16322,7 @@
       <c r="Y514" s="5"/>
       <c r="Z514" s="5"/>
       <c r="AA514" s="5"/>
+      <c r="AB514" s="5"/>
     </row>
     <row r="515">
       <c r="A515" s="5"/>
@@ -15685,6 +16352,7 @@
       <c r="Y515" s="5"/>
       <c r="Z515" s="5"/>
       <c r="AA515" s="5"/>
+      <c r="AB515" s="5"/>
     </row>
     <row r="516">
       <c r="A516" s="5"/>
@@ -15714,6 +16382,7 @@
       <c r="Y516" s="5"/>
       <c r="Z516" s="5"/>
       <c r="AA516" s="5"/>
+      <c r="AB516" s="5"/>
     </row>
     <row r="517">
       <c r="A517" s="5"/>
@@ -15743,6 +16412,7 @@
       <c r="Y517" s="5"/>
       <c r="Z517" s="5"/>
       <c r="AA517" s="5"/>
+      <c r="AB517" s="5"/>
     </row>
     <row r="518">
       <c r="A518" s="5"/>
@@ -15772,6 +16442,7 @@
       <c r="Y518" s="5"/>
       <c r="Z518" s="5"/>
       <c r="AA518" s="5"/>
+      <c r="AB518" s="5"/>
     </row>
     <row r="519">
       <c r="A519" s="5"/>
@@ -15801,6 +16472,7 @@
       <c r="Y519" s="5"/>
       <c r="Z519" s="5"/>
       <c r="AA519" s="5"/>
+      <c r="AB519" s="5"/>
     </row>
     <row r="520">
       <c r="A520" s="5"/>
@@ -15830,6 +16502,7 @@
       <c r="Y520" s="5"/>
       <c r="Z520" s="5"/>
       <c r="AA520" s="5"/>
+      <c r="AB520" s="5"/>
     </row>
     <row r="521">
       <c r="A521" s="5"/>
@@ -15859,6 +16532,7 @@
       <c r="Y521" s="5"/>
       <c r="Z521" s="5"/>
       <c r="AA521" s="5"/>
+      <c r="AB521" s="5"/>
     </row>
     <row r="522">
       <c r="A522" s="5"/>
@@ -15888,6 +16562,7 @@
       <c r="Y522" s="5"/>
       <c r="Z522" s="5"/>
       <c r="AA522" s="5"/>
+      <c r="AB522" s="5"/>
     </row>
     <row r="523">
       <c r="A523" s="5"/>
@@ -15917,6 +16592,7 @@
       <c r="Y523" s="5"/>
       <c r="Z523" s="5"/>
       <c r="AA523" s="5"/>
+      <c r="AB523" s="5"/>
     </row>
     <row r="524">
       <c r="A524" s="5"/>
@@ -15946,6 +16622,7 @@
       <c r="Y524" s="5"/>
       <c r="Z524" s="5"/>
       <c r="AA524" s="5"/>
+      <c r="AB524" s="5"/>
     </row>
     <row r="525">
       <c r="A525" s="5"/>
@@ -15975,6 +16652,7 @@
       <c r="Y525" s="5"/>
       <c r="Z525" s="5"/>
       <c r="AA525" s="5"/>
+      <c r="AB525" s="5"/>
     </row>
     <row r="526">
       <c r="A526" s="5"/>
@@ -16004,6 +16682,7 @@
       <c r="Y526" s="5"/>
       <c r="Z526" s="5"/>
       <c r="AA526" s="5"/>
+      <c r="AB526" s="5"/>
     </row>
     <row r="527">
       <c r="A527" s="5"/>
@@ -16033,6 +16712,7 @@
       <c r="Y527" s="5"/>
       <c r="Z527" s="5"/>
       <c r="AA527" s="5"/>
+      <c r="AB527" s="5"/>
     </row>
     <row r="528">
       <c r="A528" s="5"/>
@@ -16062,6 +16742,7 @@
       <c r="Y528" s="5"/>
       <c r="Z528" s="5"/>
       <c r="AA528" s="5"/>
+      <c r="AB528" s="5"/>
     </row>
     <row r="529">
       <c r="A529" s="5"/>
@@ -16091,6 +16772,7 @@
       <c r="Y529" s="5"/>
       <c r="Z529" s="5"/>
       <c r="AA529" s="5"/>
+      <c r="AB529" s="5"/>
     </row>
     <row r="530">
       <c r="A530" s="5"/>
@@ -16120,6 +16802,7 @@
       <c r="Y530" s="5"/>
       <c r="Z530" s="5"/>
       <c r="AA530" s="5"/>
+      <c r="AB530" s="5"/>
     </row>
     <row r="531">
       <c r="A531" s="5"/>
@@ -16149,6 +16832,7 @@
       <c r="Y531" s="5"/>
       <c r="Z531" s="5"/>
       <c r="AA531" s="5"/>
+      <c r="AB531" s="5"/>
     </row>
     <row r="532">
       <c r="A532" s="5"/>
@@ -16178,6 +16862,7 @@
       <c r="Y532" s="5"/>
       <c r="Z532" s="5"/>
       <c r="AA532" s="5"/>
+      <c r="AB532" s="5"/>
     </row>
     <row r="533">
       <c r="A533" s="5"/>
@@ -16207,6 +16892,7 @@
       <c r="Y533" s="5"/>
       <c r="Z533" s="5"/>
       <c r="AA533" s="5"/>
+      <c r="AB533" s="5"/>
     </row>
     <row r="534">
       <c r="A534" s="5"/>
@@ -16236,6 +16922,7 @@
       <c r="Y534" s="5"/>
       <c r="Z534" s="5"/>
       <c r="AA534" s="5"/>
+      <c r="AB534" s="5"/>
     </row>
     <row r="535">
       <c r="A535" s="5"/>
@@ -16265,6 +16952,7 @@
       <c r="Y535" s="5"/>
       <c r="Z535" s="5"/>
       <c r="AA535" s="5"/>
+      <c r="AB535" s="5"/>
     </row>
     <row r="536">
       <c r="A536" s="5"/>
@@ -16294,6 +16982,7 @@
       <c r="Y536" s="5"/>
       <c r="Z536" s="5"/>
       <c r="AA536" s="5"/>
+      <c r="AB536" s="5"/>
     </row>
     <row r="537">
       <c r="A537" s="5"/>
@@ -16323,6 +17012,7 @@
       <c r="Y537" s="5"/>
       <c r="Z537" s="5"/>
       <c r="AA537" s="5"/>
+      <c r="AB537" s="5"/>
     </row>
     <row r="538">
       <c r="A538" s="5"/>
@@ -16352,6 +17042,7 @@
       <c r="Y538" s="5"/>
       <c r="Z538" s="5"/>
       <c r="AA538" s="5"/>
+      <c r="AB538" s="5"/>
     </row>
     <row r="539">
       <c r="A539" s="5"/>
@@ -16381,6 +17072,7 @@
       <c r="Y539" s="5"/>
       <c r="Z539" s="5"/>
       <c r="AA539" s="5"/>
+      <c r="AB539" s="5"/>
     </row>
     <row r="540">
       <c r="A540" s="5"/>
@@ -16410,6 +17102,7 @@
       <c r="Y540" s="5"/>
       <c r="Z540" s="5"/>
       <c r="AA540" s="5"/>
+      <c r="AB540" s="5"/>
     </row>
     <row r="541">
       <c r="A541" s="5"/>
@@ -16439,6 +17132,7 @@
       <c r="Y541" s="5"/>
       <c r="Z541" s="5"/>
       <c r="AA541" s="5"/>
+      <c r="AB541" s="5"/>
     </row>
     <row r="542">
       <c r="A542" s="5"/>
@@ -16468,6 +17162,7 @@
       <c r="Y542" s="5"/>
       <c r="Z542" s="5"/>
       <c r="AA542" s="5"/>
+      <c r="AB542" s="5"/>
     </row>
     <row r="543">
       <c r="A543" s="5"/>
@@ -16497,6 +17192,7 @@
       <c r="Y543" s="5"/>
       <c r="Z543" s="5"/>
       <c r="AA543" s="5"/>
+      <c r="AB543" s="5"/>
     </row>
     <row r="544">
       <c r="A544" s="5"/>
@@ -16526,6 +17222,7 @@
       <c r="Y544" s="5"/>
       <c r="Z544" s="5"/>
       <c r="AA544" s="5"/>
+      <c r="AB544" s="5"/>
     </row>
     <row r="545">
       <c r="A545" s="5"/>
@@ -16555,6 +17252,7 @@
       <c r="Y545" s="5"/>
       <c r="Z545" s="5"/>
       <c r="AA545" s="5"/>
+      <c r="AB545" s="5"/>
     </row>
     <row r="546">
       <c r="A546" s="5"/>
@@ -16584,6 +17282,7 @@
       <c r="Y546" s="5"/>
       <c r="Z546" s="5"/>
       <c r="AA546" s="5"/>
+      <c r="AB546" s="5"/>
     </row>
     <row r="547">
       <c r="A547" s="5"/>
@@ -16613,6 +17312,7 @@
       <c r="Y547" s="5"/>
       <c r="Z547" s="5"/>
       <c r="AA547" s="5"/>
+      <c r="AB547" s="5"/>
     </row>
     <row r="548">
       <c r="A548" s="5"/>
@@ -16642,6 +17342,7 @@
       <c r="Y548" s="5"/>
       <c r="Z548" s="5"/>
       <c r="AA548" s="5"/>
+      <c r="AB548" s="5"/>
     </row>
     <row r="549">
       <c r="A549" s="5"/>
@@ -16671,6 +17372,7 @@
       <c r="Y549" s="5"/>
       <c r="Z549" s="5"/>
       <c r="AA549" s="5"/>
+      <c r="AB549" s="5"/>
     </row>
     <row r="550">
       <c r="A550" s="5"/>
@@ -16700,6 +17402,7 @@
       <c r="Y550" s="5"/>
       <c r="Z550" s="5"/>
       <c r="AA550" s="5"/>
+      <c r="AB550" s="5"/>
     </row>
     <row r="551">
       <c r="A551" s="5"/>
@@ -16729,6 +17432,7 @@
       <c r="Y551" s="5"/>
       <c r="Z551" s="5"/>
       <c r="AA551" s="5"/>
+      <c r="AB551" s="5"/>
     </row>
     <row r="552">
       <c r="A552" s="5"/>
@@ -16758,6 +17462,7 @@
       <c r="Y552" s="5"/>
       <c r="Z552" s="5"/>
       <c r="AA552" s="5"/>
+      <c r="AB552" s="5"/>
     </row>
     <row r="553">
       <c r="A553" s="5"/>
@@ -16787,6 +17492,7 @@
       <c r="Y553" s="5"/>
       <c r="Z553" s="5"/>
       <c r="AA553" s="5"/>
+      <c r="AB553" s="5"/>
     </row>
     <row r="554">
       <c r="A554" s="5"/>
@@ -16816,6 +17522,7 @@
       <c r="Y554" s="5"/>
       <c r="Z554" s="5"/>
       <c r="AA554" s="5"/>
+      <c r="AB554" s="5"/>
     </row>
     <row r="555">
       <c r="A555" s="5"/>
@@ -16845,6 +17552,7 @@
       <c r="Y555" s="5"/>
       <c r="Z555" s="5"/>
       <c r="AA555" s="5"/>
+      <c r="AB555" s="5"/>
     </row>
     <row r="556">
       <c r="A556" s="5"/>
@@ -16874,6 +17582,7 @@
       <c r="Y556" s="5"/>
       <c r="Z556" s="5"/>
       <c r="AA556" s="5"/>
+      <c r="AB556" s="5"/>
     </row>
     <row r="557">
       <c r="A557" s="5"/>
@@ -16903,6 +17612,7 @@
       <c r="Y557" s="5"/>
       <c r="Z557" s="5"/>
       <c r="AA557" s="5"/>
+      <c r="AB557" s="5"/>
     </row>
     <row r="558">
       <c r="A558" s="5"/>
@@ -16932,6 +17642,7 @@
       <c r="Y558" s="5"/>
       <c r="Z558" s="5"/>
       <c r="AA558" s="5"/>
+      <c r="AB558" s="5"/>
     </row>
     <row r="559">
       <c r="A559" s="5"/>
@@ -16961,6 +17672,7 @@
       <c r="Y559" s="5"/>
       <c r="Z559" s="5"/>
       <c r="AA559" s="5"/>
+      <c r="AB559" s="5"/>
     </row>
     <row r="560">
       <c r="A560" s="5"/>
@@ -16990,6 +17702,7 @@
       <c r="Y560" s="5"/>
       <c r="Z560" s="5"/>
       <c r="AA560" s="5"/>
+      <c r="AB560" s="5"/>
     </row>
     <row r="561">
       <c r="A561" s="5"/>
@@ -17019,6 +17732,7 @@
       <c r="Y561" s="5"/>
       <c r="Z561" s="5"/>
       <c r="AA561" s="5"/>
+      <c r="AB561" s="5"/>
     </row>
     <row r="562">
       <c r="A562" s="5"/>
@@ -17048,6 +17762,7 @@
       <c r="Y562" s="5"/>
       <c r="Z562" s="5"/>
       <c r="AA562" s="5"/>
+      <c r="AB562" s="5"/>
     </row>
     <row r="563">
       <c r="A563" s="5"/>
@@ -17077,6 +17792,7 @@
       <c r="Y563" s="5"/>
       <c r="Z563" s="5"/>
       <c r="AA563" s="5"/>
+      <c r="AB563" s="5"/>
     </row>
     <row r="564">
       <c r="A564" s="5"/>
@@ -17106,6 +17822,7 @@
       <c r="Y564" s="5"/>
       <c r="Z564" s="5"/>
       <c r="AA564" s="5"/>
+      <c r="AB564" s="5"/>
     </row>
     <row r="565">
       <c r="A565" s="5"/>
@@ -17135,6 +17852,7 @@
       <c r="Y565" s="5"/>
       <c r="Z565" s="5"/>
       <c r="AA565" s="5"/>
+      <c r="AB565" s="5"/>
     </row>
     <row r="566">
       <c r="A566" s="5"/>
@@ -17164,6 +17882,7 @@
       <c r="Y566" s="5"/>
       <c r="Z566" s="5"/>
       <c r="AA566" s="5"/>
+      <c r="AB566" s="5"/>
     </row>
     <row r="567">
       <c r="A567" s="5"/>
@@ -17193,6 +17912,7 @@
       <c r="Y567" s="5"/>
       <c r="Z567" s="5"/>
       <c r="AA567" s="5"/>
+      <c r="AB567" s="5"/>
     </row>
     <row r="568">
       <c r="A568" s="5"/>
@@ -17222,6 +17942,7 @@
       <c r="Y568" s="5"/>
       <c r="Z568" s="5"/>
       <c r="AA568" s="5"/>
+      <c r="AB568" s="5"/>
     </row>
     <row r="569">
       <c r="A569" s="5"/>
@@ -17251,6 +17972,7 @@
       <c r="Y569" s="5"/>
       <c r="Z569" s="5"/>
       <c r="AA569" s="5"/>
+      <c r="AB569" s="5"/>
     </row>
     <row r="570">
       <c r="A570" s="5"/>
@@ -17280,6 +18002,7 @@
       <c r="Y570" s="5"/>
       <c r="Z570" s="5"/>
       <c r="AA570" s="5"/>
+      <c r="AB570" s="5"/>
     </row>
     <row r="571">
       <c r="A571" s="5"/>
@@ -17309,6 +18032,7 @@
       <c r="Y571" s="5"/>
       <c r="Z571" s="5"/>
       <c r="AA571" s="5"/>
+      <c r="AB571" s="5"/>
     </row>
     <row r="572">
       <c r="A572" s="5"/>
@@ -17338,6 +18062,7 @@
       <c r="Y572" s="5"/>
       <c r="Z572" s="5"/>
       <c r="AA572" s="5"/>
+      <c r="AB572" s="5"/>
     </row>
     <row r="573">
       <c r="A573" s="5"/>
@@ -17367,6 +18092,7 @@
       <c r="Y573" s="5"/>
       <c r="Z573" s="5"/>
       <c r="AA573" s="5"/>
+      <c r="AB573" s="5"/>
     </row>
     <row r="574">
       <c r="A574" s="5"/>
@@ -17396,6 +18122,7 @@
       <c r="Y574" s="5"/>
       <c r="Z574" s="5"/>
       <c r="AA574" s="5"/>
+      <c r="AB574" s="5"/>
     </row>
     <row r="575">
       <c r="A575" s="5"/>
@@ -17425,6 +18152,7 @@
       <c r="Y575" s="5"/>
       <c r="Z575" s="5"/>
       <c r="AA575" s="5"/>
+      <c r="AB575" s="5"/>
     </row>
     <row r="576">
       <c r="A576" s="5"/>
@@ -17454,6 +18182,7 @@
       <c r="Y576" s="5"/>
       <c r="Z576" s="5"/>
       <c r="AA576" s="5"/>
+      <c r="AB576" s="5"/>
     </row>
     <row r="577">
       <c r="A577" s="5"/>
@@ -17483,6 +18212,7 @@
       <c r="Y577" s="5"/>
       <c r="Z577" s="5"/>
       <c r="AA577" s="5"/>
+      <c r="AB577" s="5"/>
     </row>
     <row r="578">
       <c r="A578" s="5"/>
@@ -17512,6 +18242,7 @@
       <c r="Y578" s="5"/>
       <c r="Z578" s="5"/>
       <c r="AA578" s="5"/>
+      <c r="AB578" s="5"/>
     </row>
     <row r="579">
       <c r="A579" s="5"/>
@@ -17541,6 +18272,7 @@
       <c r="Y579" s="5"/>
       <c r="Z579" s="5"/>
       <c r="AA579" s="5"/>
+      <c r="AB579" s="5"/>
     </row>
     <row r="580">
       <c r="A580" s="5"/>
@@ -17570,6 +18302,7 @@
       <c r="Y580" s="5"/>
       <c r="Z580" s="5"/>
       <c r="AA580" s="5"/>
+      <c r="AB580" s="5"/>
     </row>
     <row r="581">
       <c r="A581" s="5"/>
@@ -17599,6 +18332,7 @@
       <c r="Y581" s="5"/>
       <c r="Z581" s="5"/>
       <c r="AA581" s="5"/>
+      <c r="AB581" s="5"/>
     </row>
     <row r="582">
       <c r="A582" s="5"/>
@@ -17628,6 +18362,7 @@
       <c r="Y582" s="5"/>
       <c r="Z582" s="5"/>
       <c r="AA582" s="5"/>
+      <c r="AB582" s="5"/>
     </row>
     <row r="583">
       <c r="A583" s="5"/>
@@ -17657,6 +18392,7 @@
       <c r="Y583" s="5"/>
       <c r="Z583" s="5"/>
       <c r="AA583" s="5"/>
+      <c r="AB583" s="5"/>
     </row>
     <row r="584">
       <c r="A584" s="5"/>
@@ -17686,6 +18422,7 @@
       <c r="Y584" s="5"/>
       <c r="Z584" s="5"/>
       <c r="AA584" s="5"/>
+      <c r="AB584" s="5"/>
     </row>
     <row r="585">
       <c r="A585" s="5"/>
@@ -17715,6 +18452,7 @@
       <c r="Y585" s="5"/>
       <c r="Z585" s="5"/>
       <c r="AA585" s="5"/>
+      <c r="AB585" s="5"/>
     </row>
     <row r="586">
       <c r="A586" s="5"/>
@@ -17744,6 +18482,7 @@
       <c r="Y586" s="5"/>
       <c r="Z586" s="5"/>
       <c r="AA586" s="5"/>
+      <c r="AB586" s="5"/>
     </row>
     <row r="587">
       <c r="A587" s="5"/>
@@ -17773,6 +18512,7 @@
       <c r="Y587" s="5"/>
       <c r="Z587" s="5"/>
       <c r="AA587" s="5"/>
+      <c r="AB587" s="5"/>
     </row>
     <row r="588">
       <c r="A588" s="5"/>
@@ -17802,6 +18542,7 @@
       <c r="Y588" s="5"/>
       <c r="Z588" s="5"/>
       <c r="AA588" s="5"/>
+      <c r="AB588" s="5"/>
     </row>
     <row r="589">
       <c r="A589" s="5"/>
@@ -17831,6 +18572,7 @@
       <c r="Y589" s="5"/>
       <c r="Z589" s="5"/>
       <c r="AA589" s="5"/>
+      <c r="AB589" s="5"/>
     </row>
     <row r="590">
       <c r="A590" s="5"/>
@@ -17860,6 +18602,7 @@
       <c r="Y590" s="5"/>
       <c r="Z590" s="5"/>
       <c r="AA590" s="5"/>
+      <c r="AB590" s="5"/>
     </row>
     <row r="591">
       <c r="A591" s="5"/>
@@ -17889,6 +18632,7 @@
       <c r="Y591" s="5"/>
       <c r="Z591" s="5"/>
       <c r="AA591" s="5"/>
+      <c r="AB591" s="5"/>
     </row>
     <row r="592">
       <c r="A592" s="5"/>
@@ -17918,6 +18662,7 @@
       <c r="Y592" s="5"/>
       <c r="Z592" s="5"/>
       <c r="AA592" s="5"/>
+      <c r="AB592" s="5"/>
     </row>
     <row r="593">
       <c r="A593" s="5"/>
@@ -17947,6 +18692,7 @@
       <c r="Y593" s="5"/>
       <c r="Z593" s="5"/>
       <c r="AA593" s="5"/>
+      <c r="AB593" s="5"/>
     </row>
     <row r="594">
       <c r="A594" s="5"/>
@@ -17976,6 +18722,7 @@
       <c r="Y594" s="5"/>
       <c r="Z594" s="5"/>
       <c r="AA594" s="5"/>
+      <c r="AB594" s="5"/>
     </row>
     <row r="595">
       <c r="A595" s="5"/>
@@ -18005,6 +18752,7 @@
       <c r="Y595" s="5"/>
       <c r="Z595" s="5"/>
       <c r="AA595" s="5"/>
+      <c r="AB595" s="5"/>
     </row>
     <row r="596">
       <c r="A596" s="5"/>
@@ -18034,6 +18782,7 @@
       <c r="Y596" s="5"/>
       <c r="Z596" s="5"/>
       <c r="AA596" s="5"/>
+      <c r="AB596" s="5"/>
     </row>
     <row r="597">
       <c r="A597" s="5"/>
@@ -18063,6 +18812,7 @@
       <c r="Y597" s="5"/>
       <c r="Z597" s="5"/>
       <c r="AA597" s="5"/>
+      <c r="AB597" s="5"/>
     </row>
     <row r="598">
       <c r="A598" s="5"/>
@@ -18092,6 +18842,7 @@
       <c r="Y598" s="5"/>
       <c r="Z598" s="5"/>
       <c r="AA598" s="5"/>
+      <c r="AB598" s="5"/>
     </row>
     <row r="599">
       <c r="A599" s="5"/>
@@ -18121,6 +18872,7 @@
       <c r="Y599" s="5"/>
       <c r="Z599" s="5"/>
       <c r="AA599" s="5"/>
+      <c r="AB599" s="5"/>
     </row>
     <row r="600">
       <c r="A600" s="5"/>
@@ -18150,6 +18902,7 @@
       <c r="Y600" s="5"/>
       <c r="Z600" s="5"/>
       <c r="AA600" s="5"/>
+      <c r="AB600" s="5"/>
     </row>
     <row r="601">
       <c r="A601" s="5"/>
@@ -18179,6 +18932,7 @@
       <c r="Y601" s="5"/>
       <c r="Z601" s="5"/>
       <c r="AA601" s="5"/>
+      <c r="AB601" s="5"/>
     </row>
     <row r="602">
       <c r="A602" s="5"/>
@@ -18208,6 +18962,7 @@
       <c r="Y602" s="5"/>
       <c r="Z602" s="5"/>
       <c r="AA602" s="5"/>
+      <c r="AB602" s="5"/>
     </row>
     <row r="603">
       <c r="A603" s="5"/>
@@ -18237,6 +18992,7 @@
       <c r="Y603" s="5"/>
       <c r="Z603" s="5"/>
       <c r="AA603" s="5"/>
+      <c r="AB603" s="5"/>
     </row>
     <row r="604">
       <c r="A604" s="5"/>
@@ -18266,6 +19022,7 @@
       <c r="Y604" s="5"/>
       <c r="Z604" s="5"/>
       <c r="AA604" s="5"/>
+      <c r="AB604" s="5"/>
     </row>
     <row r="605">
       <c r="A605" s="5"/>
@@ -18295,6 +19052,7 @@
       <c r="Y605" s="5"/>
       <c r="Z605" s="5"/>
       <c r="AA605" s="5"/>
+      <c r="AB605" s="5"/>
     </row>
     <row r="606">
       <c r="A606" s="5"/>
@@ -18324,6 +19082,7 @@
       <c r="Y606" s="5"/>
       <c r="Z606" s="5"/>
       <c r="AA606" s="5"/>
+      <c r="AB606" s="5"/>
     </row>
     <row r="607">
       <c r="A607" s="5"/>
@@ -18353,6 +19112,7 @@
       <c r="Y607" s="5"/>
       <c r="Z607" s="5"/>
       <c r="AA607" s="5"/>
+      <c r="AB607" s="5"/>
     </row>
     <row r="608">
       <c r="A608" s="5"/>
@@ -18382,6 +19142,7 @@
       <c r="Y608" s="5"/>
       <c r="Z608" s="5"/>
       <c r="AA608" s="5"/>
+      <c r="AB608" s="5"/>
     </row>
     <row r="609">
       <c r="A609" s="5"/>
@@ -18411,6 +19172,7 @@
       <c r="Y609" s="5"/>
       <c r="Z609" s="5"/>
       <c r="AA609" s="5"/>
+      <c r="AB609" s="5"/>
     </row>
     <row r="610">
       <c r="A610" s="5"/>
@@ -18440,6 +19202,7 @@
       <c r="Y610" s="5"/>
       <c r="Z610" s="5"/>
       <c r="AA610" s="5"/>
+      <c r="AB610" s="5"/>
     </row>
     <row r="611">
       <c r="A611" s="5"/>
@@ -18469,6 +19232,7 @@
       <c r="Y611" s="5"/>
       <c r="Z611" s="5"/>
       <c r="AA611" s="5"/>
+      <c r="AB611" s="5"/>
     </row>
     <row r="612">
       <c r="A612" s="5"/>
@@ -18498,6 +19262,7 @@
       <c r="Y612" s="5"/>
       <c r="Z612" s="5"/>
       <c r="AA612" s="5"/>
+      <c r="AB612" s="5"/>
     </row>
     <row r="613">
       <c r="A613" s="5"/>
@@ -18527,6 +19292,7 @@
       <c r="Y613" s="5"/>
       <c r="Z613" s="5"/>
       <c r="AA613" s="5"/>
+      <c r="AB613" s="5"/>
     </row>
     <row r="614">
       <c r="A614" s="5"/>
@@ -18556,6 +19322,7 @@
       <c r="Y614" s="5"/>
       <c r="Z614" s="5"/>
       <c r="AA614" s="5"/>
+      <c r="AB614" s="5"/>
     </row>
     <row r="615">
       <c r="A615" s="5"/>
@@ -18585,6 +19352,7 @@
       <c r="Y615" s="5"/>
       <c r="Z615" s="5"/>
       <c r="AA615" s="5"/>
+      <c r="AB615" s="5"/>
     </row>
     <row r="616">
       <c r="A616" s="5"/>
@@ -18614,6 +19382,7 @@
       <c r="Y616" s="5"/>
       <c r="Z616" s="5"/>
       <c r="AA616" s="5"/>
+      <c r="AB616" s="5"/>
     </row>
     <row r="617">
       <c r="A617" s="5"/>
@@ -18643,6 +19412,7 @@
       <c r="Y617" s="5"/>
       <c r="Z617" s="5"/>
       <c r="AA617" s="5"/>
+      <c r="AB617" s="5"/>
     </row>
     <row r="618">
       <c r="A618" s="5"/>
@@ -18672,6 +19442,7 @@
       <c r="Y618" s="5"/>
       <c r="Z618" s="5"/>
       <c r="AA618" s="5"/>
+      <c r="AB618" s="5"/>
     </row>
     <row r="619">
       <c r="A619" s="5"/>
@@ -18701,6 +19472,7 @@
       <c r="Y619" s="5"/>
       <c r="Z619" s="5"/>
       <c r="AA619" s="5"/>
+      <c r="AB619" s="5"/>
     </row>
     <row r="620">
       <c r="A620" s="5"/>
@@ -18730,6 +19502,7 @@
       <c r="Y620" s="5"/>
       <c r="Z620" s="5"/>
       <c r="AA620" s="5"/>
+      <c r="AB620" s="5"/>
     </row>
     <row r="621">
       <c r="A621" s="5"/>
@@ -18759,6 +19532,7 @@
       <c r="Y621" s="5"/>
       <c r="Z621" s="5"/>
       <c r="AA621" s="5"/>
+      <c r="AB621" s="5"/>
     </row>
     <row r="622">
       <c r="A622" s="5"/>
@@ -18788,6 +19562,7 @@
       <c r="Y622" s="5"/>
       <c r="Z622" s="5"/>
       <c r="AA622" s="5"/>
+      <c r="AB622" s="5"/>
     </row>
     <row r="623">
       <c r="A623" s="5"/>
@@ -18817,6 +19592,7 @@
       <c r="Y623" s="5"/>
       <c r="Z623" s="5"/>
       <c r="AA623" s="5"/>
+      <c r="AB623" s="5"/>
     </row>
     <row r="624">
       <c r="A624" s="5"/>
@@ -18846,6 +19622,7 @@
       <c r="Y624" s="5"/>
       <c r="Z624" s="5"/>
       <c r="AA624" s="5"/>
+      <c r="AB624" s="5"/>
     </row>
     <row r="625">
       <c r="A625" s="5"/>
@@ -18875,6 +19652,7 @@
       <c r="Y625" s="5"/>
       <c r="Z625" s="5"/>
       <c r="AA625" s="5"/>
+      <c r="AB625" s="5"/>
     </row>
     <row r="626">
       <c r="A626" s="5"/>
@@ -18904,6 +19682,7 @@
       <c r="Y626" s="5"/>
       <c r="Z626" s="5"/>
       <c r="AA626" s="5"/>
+      <c r="AB626" s="5"/>
     </row>
     <row r="627">
       <c r="A627" s="5"/>
@@ -18933,6 +19712,7 @@
       <c r="Y627" s="5"/>
       <c r="Z627" s="5"/>
       <c r="AA627" s="5"/>
+      <c r="AB627" s="5"/>
     </row>
     <row r="628">
       <c r="A628" s="5"/>
@@ -18962,6 +19742,7 @@
       <c r="Y628" s="5"/>
       <c r="Z628" s="5"/>
       <c r="AA628" s="5"/>
+      <c r="AB628" s="5"/>
     </row>
     <row r="629">
       <c r="A629" s="5"/>
@@ -18991,6 +19772,7 @@
       <c r="Y629" s="5"/>
       <c r="Z629" s="5"/>
       <c r="AA629" s="5"/>
+      <c r="AB629" s="5"/>
     </row>
     <row r="630">
       <c r="A630" s="5"/>
@@ -19020,6 +19802,7 @@
       <c r="Y630" s="5"/>
       <c r="Z630" s="5"/>
       <c r="AA630" s="5"/>
+      <c r="AB630" s="5"/>
     </row>
     <row r="631">
       <c r="A631" s="5"/>
@@ -19049,6 +19832,7 @@
       <c r="Y631" s="5"/>
       <c r="Z631" s="5"/>
       <c r="AA631" s="5"/>
+      <c r="AB631" s="5"/>
     </row>
     <row r="632">
       <c r="A632" s="5"/>
@@ -19078,6 +19862,7 @@
       <c r="Y632" s="5"/>
       <c r="Z632" s="5"/>
       <c r="AA632" s="5"/>
+      <c r="AB632" s="5"/>
     </row>
     <row r="633">
       <c r="A633" s="5"/>
@@ -19107,6 +19892,7 @@
       <c r="Y633" s="5"/>
       <c r="Z633" s="5"/>
       <c r="AA633" s="5"/>
+      <c r="AB633" s="5"/>
     </row>
     <row r="634">
       <c r="A634" s="5"/>
@@ -19136,6 +19922,7 @@
       <c r="Y634" s="5"/>
       <c r="Z634" s="5"/>
       <c r="AA634" s="5"/>
+      <c r="AB634" s="5"/>
     </row>
     <row r="635">
       <c r="A635" s="5"/>
@@ -19165,6 +19952,7 @@
       <c r="Y635" s="5"/>
       <c r="Z635" s="5"/>
       <c r="AA635" s="5"/>
+      <c r="AB635" s="5"/>
     </row>
     <row r="636">
       <c r="A636" s="5"/>
@@ -19194,6 +19982,7 @@
       <c r="Y636" s="5"/>
       <c r="Z636" s="5"/>
       <c r="AA636" s="5"/>
+      <c r="AB636" s="5"/>
     </row>
     <row r="637">
       <c r="A637" s="5"/>
@@ -19223,6 +20012,7 @@
       <c r="Y637" s="5"/>
       <c r="Z637" s="5"/>
       <c r="AA637" s="5"/>
+      <c r="AB637" s="5"/>
     </row>
     <row r="638">
       <c r="A638" s="5"/>
@@ -19252,6 +20042,7 @@
       <c r="Y638" s="5"/>
       <c r="Z638" s="5"/>
       <c r="AA638" s="5"/>
+      <c r="AB638" s="5"/>
     </row>
     <row r="639">
       <c r="A639" s="5"/>
@@ -19281,6 +20072,7 @@
       <c r="Y639" s="5"/>
       <c r="Z639" s="5"/>
       <c r="AA639" s="5"/>
+      <c r="AB639" s="5"/>
     </row>
     <row r="640">
       <c r="A640" s="5"/>
@@ -19310,6 +20102,7 @@
       <c r="Y640" s="5"/>
       <c r="Z640" s="5"/>
       <c r="AA640" s="5"/>
+      <c r="AB640" s="5"/>
     </row>
     <row r="641">
       <c r="A641" s="5"/>
@@ -19339,6 +20132,7 @@
       <c r="Y641" s="5"/>
       <c r="Z641" s="5"/>
       <c r="AA641" s="5"/>
+      <c r="AB641" s="5"/>
     </row>
     <row r="642">
       <c r="A642" s="5"/>
@@ -19368,6 +20162,7 @@
       <c r="Y642" s="5"/>
       <c r="Z642" s="5"/>
       <c r="AA642" s="5"/>
+      <c r="AB642" s="5"/>
     </row>
     <row r="643">
       <c r="A643" s="5"/>
@@ -19397,6 +20192,7 @@
       <c r="Y643" s="5"/>
       <c r="Z643" s="5"/>
       <c r="AA643" s="5"/>
+      <c r="AB643" s="5"/>
     </row>
     <row r="644">
       <c r="A644" s="5"/>
@@ -19426,6 +20222,7 @@
       <c r="Y644" s="5"/>
       <c r="Z644" s="5"/>
       <c r="AA644" s="5"/>
+      <c r="AB644" s="5"/>
     </row>
     <row r="645">
       <c r="A645" s="5"/>
@@ -19455,6 +20252,7 @@
       <c r="Y645" s="5"/>
       <c r="Z645" s="5"/>
       <c r="AA645" s="5"/>
+      <c r="AB645" s="5"/>
     </row>
     <row r="646">
       <c r="A646" s="5"/>
@@ -19484,6 +20282,7 @@
       <c r="Y646" s="5"/>
       <c r="Z646" s="5"/>
       <c r="AA646" s="5"/>
+      <c r="AB646" s="5"/>
     </row>
     <row r="647">
       <c r="A647" s="5"/>
@@ -19513,6 +20312,7 @@
       <c r="Y647" s="5"/>
       <c r="Z647" s="5"/>
       <c r="AA647" s="5"/>
+      <c r="AB647" s="5"/>
     </row>
     <row r="648">
       <c r="A648" s="5"/>
@@ -19542,6 +20342,7 @@
       <c r="Y648" s="5"/>
       <c r="Z648" s="5"/>
       <c r="AA648" s="5"/>
+      <c r="AB648" s="5"/>
     </row>
     <row r="649">
       <c r="A649" s="5"/>
@@ -19571,6 +20372,7 @@
       <c r="Y649" s="5"/>
       <c r="Z649" s="5"/>
       <c r="AA649" s="5"/>
+      <c r="AB649" s="5"/>
     </row>
     <row r="650">
       <c r="A650" s="5"/>
@@ -19600,6 +20402,7 @@
       <c r="Y650" s="5"/>
       <c r="Z650" s="5"/>
       <c r="AA650" s="5"/>
+      <c r="AB650" s="5"/>
     </row>
     <row r="651">
       <c r="A651" s="5"/>
@@ -19629,6 +20432,7 @@
       <c r="Y651" s="5"/>
       <c r="Z651" s="5"/>
       <c r="AA651" s="5"/>
+      <c r="AB651" s="5"/>
     </row>
     <row r="652">
       <c r="A652" s="5"/>
@@ -19658,6 +20462,7 @@
       <c r="Y652" s="5"/>
       <c r="Z652" s="5"/>
       <c r="AA652" s="5"/>
+      <c r="AB652" s="5"/>
     </row>
     <row r="653">
       <c r="A653" s="5"/>
@@ -19687,6 +20492,7 @@
       <c r="Y653" s="5"/>
       <c r="Z653" s="5"/>
       <c r="AA653" s="5"/>
+      <c r="AB653" s="5"/>
     </row>
     <row r="654">
       <c r="A654" s="5"/>
@@ -19716,6 +20522,7 @@
       <c r="Y654" s="5"/>
       <c r="Z654" s="5"/>
       <c r="AA654" s="5"/>
+      <c r="AB654" s="5"/>
     </row>
     <row r="655">
       <c r="A655" s="5"/>
@@ -19745,6 +20552,7 @@
       <c r="Y655" s="5"/>
       <c r="Z655" s="5"/>
       <c r="AA655" s="5"/>
+      <c r="AB655" s="5"/>
     </row>
     <row r="656">
       <c r="A656" s="5"/>
@@ -19774,6 +20582,7 @@
       <c r="Y656" s="5"/>
       <c r="Z656" s="5"/>
       <c r="AA656" s="5"/>
+      <c r="AB656" s="5"/>
     </row>
     <row r="657">
       <c r="A657" s="5"/>
@@ -19803,6 +20612,7 @@
       <c r="Y657" s="5"/>
       <c r="Z657" s="5"/>
       <c r="AA657" s="5"/>
+      <c r="AB657" s="5"/>
     </row>
     <row r="658">
       <c r="A658" s="5"/>
@@ -19832,6 +20642,7 @@
       <c r="Y658" s="5"/>
       <c r="Z658" s="5"/>
       <c r="AA658" s="5"/>
+      <c r="AB658" s="5"/>
     </row>
     <row r="659">
       <c r="A659" s="5"/>
@@ -19861,6 +20672,7 @@
       <c r="Y659" s="5"/>
       <c r="Z659" s="5"/>
       <c r="AA659" s="5"/>
+      <c r="AB659" s="5"/>
     </row>
     <row r="660">
       <c r="A660" s="5"/>
@@ -19890,6 +20702,7 @@
       <c r="Y660" s="5"/>
       <c r="Z660" s="5"/>
       <c r="AA660" s="5"/>
+      <c r="AB660" s="5"/>
     </row>
     <row r="661">
       <c r="A661" s="5"/>
@@ -19919,6 +20732,7 @@
       <c r="Y661" s="5"/>
       <c r="Z661" s="5"/>
       <c r="AA661" s="5"/>
+      <c r="AB661" s="5"/>
     </row>
     <row r="662">
       <c r="A662" s="5"/>
@@ -19948,6 +20762,7 @@
       <c r="Y662" s="5"/>
       <c r="Z662" s="5"/>
       <c r="AA662" s="5"/>
+      <c r="AB662" s="5"/>
     </row>
     <row r="663">
       <c r="A663" s="5"/>
@@ -19977,6 +20792,7 @@
       <c r="Y663" s="5"/>
       <c r="Z663" s="5"/>
       <c r="AA663" s="5"/>
+      <c r="AB663" s="5"/>
     </row>
     <row r="664">
       <c r="A664" s="5"/>
@@ -20006,6 +20822,7 @@
       <c r="Y664" s="5"/>
       <c r="Z664" s="5"/>
       <c r="AA664" s="5"/>
+      <c r="AB664" s="5"/>
     </row>
     <row r="665">
       <c r="A665" s="5"/>
@@ -20035,6 +20852,7 @@
       <c r="Y665" s="5"/>
       <c r="Z665" s="5"/>
       <c r="AA665" s="5"/>
+      <c r="AB665" s="5"/>
     </row>
     <row r="666">
       <c r="A666" s="5"/>
@@ -20064,6 +20882,7 @@
       <c r="Y666" s="5"/>
       <c r="Z666" s="5"/>
       <c r="AA666" s="5"/>
+      <c r="AB666" s="5"/>
     </row>
     <row r="667">
       <c r="A667" s="5"/>
@@ -20093,6 +20912,7 @@
       <c r="Y667" s="5"/>
       <c r="Z667" s="5"/>
       <c r="AA667" s="5"/>
+      <c r="AB667" s="5"/>
     </row>
     <row r="668">
       <c r="A668" s="5"/>
@@ -20122,6 +20942,7 @@
       <c r="Y668" s="5"/>
       <c r="Z668" s="5"/>
       <c r="AA668" s="5"/>
+      <c r="AB668" s="5"/>
     </row>
     <row r="669">
       <c r="A669" s="5"/>
@@ -20151,6 +20972,7 @@
       <c r="Y669" s="5"/>
       <c r="Z669" s="5"/>
       <c r="AA669" s="5"/>
+      <c r="AB669" s="5"/>
     </row>
     <row r="670">
       <c r="A670" s="5"/>
@@ -20180,6 +21002,7 @@
       <c r="Y670" s="5"/>
       <c r="Z670" s="5"/>
       <c r="AA670" s="5"/>
+      <c r="AB670" s="5"/>
     </row>
     <row r="671">
       <c r="A671" s="5"/>
@@ -20209,6 +21032,7 @@
       <c r="Y671" s="5"/>
       <c r="Z671" s="5"/>
       <c r="AA671" s="5"/>
+      <c r="AB671" s="5"/>
     </row>
     <row r="672">
       <c r="A672" s="5"/>
@@ -20238,6 +21062,7 @@
       <c r="Y672" s="5"/>
       <c r="Z672" s="5"/>
       <c r="AA672" s="5"/>
+      <c r="AB672" s="5"/>
     </row>
     <row r="673">
       <c r="A673" s="5"/>
@@ -20267,6 +21092,7 @@
       <c r="Y673" s="5"/>
       <c r="Z673" s="5"/>
       <c r="AA673" s="5"/>
+      <c r="AB673" s="5"/>
     </row>
     <row r="674">
       <c r="A674" s="5"/>
@@ -20296,6 +21122,7 @@
       <c r="Y674" s="5"/>
       <c r="Z674" s="5"/>
       <c r="AA674" s="5"/>
+      <c r="AB674" s="5"/>
     </row>
     <row r="675">
       <c r="A675" s="5"/>
@@ -20325,6 +21152,7 @@
       <c r="Y675" s="5"/>
       <c r="Z675" s="5"/>
       <c r="AA675" s="5"/>
+      <c r="AB675" s="5"/>
     </row>
     <row r="676">
       <c r="A676" s="5"/>
@@ -20354,6 +21182,7 @@
       <c r="Y676" s="5"/>
       <c r="Z676" s="5"/>
       <c r="AA676" s="5"/>
+      <c r="AB676" s="5"/>
     </row>
     <row r="677">
       <c r="A677" s="5"/>
@@ -20383,6 +21212,7 @@
       <c r="Y677" s="5"/>
       <c r="Z677" s="5"/>
       <c r="AA677" s="5"/>
+      <c r="AB677" s="5"/>
     </row>
     <row r="678">
       <c r="A678" s="5"/>
@@ -20412,6 +21242,7 @@
       <c r="Y678" s="5"/>
       <c r="Z678" s="5"/>
       <c r="AA678" s="5"/>
+      <c r="AB678" s="5"/>
     </row>
     <row r="679">
       <c r="A679" s="5"/>
@@ -20441,6 +21272,7 @@
       <c r="Y679" s="5"/>
       <c r="Z679" s="5"/>
       <c r="AA679" s="5"/>
+      <c r="AB679" s="5"/>
     </row>
     <row r="680">
       <c r="A680" s="5"/>
@@ -20470,6 +21302,7 @@
       <c r="Y680" s="5"/>
       <c r="Z680" s="5"/>
       <c r="AA680" s="5"/>
+      <c r="AB680" s="5"/>
     </row>
     <row r="681">
       <c r="A681" s="5"/>
@@ -20499,6 +21332,7 @@
       <c r="Y681" s="5"/>
       <c r="Z681" s="5"/>
       <c r="AA681" s="5"/>
+      <c r="AB681" s="5"/>
     </row>
     <row r="682">
       <c r="A682" s="5"/>
@@ -20528,6 +21362,7 @@
       <c r="Y682" s="5"/>
       <c r="Z682" s="5"/>
       <c r="AA682" s="5"/>
+      <c r="AB682" s="5"/>
     </row>
     <row r="683">
       <c r="A683" s="5"/>
@@ -20557,6 +21392,7 @@
       <c r="Y683" s="5"/>
       <c r="Z683" s="5"/>
       <c r="AA683" s="5"/>
+      <c r="AB683" s="5"/>
     </row>
     <row r="684">
       <c r="A684" s="5"/>
@@ -20586,6 +21422,7 @@
       <c r="Y684" s="5"/>
       <c r="Z684" s="5"/>
       <c r="AA684" s="5"/>
+      <c r="AB684" s="5"/>
     </row>
     <row r="685">
       <c r="A685" s="5"/>
@@ -20615,6 +21452,7 @@
       <c r="Y685" s="5"/>
       <c r="Z685" s="5"/>
       <c r="AA685" s="5"/>
+      <c r="AB685" s="5"/>
     </row>
     <row r="686">
       <c r="A686" s="5"/>
@@ -20644,6 +21482,7 @@
       <c r="Y686" s="5"/>
       <c r="Z686" s="5"/>
       <c r="AA686" s="5"/>
+      <c r="AB686" s="5"/>
     </row>
     <row r="687">
       <c r="A687" s="5"/>
@@ -20673,6 +21512,7 @@
       <c r="Y687" s="5"/>
       <c r="Z687" s="5"/>
       <c r="AA687" s="5"/>
+      <c r="AB687" s="5"/>
     </row>
     <row r="688">
       <c r="A688" s="5"/>
@@ -20702,6 +21542,7 @@
       <c r="Y688" s="5"/>
       <c r="Z688" s="5"/>
       <c r="AA688" s="5"/>
+      <c r="AB688" s="5"/>
     </row>
     <row r="689">
       <c r="A689" s="5"/>
@@ -20731,6 +21572,7 @@
       <c r="Y689" s="5"/>
       <c r="Z689" s="5"/>
       <c r="AA689" s="5"/>
+      <c r="AB689" s="5"/>
     </row>
     <row r="690">
       <c r="A690" s="5"/>
@@ -20760,6 +21602,7 @@
       <c r="Y690" s="5"/>
       <c r="Z690" s="5"/>
       <c r="AA690" s="5"/>
+      <c r="AB690" s="5"/>
     </row>
     <row r="691">
       <c r="A691" s="5"/>
@@ -20789,6 +21632,7 @@
       <c r="Y691" s="5"/>
       <c r="Z691" s="5"/>
       <c r="AA691" s="5"/>
+      <c r="AB691" s="5"/>
     </row>
     <row r="692">
       <c r="A692" s="5"/>
@@ -20818,6 +21662,7 @@
       <c r="Y692" s="5"/>
       <c r="Z692" s="5"/>
       <c r="AA692" s="5"/>
+      <c r="AB692" s="5"/>
     </row>
     <row r="693">
       <c r="A693" s="5"/>
@@ -20847,6 +21692,7 @@
       <c r="Y693" s="5"/>
       <c r="Z693" s="5"/>
       <c r="AA693" s="5"/>
+      <c r="AB693" s="5"/>
     </row>
     <row r="694">
       <c r="A694" s="5"/>
@@ -20876,6 +21722,7 @@
       <c r="Y694" s="5"/>
       <c r="Z694" s="5"/>
       <c r="AA694" s="5"/>
+      <c r="AB694" s="5"/>
     </row>
     <row r="695">
       <c r="A695" s="5"/>
@@ -20905,6 +21752,7 @@
       <c r="Y695" s="5"/>
       <c r="Z695" s="5"/>
       <c r="AA695" s="5"/>
+      <c r="AB695" s="5"/>
     </row>
     <row r="696">
       <c r="A696" s="5"/>
@@ -20934,6 +21782,7 @@
       <c r="Y696" s="5"/>
       <c r="Z696" s="5"/>
       <c r="AA696" s="5"/>
+      <c r="AB696" s="5"/>
     </row>
     <row r="697">
       <c r="A697" s="5"/>
@@ -20963,6 +21812,7 @@
       <c r="Y697" s="5"/>
       <c r="Z697" s="5"/>
       <c r="AA697" s="5"/>
+      <c r="AB697" s="5"/>
     </row>
     <row r="698">
       <c r="A698" s="5"/>
@@ -20992,6 +21842,7 @@
       <c r="Y698" s="5"/>
       <c r="Z698" s="5"/>
       <c r="AA698" s="5"/>
+      <c r="AB698" s="5"/>
     </row>
     <row r="699">
       <c r="A699" s="5"/>
@@ -21021,6 +21872,7 @@
       <c r="Y699" s="5"/>
       <c r="Z699" s="5"/>
       <c r="AA699" s="5"/>
+      <c r="AB699" s="5"/>
     </row>
     <row r="700">
       <c r="A700" s="5"/>
@@ -21050,6 +21902,7 @@
       <c r="Y700" s="5"/>
       <c r="Z700" s="5"/>
       <c r="AA700" s="5"/>
+      <c r="AB700" s="5"/>
     </row>
     <row r="701">
       <c r="A701" s="5"/>
@@ -21079,6 +21932,7 @@
       <c r="Y701" s="5"/>
       <c r="Z701" s="5"/>
       <c r="AA701" s="5"/>
+      <c r="AB701" s="5"/>
     </row>
     <row r="702">
       <c r="A702" s="5"/>
@@ -21108,6 +21962,7 @@
       <c r="Y702" s="5"/>
       <c r="Z702" s="5"/>
       <c r="AA702" s="5"/>
+      <c r="AB702" s="5"/>
     </row>
     <row r="703">
       <c r="A703" s="5"/>
@@ -21137,6 +21992,7 @@
       <c r="Y703" s="5"/>
       <c r="Z703" s="5"/>
       <c r="AA703" s="5"/>
+      <c r="AB703" s="5"/>
     </row>
     <row r="704">
       <c r="A704" s="5"/>
@@ -21166,6 +22022,7 @@
       <c r="Y704" s="5"/>
       <c r="Z704" s="5"/>
       <c r="AA704" s="5"/>
+      <c r="AB704" s="5"/>
     </row>
     <row r="705">
       <c r="A705" s="5"/>
@@ -21195,6 +22052,7 @@
       <c r="Y705" s="5"/>
       <c r="Z705" s="5"/>
       <c r="AA705" s="5"/>
+      <c r="AB705" s="5"/>
     </row>
     <row r="706">
       <c r="A706" s="5"/>
@@ -21224,6 +22082,7 @@
       <c r="Y706" s="5"/>
       <c r="Z706" s="5"/>
       <c r="AA706" s="5"/>
+      <c r="AB706" s="5"/>
     </row>
     <row r="707">
       <c r="A707" s="5"/>
@@ -21253,6 +22112,7 @@
       <c r="Y707" s="5"/>
       <c r="Z707" s="5"/>
       <c r="AA707" s="5"/>
+      <c r="AB707" s="5"/>
     </row>
     <row r="708">
       <c r="A708" s="5"/>
@@ -21282,6 +22142,7 @@
       <c r="Y708" s="5"/>
       <c r="Z708" s="5"/>
       <c r="AA708" s="5"/>
+      <c r="AB708" s="5"/>
     </row>
     <row r="709">
       <c r="A709" s="5"/>
@@ -21311,6 +22172,7 @@
       <c r="Y709" s="5"/>
       <c r="Z709" s="5"/>
       <c r="AA709" s="5"/>
+      <c r="AB709" s="5"/>
     </row>
     <row r="710">
       <c r="A710" s="5"/>
@@ -21340,6 +22202,7 @@
       <c r="Y710" s="5"/>
       <c r="Z710" s="5"/>
       <c r="AA710" s="5"/>
+      <c r="AB710" s="5"/>
     </row>
     <row r="711">
       <c r="A711" s="5"/>
@@ -21369,6 +22232,7 @@
       <c r="Y711" s="5"/>
       <c r="Z711" s="5"/>
       <c r="AA711" s="5"/>
+      <c r="AB711" s="5"/>
     </row>
     <row r="712">
       <c r="A712" s="5"/>
@@ -21398,6 +22262,7 @@
       <c r="Y712" s="5"/>
       <c r="Z712" s="5"/>
       <c r="AA712" s="5"/>
+      <c r="AB712" s="5"/>
     </row>
     <row r="713">
       <c r="A713" s="5"/>
@@ -21427,6 +22292,7 @@
       <c r="Y713" s="5"/>
       <c r="Z713" s="5"/>
       <c r="AA713" s="5"/>
+      <c r="AB713" s="5"/>
     </row>
     <row r="714">
       <c r="A714" s="5"/>
@@ -21456,6 +22322,7 @@
       <c r="Y714" s="5"/>
       <c r="Z714" s="5"/>
       <c r="AA714" s="5"/>
+      <c r="AB714" s="5"/>
     </row>
     <row r="715">
       <c r="A715" s="5"/>
@@ -21485,6 +22352,7 @@
       <c r="Y715" s="5"/>
       <c r="Z715" s="5"/>
       <c r="AA715" s="5"/>
+      <c r="AB715" s="5"/>
     </row>
     <row r="716">
       <c r="A716" s="5"/>
@@ -21514,6 +22382,7 @@
       <c r="Y716" s="5"/>
       <c r="Z716" s="5"/>
       <c r="AA716" s="5"/>
+      <c r="AB716" s="5"/>
     </row>
     <row r="717">
       <c r="A717" s="5"/>
@@ -21543,6 +22412,7 @@
       <c r="Y717" s="5"/>
       <c r="Z717" s="5"/>
       <c r="AA717" s="5"/>
+      <c r="AB717" s="5"/>
     </row>
     <row r="718">
       <c r="A718" s="5"/>
@@ -21572,6 +22442,7 @@
       <c r="Y718" s="5"/>
       <c r="Z718" s="5"/>
       <c r="AA718" s="5"/>
+      <c r="AB718" s="5"/>
     </row>
     <row r="719">
       <c r="A719" s="5"/>
@@ -21601,6 +22472,7 @@
       <c r="Y719" s="5"/>
       <c r="Z719" s="5"/>
       <c r="AA719" s="5"/>
+      <c r="AB719" s="5"/>
     </row>
     <row r="720">
       <c r="A720" s="5"/>
@@ -21630,6 +22502,7 @@
       <c r="Y720" s="5"/>
       <c r="Z720" s="5"/>
       <c r="AA720" s="5"/>
+      <c r="AB720" s="5"/>
     </row>
     <row r="721">
       <c r="A721" s="5"/>
@@ -21659,6 +22532,7 @@
       <c r="Y721" s="5"/>
       <c r="Z721" s="5"/>
       <c r="AA721" s="5"/>
+      <c r="AB721" s="5"/>
     </row>
     <row r="722">
       <c r="A722" s="5"/>
@@ -21688,6 +22562,7 @@
       <c r="Y722" s="5"/>
       <c r="Z722" s="5"/>
       <c r="AA722" s="5"/>
+      <c r="AB722" s="5"/>
     </row>
     <row r="723">
       <c r="A723" s="5"/>
@@ -21717,6 +22592,7 @@
       <c r="Y723" s="5"/>
       <c r="Z723" s="5"/>
       <c r="AA723" s="5"/>
+      <c r="AB723" s="5"/>
     </row>
     <row r="724">
       <c r="A724" s="5"/>
@@ -21746,6 +22622,7 @@
       <c r="Y724" s="5"/>
       <c r="Z724" s="5"/>
       <c r="AA724" s="5"/>
+      <c r="AB724" s="5"/>
     </row>
     <row r="725">
       <c r="A725" s="5"/>
@@ -21775,6 +22652,7 @@
       <c r="Y725" s="5"/>
       <c r="Z725" s="5"/>
       <c r="AA725" s="5"/>
+      <c r="AB725" s="5"/>
     </row>
     <row r="726">
       <c r="A726" s="5"/>
@@ -21804,6 +22682,7 @@
       <c r="Y726" s="5"/>
       <c r="Z726" s="5"/>
       <c r="AA726" s="5"/>
+      <c r="AB726" s="5"/>
     </row>
     <row r="727">
       <c r="A727" s="5"/>
@@ -21833,6 +22712,7 @@
       <c r="Y727" s="5"/>
       <c r="Z727" s="5"/>
       <c r="AA727" s="5"/>
+      <c r="AB727" s="5"/>
     </row>
     <row r="728">
       <c r="A728" s="5"/>
@@ -21862,6 +22742,7 @@
       <c r="Y728" s="5"/>
       <c r="Z728" s="5"/>
       <c r="AA728" s="5"/>
+      <c r="AB728" s="5"/>
     </row>
     <row r="729">
       <c r="A729" s="5"/>
@@ -21891,6 +22772,7 @@
       <c r="Y729" s="5"/>
       <c r="Z729" s="5"/>
       <c r="AA729" s="5"/>
+      <c r="AB729" s="5"/>
     </row>
     <row r="730">
       <c r="A730" s="5"/>
@@ -21920,6 +22802,7 @@
       <c r="Y730" s="5"/>
       <c r="Z730" s="5"/>
       <c r="AA730" s="5"/>
+      <c r="AB730" s="5"/>
     </row>
     <row r="731">
       <c r="A731" s="5"/>
@@ -21949,6 +22832,7 @@
       <c r="Y731" s="5"/>
       <c r="Z731" s="5"/>
       <c r="AA731" s="5"/>
+      <c r="AB731" s="5"/>
     </row>
     <row r="732">
       <c r="A732" s="5"/>
@@ -21978,6 +22862,7 @@
       <c r="Y732" s="5"/>
       <c r="Z732" s="5"/>
       <c r="AA732" s="5"/>
+      <c r="AB732" s="5"/>
     </row>
     <row r="733">
       <c r="A733" s="5"/>
@@ -22007,6 +22892,7 @@
       <c r="Y733" s="5"/>
       <c r="Z733" s="5"/>
       <c r="AA733" s="5"/>
+      <c r="AB733" s="5"/>
     </row>
     <row r="734">
       <c r="A734" s="5"/>
@@ -22036,6 +22922,7 @@
       <c r="Y734" s="5"/>
       <c r="Z734" s="5"/>
       <c r="AA734" s="5"/>
+      <c r="AB734" s="5"/>
     </row>
     <row r="735">
       <c r="A735" s="5"/>
@@ -22065,6 +22952,7 @@
       <c r="Y735" s="5"/>
       <c r="Z735" s="5"/>
       <c r="AA735" s="5"/>
+      <c r="AB735" s="5"/>
     </row>
     <row r="736">
       <c r="A736" s="5"/>
@@ -22094,6 +22982,7 @@
       <c r="Y736" s="5"/>
       <c r="Z736" s="5"/>
       <c r="AA736" s="5"/>
+      <c r="AB736" s="5"/>
     </row>
     <row r="737">
       <c r="A737" s="5"/>
@@ -22123,6 +23012,7 @@
       <c r="Y737" s="5"/>
       <c r="Z737" s="5"/>
       <c r="AA737" s="5"/>
+      <c r="AB737" s="5"/>
     </row>
     <row r="738">
       <c r="A738" s="5"/>
@@ -22152,6 +23042,7 @@
       <c r="Y738" s="5"/>
       <c r="Z738" s="5"/>
       <c r="AA738" s="5"/>
+      <c r="AB738" s="5"/>
     </row>
     <row r="739">
       <c r="A739" s="5"/>
@@ -22181,6 +23072,7 @@
       <c r="Y739" s="5"/>
       <c r="Z739" s="5"/>
       <c r="AA739" s="5"/>
+      <c r="AB739" s="5"/>
     </row>
     <row r="740">
       <c r="A740" s="5"/>
@@ -22210,6 +23102,7 @@
       <c r="Y740" s="5"/>
       <c r="Z740" s="5"/>
       <c r="AA740" s="5"/>
+      <c r="AB740" s="5"/>
     </row>
     <row r="741">
       <c r="A741" s="5"/>
@@ -22239,6 +23132,7 @@
       <c r="Y741" s="5"/>
       <c r="Z741" s="5"/>
       <c r="AA741" s="5"/>
+      <c r="AB741" s="5"/>
     </row>
     <row r="742">
       <c r="A742" s="5"/>
@@ -22268,6 +23162,7 @@
       <c r="Y742" s="5"/>
       <c r="Z742" s="5"/>
       <c r="AA742" s="5"/>
+      <c r="AB742" s="5"/>
     </row>
     <row r="743">
       <c r="A743" s="5"/>
@@ -22297,6 +23192,7 @@
       <c r="Y743" s="5"/>
       <c r="Z743" s="5"/>
       <c r="AA743" s="5"/>
+      <c r="AB743" s="5"/>
     </row>
     <row r="744">
       <c r="A744" s="5"/>
@@ -22326,6 +23222,7 @@
       <c r="Y744" s="5"/>
       <c r="Z744" s="5"/>
       <c r="AA744" s="5"/>
+      <c r="AB744" s="5"/>
     </row>
     <row r="745">
       <c r="A745" s="5"/>
@@ -22355,6 +23252,7 @@
       <c r="Y745" s="5"/>
       <c r="Z745" s="5"/>
       <c r="AA745" s="5"/>
+      <c r="AB745" s="5"/>
     </row>
     <row r="746">
       <c r="A746" s="5"/>
@@ -22384,6 +23282,7 @@
       <c r="Y746" s="5"/>
       <c r="Z746" s="5"/>
       <c r="AA746" s="5"/>
+      <c r="AB746" s="5"/>
     </row>
     <row r="747">
       <c r="A747" s="5"/>
@@ -22413,6 +23312,7 @@
       <c r="Y747" s="5"/>
       <c r="Z747" s="5"/>
       <c r="AA747" s="5"/>
+      <c r="AB747" s="5"/>
     </row>
     <row r="748">
       <c r="A748" s="5"/>
@@ -22442,6 +23342,7 @@
       <c r="Y748" s="5"/>
       <c r="Z748" s="5"/>
       <c r="AA748" s="5"/>
+      <c r="AB748" s="5"/>
     </row>
     <row r="749">
       <c r="A749" s="5"/>
@@ -22471,6 +23372,7 @@
       <c r="Y749" s="5"/>
       <c r="Z749" s="5"/>
       <c r="AA749" s="5"/>
+      <c r="AB749" s="5"/>
     </row>
     <row r="750">
       <c r="A750" s="5"/>
@@ -22500,6 +23402,7 @@
       <c r="Y750" s="5"/>
       <c r="Z750" s="5"/>
       <c r="AA750" s="5"/>
+      <c r="AB750" s="5"/>
     </row>
     <row r="751">
       <c r="A751" s="5"/>
@@ -22529,6 +23432,7 @@
       <c r="Y751" s="5"/>
       <c r="Z751" s="5"/>
       <c r="AA751" s="5"/>
+      <c r="AB751" s="5"/>
     </row>
     <row r="752">
       <c r="A752" s="5"/>
@@ -22558,6 +23462,7 @@
       <c r="Y752" s="5"/>
       <c r="Z752" s="5"/>
       <c r="AA752" s="5"/>
+      <c r="AB752" s="5"/>
     </row>
     <row r="753">
       <c r="A753" s="5"/>
@@ -22587,6 +23492,7 @@
       <c r="Y753" s="5"/>
       <c r="Z753" s="5"/>
       <c r="AA753" s="5"/>
+      <c r="AB753" s="5"/>
     </row>
     <row r="754">
       <c r="A754" s="5"/>
@@ -22616,6 +23522,7 @@
       <c r="Y754" s="5"/>
       <c r="Z754" s="5"/>
       <c r="AA754" s="5"/>
+      <c r="AB754" s="5"/>
     </row>
     <row r="755">
       <c r="A755" s="5"/>
@@ -22645,6 +23552,7 @@
       <c r="Y755" s="5"/>
       <c r="Z755" s="5"/>
       <c r="AA755" s="5"/>
+      <c r="AB755" s="5"/>
     </row>
     <row r="756">
       <c r="A756" s="5"/>
@@ -22674,6 +23582,7 @@
       <c r="Y756" s="5"/>
       <c r="Z756" s="5"/>
       <c r="AA756" s="5"/>
+      <c r="AB756" s="5"/>
     </row>
     <row r="757">
       <c r="A757" s="5"/>
@@ -22703,6 +23612,7 @@
       <c r="Y757" s="5"/>
       <c r="Z757" s="5"/>
       <c r="AA757" s="5"/>
+      <c r="AB757" s="5"/>
     </row>
     <row r="758">
       <c r="A758" s="5"/>
@@ -22732,6 +23642,7 @@
       <c r="Y758" s="5"/>
       <c r="Z758" s="5"/>
       <c r="AA758" s="5"/>
+      <c r="AB758" s="5"/>
     </row>
     <row r="759">
       <c r="A759" s="5"/>
@@ -22761,6 +23672,7 @@
       <c r="Y759" s="5"/>
       <c r="Z759" s="5"/>
       <c r="AA759" s="5"/>
+      <c r="AB759" s="5"/>
     </row>
     <row r="760">
       <c r="A760" s="5"/>
@@ -22790,6 +23702,7 @@
       <c r="Y760" s="5"/>
       <c r="Z760" s="5"/>
       <c r="AA760" s="5"/>
+      <c r="AB760" s="5"/>
     </row>
     <row r="761">
       <c r="A761" s="5"/>
@@ -22819,6 +23732,7 @@
       <c r="Y761" s="5"/>
       <c r="Z761" s="5"/>
       <c r="AA761" s="5"/>
+      <c r="AB761" s="5"/>
     </row>
     <row r="762">
       <c r="A762" s="5"/>
@@ -22848,6 +23762,7 @@
       <c r="Y762" s="5"/>
       <c r="Z762" s="5"/>
       <c r="AA762" s="5"/>
+      <c r="AB762" s="5"/>
     </row>
     <row r="763">
       <c r="A763" s="5"/>
@@ -22877,6 +23792,7 @@
       <c r="Y763" s="5"/>
       <c r="Z763" s="5"/>
       <c r="AA763" s="5"/>
+      <c r="AB763" s="5"/>
     </row>
     <row r="764">
       <c r="A764" s="5"/>
@@ -22906,6 +23822,7 @@
       <c r="Y764" s="5"/>
       <c r="Z764" s="5"/>
       <c r="AA764" s="5"/>
+      <c r="AB764" s="5"/>
     </row>
     <row r="765">
       <c r="A765" s="5"/>
@@ -22935,6 +23852,7 @@
       <c r="Y765" s="5"/>
       <c r="Z765" s="5"/>
       <c r="AA765" s="5"/>
+      <c r="AB765" s="5"/>
     </row>
     <row r="766">
       <c r="A766" s="5"/>
@@ -22964,6 +23882,7 @@
       <c r="Y766" s="5"/>
       <c r="Z766" s="5"/>
       <c r="AA766" s="5"/>
+      <c r="AB766" s="5"/>
     </row>
     <row r="767">
       <c r="A767" s="5"/>
@@ -22993,6 +23912,7 @@
       <c r="Y767" s="5"/>
       <c r="Z767" s="5"/>
       <c r="AA767" s="5"/>
+      <c r="AB767" s="5"/>
     </row>
     <row r="768">
       <c r="A768" s="5"/>
@@ -23022,6 +23942,7 @@
       <c r="Y768" s="5"/>
       <c r="Z768" s="5"/>
       <c r="AA768" s="5"/>
+      <c r="AB768" s="5"/>
     </row>
     <row r="769">
       <c r="A769" s="5"/>
@@ -23051,6 +23972,7 @@
       <c r="Y769" s="5"/>
       <c r="Z769" s="5"/>
       <c r="AA769" s="5"/>
+      <c r="AB769" s="5"/>
     </row>
     <row r="770">
       <c r="A770" s="5"/>
@@ -23080,6 +24002,7 @@
       <c r="Y770" s="5"/>
       <c r="Z770" s="5"/>
       <c r="AA770" s="5"/>
+      <c r="AB770" s="5"/>
     </row>
     <row r="771">
       <c r="A771" s="5"/>
@@ -23109,6 +24032,7 @@
       <c r="Y771" s="5"/>
       <c r="Z771" s="5"/>
       <c r="AA771" s="5"/>
+      <c r="AB771" s="5"/>
     </row>
     <row r="772">
       <c r="A772" s="5"/>
@@ -23138,6 +24062,7 @@
       <c r="Y772" s="5"/>
       <c r="Z772" s="5"/>
       <c r="AA772" s="5"/>
+      <c r="AB772" s="5"/>
     </row>
     <row r="773">
       <c r="A773" s="5"/>
@@ -23167,6 +24092,7 @@
       <c r="Y773" s="5"/>
       <c r="Z773" s="5"/>
       <c r="AA773" s="5"/>
+      <c r="AB773" s="5"/>
     </row>
     <row r="774">
       <c r="A774" s="5"/>
@@ -23196,6 +24122,7 @@
       <c r="Y774" s="5"/>
       <c r="Z774" s="5"/>
       <c r="AA774" s="5"/>
+      <c r="AB774" s="5"/>
     </row>
     <row r="775">
       <c r="A775" s="5"/>
@@ -23225,6 +24152,7 @@
       <c r="Y775" s="5"/>
       <c r="Z775" s="5"/>
       <c r="AA775" s="5"/>
+      <c r="AB775" s="5"/>
     </row>
     <row r="776">
       <c r="A776" s="5"/>
@@ -23254,6 +24182,7 @@
       <c r="Y776" s="5"/>
       <c r="Z776" s="5"/>
       <c r="AA776" s="5"/>
+      <c r="AB776" s="5"/>
     </row>
     <row r="777">
       <c r="A777" s="5"/>
@@ -23283,6 +24212,7 @@
       <c r="Y777" s="5"/>
       <c r="Z777" s="5"/>
       <c r="AA777" s="5"/>
+      <c r="AB777" s="5"/>
     </row>
     <row r="778">
       <c r="A778" s="5"/>
@@ -23312,6 +24242,7 @@
       <c r="Y778" s="5"/>
       <c r="Z778" s="5"/>
       <c r="AA778" s="5"/>
+      <c r="AB778" s="5"/>
     </row>
     <row r="779">
       <c r="A779" s="5"/>
@@ -23341,6 +24272,7 @@
       <c r="Y779" s="5"/>
       <c r="Z779" s="5"/>
       <c r="AA779" s="5"/>
+      <c r="AB779" s="5"/>
     </row>
     <row r="780">
       <c r="A780" s="5"/>
@@ -23370,6 +24302,7 @@
       <c r="Y780" s="5"/>
       <c r="Z780" s="5"/>
       <c r="AA780" s="5"/>
+      <c r="AB780" s="5"/>
     </row>
     <row r="781">
       <c r="A781" s="5"/>
@@ -23399,6 +24332,7 @@
       <c r="Y781" s="5"/>
       <c r="Z781" s="5"/>
       <c r="AA781" s="5"/>
+      <c r="AB781" s="5"/>
     </row>
     <row r="782">
       <c r="A782" s="5"/>
@@ -23428,6 +24362,7 @@
       <c r="Y782" s="5"/>
       <c r="Z782" s="5"/>
       <c r="AA782" s="5"/>
+      <c r="AB782" s="5"/>
     </row>
     <row r="783">
       <c r="A783" s="5"/>
@@ -23457,6 +24392,7 @@
       <c r="Y783" s="5"/>
       <c r="Z783" s="5"/>
       <c r="AA783" s="5"/>
+      <c r="AB783" s="5"/>
     </row>
     <row r="784">
       <c r="A784" s="5"/>
@@ -23486,6 +24422,7 @@
       <c r="Y784" s="5"/>
       <c r="Z784" s="5"/>
       <c r="AA784" s="5"/>
+      <c r="AB784" s="5"/>
     </row>
     <row r="785">
       <c r="A785" s="5"/>
@@ -23515,6 +24452,7 @@
       <c r="Y785" s="5"/>
       <c r="Z785" s="5"/>
       <c r="AA785" s="5"/>
+      <c r="AB785" s="5"/>
     </row>
     <row r="786">
       <c r="A786" s="5"/>
@@ -23544,6 +24482,7 @@
       <c r="Y786" s="5"/>
       <c r="Z786" s="5"/>
       <c r="AA786" s="5"/>
+      <c r="AB786" s="5"/>
     </row>
     <row r="787">
       <c r="A787" s="5"/>
@@ -23573,6 +24512,7 @@
       <c r="Y787" s="5"/>
       <c r="Z787" s="5"/>
       <c r="AA787" s="5"/>
+      <c r="AB787" s="5"/>
     </row>
     <row r="788">
       <c r="A788" s="5"/>
@@ -23602,6 +24542,7 @@
       <c r="Y788" s="5"/>
       <c r="Z788" s="5"/>
       <c r="AA788" s="5"/>
+      <c r="AB788" s="5"/>
     </row>
     <row r="789">
       <c r="A789" s="5"/>
@@ -23631,6 +24572,7 @@
       <c r="Y789" s="5"/>
       <c r="Z789" s="5"/>
       <c r="AA789" s="5"/>
+      <c r="AB789" s="5"/>
     </row>
     <row r="790">
       <c r="A790" s="5"/>
@@ -23660,6 +24602,7 @@
       <c r="Y790" s="5"/>
       <c r="Z790" s="5"/>
       <c r="AA790" s="5"/>
+      <c r="AB790" s="5"/>
     </row>
     <row r="791">
       <c r="A791" s="5"/>
@@ -23689,6 +24632,7 @@
       <c r="Y791" s="5"/>
       <c r="Z791" s="5"/>
       <c r="AA791" s="5"/>
+      <c r="AB791" s="5"/>
     </row>
     <row r="792">
       <c r="A792" s="5"/>
@@ -23718,6 +24662,7 @@
       <c r="Y792" s="5"/>
       <c r="Z792" s="5"/>
       <c r="AA792" s="5"/>
+      <c r="AB792" s="5"/>
     </row>
     <row r="793">
       <c r="A793" s="5"/>
@@ -23747,6 +24692,7 @@
       <c r="Y793" s="5"/>
       <c r="Z793" s="5"/>
       <c r="AA793" s="5"/>
+      <c r="AB793" s="5"/>
     </row>
     <row r="794">
       <c r="A794" s="5"/>
@@ -23776,6 +24722,7 @@
       <c r="Y794" s="5"/>
       <c r="Z794" s="5"/>
       <c r="AA794" s="5"/>
+      <c r="AB794" s="5"/>
     </row>
     <row r="795">
       <c r="A795" s="5"/>
@@ -23805,6 +24752,7 @@
       <c r="Y795" s="5"/>
       <c r="Z795" s="5"/>
       <c r="AA795" s="5"/>
+      <c r="AB795" s="5"/>
     </row>
     <row r="796">
       <c r="A796" s="5"/>
@@ -23834,6 +24782,7 @@
       <c r="Y796" s="5"/>
       <c r="Z796" s="5"/>
       <c r="AA796" s="5"/>
+      <c r="AB796" s="5"/>
     </row>
     <row r="797">
       <c r="A797" s="5"/>
@@ -23863,6 +24812,7 @@
       <c r="Y797" s="5"/>
       <c r="Z797" s="5"/>
       <c r="AA797" s="5"/>
+      <c r="AB797" s="5"/>
     </row>
     <row r="798">
       <c r="A798" s="5"/>
@@ -23892,6 +24842,7 @@
       <c r="Y798" s="5"/>
       <c r="Z798" s="5"/>
       <c r="AA798" s="5"/>
+      <c r="AB798" s="5"/>
     </row>
     <row r="799">
       <c r="A799" s="5"/>
@@ -23921,6 +24872,7 @@
       <c r="Y799" s="5"/>
       <c r="Z799" s="5"/>
       <c r="AA799" s="5"/>
+      <c r="AB799" s="5"/>
     </row>
     <row r="800">
       <c r="A800" s="5"/>
@@ -23950,6 +24902,7 @@
       <c r="Y800" s="5"/>
       <c r="Z800" s="5"/>
       <c r="AA800" s="5"/>
+      <c r="AB800" s="5"/>
     </row>
     <row r="801">
       <c r="A801" s="5"/>
@@ -23979,6 +24932,7 @@
       <c r="Y801" s="5"/>
       <c r="Z801" s="5"/>
       <c r="AA801" s="5"/>
+      <c r="AB801" s="5"/>
     </row>
     <row r="802">
       <c r="A802" s="5"/>
@@ -24008,6 +24962,7 @@
       <c r="Y802" s="5"/>
       <c r="Z802" s="5"/>
       <c r="AA802" s="5"/>
+      <c r="AB802" s="5"/>
     </row>
     <row r="803">
       <c r="A803" s="5"/>
@@ -24037,6 +24992,7 @@
       <c r="Y803" s="5"/>
       <c r="Z803" s="5"/>
       <c r="AA803" s="5"/>
+      <c r="AB803" s="5"/>
     </row>
     <row r="804">
       <c r="A804" s="5"/>
@@ -24066,6 +25022,7 @@
       <c r="Y804" s="5"/>
       <c r="Z804" s="5"/>
       <c r="AA804" s="5"/>
+      <c r="AB804" s="5"/>
     </row>
     <row r="805">
       <c r="A805" s="5"/>
@@ -24095,6 +25052,7 @@
       <c r="Y805" s="5"/>
       <c r="Z805" s="5"/>
       <c r="AA805" s="5"/>
+      <c r="AB805" s="5"/>
     </row>
     <row r="806">
       <c r="A806" s="5"/>
@@ -24124,6 +25082,7 @@
       <c r="Y806" s="5"/>
       <c r="Z806" s="5"/>
       <c r="AA806" s="5"/>
+      <c r="AB806" s="5"/>
     </row>
     <row r="807">
       <c r="A807" s="5"/>
@@ -24153,6 +25112,7 @@
       <c r="Y807" s="5"/>
       <c r="Z807" s="5"/>
       <c r="AA807" s="5"/>
+      <c r="AB807" s="5"/>
     </row>
     <row r="808">
       <c r="A808" s="5"/>
@@ -24182,6 +25142,7 @@
       <c r="Y808" s="5"/>
       <c r="Z808" s="5"/>
       <c r="AA808" s="5"/>
+      <c r="AB808" s="5"/>
     </row>
     <row r="809">
       <c r="A809" s="5"/>
@@ -24211,6 +25172,7 @@
       <c r="Y809" s="5"/>
       <c r="Z809" s="5"/>
       <c r="AA809" s="5"/>
+      <c r="AB809" s="5"/>
     </row>
     <row r="810">
       <c r="A810" s="5"/>
@@ -24240,6 +25202,7 @@
       <c r="Y810" s="5"/>
       <c r="Z810" s="5"/>
       <c r="AA810" s="5"/>
+      <c r="AB810" s="5"/>
     </row>
     <row r="811">
       <c r="A811" s="5"/>
@@ -24269,6 +25232,7 @@
       <c r="Y811" s="5"/>
       <c r="Z811" s="5"/>
       <c r="AA811" s="5"/>
+      <c r="AB811" s="5"/>
     </row>
     <row r="812">
       <c r="A812" s="5"/>
@@ -24298,6 +25262,7 @@
       <c r="Y812" s="5"/>
       <c r="Z812" s="5"/>
       <c r="AA812" s="5"/>
+      <c r="AB812" s="5"/>
     </row>
     <row r="813">
       <c r="A813" s="5"/>
@@ -24327,6 +25292,7 @@
       <c r="Y813" s="5"/>
       <c r="Z813" s="5"/>
       <c r="AA813" s="5"/>
+      <c r="AB813" s="5"/>
     </row>
     <row r="814">
       <c r="A814" s="5"/>
@@ -24356,6 +25322,7 @@
       <c r="Y814" s="5"/>
       <c r="Z814" s="5"/>
       <c r="AA814" s="5"/>
+      <c r="AB814" s="5"/>
     </row>
     <row r="815">
       <c r="A815" s="5"/>
@@ -24385,6 +25352,7 @@
       <c r="Y815" s="5"/>
       <c r="Z815" s="5"/>
       <c r="AA815" s="5"/>
+      <c r="AB815" s="5"/>
     </row>
     <row r="816">
       <c r="A816" s="5"/>
@@ -24414,6 +25382,7 @@
       <c r="Y816" s="5"/>
       <c r="Z816" s="5"/>
       <c r="AA816" s="5"/>
+      <c r="AB816" s="5"/>
     </row>
     <row r="817">
       <c r="A817" s="5"/>
@@ -24443,6 +25412,7 @@
       <c r="Y817" s="5"/>
       <c r="Z817" s="5"/>
       <c r="AA817" s="5"/>
+      <c r="AB817" s="5"/>
     </row>
     <row r="818">
       <c r="A818" s="5"/>
@@ -24472,6 +25442,7 @@
       <c r="Y818" s="5"/>
       <c r="Z818" s="5"/>
       <c r="AA818" s="5"/>
+      <c r="AB818" s="5"/>
     </row>
     <row r="819">
       <c r="A819" s="5"/>
@@ -24501,6 +25472,7 @@
       <c r="Y819" s="5"/>
       <c r="Z819" s="5"/>
       <c r="AA819" s="5"/>
+      <c r="AB819" s="5"/>
     </row>
     <row r="820">
       <c r="A820" s="5"/>
@@ -24530,6 +25502,7 @@
       <c r="Y820" s="5"/>
       <c r="Z820" s="5"/>
       <c r="AA820" s="5"/>
+      <c r="AB820" s="5"/>
     </row>
     <row r="821">
       <c r="A821" s="5"/>
@@ -24559,6 +25532,7 @@
       <c r="Y821" s="5"/>
       <c r="Z821" s="5"/>
       <c r="AA821" s="5"/>
+      <c r="AB821" s="5"/>
     </row>
     <row r="822">
       <c r="A822" s="5"/>
@@ -24588,6 +25562,7 @@
       <c r="Y822" s="5"/>
       <c r="Z822" s="5"/>
       <c r="AA822" s="5"/>
+      <c r="AB822" s="5"/>
     </row>
     <row r="823">
       <c r="A823" s="5"/>
@@ -24617,6 +25592,7 @@
       <c r="Y823" s="5"/>
       <c r="Z823" s="5"/>
       <c r="AA823" s="5"/>
+      <c r="AB823" s="5"/>
     </row>
     <row r="824">
       <c r="A824" s="5"/>
@@ -24646,6 +25622,7 @@
       <c r="Y824" s="5"/>
       <c r="Z824" s="5"/>
       <c r="AA824" s="5"/>
+      <c r="AB824" s="5"/>
     </row>
     <row r="825">
       <c r="A825" s="5"/>
@@ -24675,6 +25652,7 @@
       <c r="Y825" s="5"/>
       <c r="Z825" s="5"/>
       <c r="AA825" s="5"/>
+      <c r="AB825" s="5"/>
     </row>
     <row r="826">
       <c r="A826" s="5"/>
@@ -24704,6 +25682,7 @@
       <c r="Y826" s="5"/>
       <c r="Z826" s="5"/>
       <c r="AA826" s="5"/>
+      <c r="AB826" s="5"/>
     </row>
     <row r="827">
       <c r="A827" s="5"/>
@@ -24733,6 +25712,7 @@
       <c r="Y827" s="5"/>
       <c r="Z827" s="5"/>
       <c r="AA827" s="5"/>
+      <c r="AB827" s="5"/>
     </row>
     <row r="828">
       <c r="A828" s="5"/>
@@ -24762,6 +25742,7 @@
       <c r="Y828" s="5"/>
       <c r="Z828" s="5"/>
       <c r="AA828" s="5"/>
+      <c r="AB828" s="5"/>
     </row>
     <row r="829">
       <c r="A829" s="5"/>
@@ -24791,6 +25772,7 @@
       <c r="Y829" s="5"/>
       <c r="Z829" s="5"/>
       <c r="AA829" s="5"/>
+      <c r="AB829" s="5"/>
     </row>
     <row r="830">
       <c r="A830" s="5"/>
@@ -24820,6 +25802,7 @@
       <c r="Y830" s="5"/>
       <c r="Z830" s="5"/>
       <c r="AA830" s="5"/>
+      <c r="AB830" s="5"/>
     </row>
     <row r="831">
       <c r="A831" s="5"/>
@@ -24849,6 +25832,7 @@
       <c r="Y831" s="5"/>
       <c r="Z831" s="5"/>
       <c r="AA831" s="5"/>
+      <c r="AB831" s="5"/>
     </row>
     <row r="832">
       <c r="A832" s="5"/>
@@ -24878,6 +25862,7 @@
       <c r="Y832" s="5"/>
       <c r="Z832" s="5"/>
       <c r="AA832" s="5"/>
+      <c r="AB832" s="5"/>
     </row>
     <row r="833">
       <c r="A833" s="5"/>
@@ -24907,6 +25892,7 @@
       <c r="Y833" s="5"/>
       <c r="Z833" s="5"/>
       <c r="AA833" s="5"/>
+      <c r="AB833" s="5"/>
     </row>
     <row r="834">
       <c r="A834" s="5"/>
@@ -24936,6 +25922,7 @@
       <c r="Y834" s="5"/>
       <c r="Z834" s="5"/>
       <c r="AA834" s="5"/>
+      <c r="AB834" s="5"/>
     </row>
     <row r="835">
       <c r="A835" s="5"/>
@@ -24965,6 +25952,7 @@
       <c r="Y835" s="5"/>
       <c r="Z835" s="5"/>
       <c r="AA835" s="5"/>
+      <c r="AB835" s="5"/>
     </row>
     <row r="836">
       <c r="A836" s="5"/>
@@ -24994,6 +25982,7 @@
       <c r="Y836" s="5"/>
       <c r="Z836" s="5"/>
       <c r="AA836" s="5"/>
+      <c r="AB836" s="5"/>
     </row>
     <row r="837">
       <c r="A837" s="5"/>
@@ -25023,6 +26012,7 @@
       <c r="Y837" s="5"/>
       <c r="Z837" s="5"/>
       <c r="AA837" s="5"/>
+      <c r="AB837" s="5"/>
     </row>
     <row r="838">
       <c r="A838" s="5"/>
@@ -25052,6 +26042,7 @@
       <c r="Y838" s="5"/>
       <c r="Z838" s="5"/>
       <c r="AA838" s="5"/>
+      <c r="AB838" s="5"/>
     </row>
     <row r="839">
       <c r="A839" s="5"/>
@@ -25081,6 +26072,7 @@
       <c r="Y839" s="5"/>
       <c r="Z839" s="5"/>
       <c r="AA839" s="5"/>
+      <c r="AB839" s="5"/>
     </row>
     <row r="840">
       <c r="A840" s="5"/>
@@ -25110,6 +26102,7 @@
       <c r="Y840" s="5"/>
       <c r="Z840" s="5"/>
       <c r="AA840" s="5"/>
+      <c r="AB840" s="5"/>
     </row>
     <row r="841">
       <c r="A841" s="5"/>
@@ -25139,6 +26132,7 @@
       <c r="Y841" s="5"/>
       <c r="Z841" s="5"/>
       <c r="AA841" s="5"/>
+      <c r="AB841" s="5"/>
     </row>
     <row r="842">
       <c r="A842" s="5"/>
@@ -25168,6 +26162,7 @@
       <c r="Y842" s="5"/>
       <c r="Z842" s="5"/>
       <c r="AA842" s="5"/>
+      <c r="AB842" s="5"/>
     </row>
     <row r="843">
       <c r="A843" s="5"/>
@@ -25197,6 +26192,7 @@
       <c r="Y843" s="5"/>
       <c r="Z843" s="5"/>
       <c r="AA843" s="5"/>
+      <c r="AB843" s="5"/>
     </row>
     <row r="844">
       <c r="A844" s="5"/>
@@ -25226,6 +26222,7 @@
       <c r="Y844" s="5"/>
       <c r="Z844" s="5"/>
       <c r="AA844" s="5"/>
+      <c r="AB844" s="5"/>
     </row>
     <row r="845">
       <c r="A845" s="5"/>
@@ -25255,6 +26252,7 @@
       <c r="Y845" s="5"/>
       <c r="Z845" s="5"/>
       <c r="AA845" s="5"/>
+      <c r="AB845" s="5"/>
     </row>
     <row r="846">
       <c r="A846" s="5"/>
@@ -25284,6 +26282,7 @@
       <c r="Y846" s="5"/>
       <c r="Z846" s="5"/>
       <c r="AA846" s="5"/>
+      <c r="AB846" s="5"/>
     </row>
     <row r="847">
       <c r="A847" s="5"/>
@@ -25313,6 +26312,7 @@
       <c r="Y847" s="5"/>
       <c r="Z847" s="5"/>
       <c r="AA847" s="5"/>
+      <c r="AB847" s="5"/>
     </row>
     <row r="848">
       <c r="A848" s="5"/>
@@ -25342,6 +26342,7 @@
       <c r="Y848" s="5"/>
       <c r="Z848" s="5"/>
       <c r="AA848" s="5"/>
+      <c r="AB848" s="5"/>
     </row>
     <row r="849">
       <c r="A849" s="5"/>
@@ -25371,6 +26372,7 @@
       <c r="Y849" s="5"/>
       <c r="Z849" s="5"/>
       <c r="AA849" s="5"/>
+      <c r="AB849" s="5"/>
     </row>
     <row r="850">
       <c r="A850" s="5"/>
@@ -25400,6 +26402,7 @@
       <c r="Y850" s="5"/>
       <c r="Z850" s="5"/>
       <c r="AA850" s="5"/>
+      <c r="AB850" s="5"/>
     </row>
     <row r="851">
       <c r="A851" s="5"/>
@@ -25429,6 +26432,7 @@
       <c r="Y851" s="5"/>
       <c r="Z851" s="5"/>
       <c r="AA851" s="5"/>
+      <c r="AB851" s="5"/>
     </row>
     <row r="852">
       <c r="A852" s="5"/>
@@ -25458,6 +26462,7 @@
       <c r="Y852" s="5"/>
       <c r="Z852" s="5"/>
       <c r="AA852" s="5"/>
+      <c r="AB852" s="5"/>
     </row>
     <row r="853">
       <c r="A853" s="5"/>
@@ -25487,6 +26492,7 @@
       <c r="Y853" s="5"/>
       <c r="Z853" s="5"/>
       <c r="AA853" s="5"/>
+      <c r="AB853" s="5"/>
     </row>
     <row r="854">
       <c r="A854" s="5"/>
@@ -25516,6 +26522,7 @@
       <c r="Y854" s="5"/>
       <c r="Z854" s="5"/>
       <c r="AA854" s="5"/>
+      <c r="AB854" s="5"/>
     </row>
     <row r="855">
       <c r="A855" s="5"/>
@@ -25545,6 +26552,7 @@
       <c r="Y855" s="5"/>
       <c r="Z855" s="5"/>
       <c r="AA855" s="5"/>
+      <c r="AB855" s="5"/>
     </row>
     <row r="856">
       <c r="A856" s="5"/>
@@ -25574,6 +26582,7 @@
       <c r="Y856" s="5"/>
       <c r="Z856" s="5"/>
       <c r="AA856" s="5"/>
+      <c r="AB856" s="5"/>
     </row>
     <row r="857">
       <c r="A857" s="5"/>
@@ -25603,6 +26612,7 @@
       <c r="Y857" s="5"/>
       <c r="Z857" s="5"/>
       <c r="AA857" s="5"/>
+      <c r="AB857" s="5"/>
     </row>
     <row r="858">
       <c r="A858" s="5"/>
@@ -25632,6 +26642,7 @@
       <c r="Y858" s="5"/>
       <c r="Z858" s="5"/>
       <c r="AA858" s="5"/>
+      <c r="AB858" s="5"/>
     </row>
     <row r="859">
       <c r="A859" s="5"/>
@@ -25661,6 +26672,7 @@
       <c r="Y859" s="5"/>
       <c r="Z859" s="5"/>
       <c r="AA859" s="5"/>
+      <c r="AB859" s="5"/>
     </row>
     <row r="860">
       <c r="A860" s="5"/>
@@ -25690,6 +26702,7 @@
       <c r="Y860" s="5"/>
       <c r="Z860" s="5"/>
       <c r="AA860" s="5"/>
+      <c r="AB860" s="5"/>
     </row>
     <row r="861">
       <c r="A861" s="5"/>
@@ -25719,6 +26732,7 @@
       <c r="Y861" s="5"/>
       <c r="Z861" s="5"/>
       <c r="AA861" s="5"/>
+      <c r="AB861" s="5"/>
     </row>
     <row r="862">
       <c r="A862" s="5"/>
@@ -25748,6 +26762,7 @@
       <c r="Y862" s="5"/>
       <c r="Z862" s="5"/>
       <c r="AA862" s="5"/>
+      <c r="AB862" s="5"/>
     </row>
     <row r="863">
       <c r="A863" s="5"/>
@@ -25777,6 +26792,7 @@
       <c r="Y863" s="5"/>
       <c r="Z863" s="5"/>
       <c r="AA863" s="5"/>
+      <c r="AB863" s="5"/>
     </row>
     <row r="864">
       <c r="A864" s="5"/>
@@ -25806,6 +26822,7 @@
       <c r="Y864" s="5"/>
       <c r="Z864" s="5"/>
       <c r="AA864" s="5"/>
+      <c r="AB864" s="5"/>
     </row>
     <row r="865">
       <c r="A865" s="5"/>
@@ -25835,6 +26852,7 @@
       <c r="Y865" s="5"/>
       <c r="Z865" s="5"/>
       <c r="AA865" s="5"/>
+      <c r="AB865" s="5"/>
     </row>
     <row r="866">
       <c r="A866" s="5"/>
@@ -25864,6 +26882,7 @@
       <c r="Y866" s="5"/>
       <c r="Z866" s="5"/>
       <c r="AA866" s="5"/>
+      <c r="AB866" s="5"/>
     </row>
     <row r="867">
       <c r="A867" s="5"/>
@@ -25893,6 +26912,7 @@
       <c r="Y867" s="5"/>
       <c r="Z867" s="5"/>
       <c r="AA867" s="5"/>
+      <c r="AB867" s="5"/>
     </row>
     <row r="868">
       <c r="A868" s="5"/>
@@ -25922,6 +26942,7 @@
       <c r="Y868" s="5"/>
       <c r="Z868" s="5"/>
       <c r="AA868" s="5"/>
+      <c r="AB868" s="5"/>
     </row>
     <row r="869">
       <c r="A869" s="5"/>
@@ -25951,6 +26972,7 @@
       <c r="Y869" s="5"/>
       <c r="Z869" s="5"/>
       <c r="AA869" s="5"/>
+      <c r="AB869" s="5"/>
     </row>
     <row r="870">
       <c r="A870" s="5"/>
@@ -25980,6 +27002,7 @@
       <c r="Y870" s="5"/>
       <c r="Z870" s="5"/>
       <c r="AA870" s="5"/>
+      <c r="AB870" s="5"/>
     </row>
     <row r="871">
       <c r="A871" s="5"/>
@@ -26009,6 +27032,7 @@
       <c r="Y871" s="5"/>
       <c r="Z871" s="5"/>
       <c r="AA871" s="5"/>
+      <c r="AB871" s="5"/>
     </row>
     <row r="872">
       <c r="A872" s="5"/>
@@ -26038,6 +27062,7 @@
       <c r="Y872" s="5"/>
       <c r="Z872" s="5"/>
       <c r="AA872" s="5"/>
+      <c r="AB872" s="5"/>
     </row>
     <row r="873">
       <c r="A873" s="5"/>
@@ -26067,6 +27092,7 @@
       <c r="Y873" s="5"/>
       <c r="Z873" s="5"/>
       <c r="AA873" s="5"/>
+      <c r="AB873" s="5"/>
     </row>
     <row r="874">
       <c r="A874" s="5"/>
@@ -26096,6 +27122,7 @@
       <c r="Y874" s="5"/>
       <c r="Z874" s="5"/>
       <c r="AA874" s="5"/>
+      <c r="AB874" s="5"/>
     </row>
     <row r="875">
       <c r="A875" s="5"/>
@@ -26125,6 +27152,7 @@
       <c r="Y875" s="5"/>
       <c r="Z875" s="5"/>
       <c r="AA875" s="5"/>
+      <c r="AB875" s="5"/>
     </row>
     <row r="876">
       <c r="A876" s="5"/>
@@ -26154,6 +27182,7 @@
       <c r="Y876" s="5"/>
       <c r="Z876" s="5"/>
       <c r="AA876" s="5"/>
+      <c r="AB876" s="5"/>
     </row>
     <row r="877">
       <c r="A877" s="5"/>
@@ -26183,6 +27212,7 @@
       <c r="Y877" s="5"/>
       <c r="Z877" s="5"/>
       <c r="AA877" s="5"/>
+      <c r="AB877" s="5"/>
     </row>
     <row r="878">
       <c r="A878" s="5"/>
@@ -26212,6 +27242,7 @@
       <c r="Y878" s="5"/>
       <c r="Z878" s="5"/>
       <c r="AA878" s="5"/>
+      <c r="AB878" s="5"/>
     </row>
     <row r="879">
       <c r="A879" s="5"/>
@@ -26241,6 +27272,7 @@
       <c r="Y879" s="5"/>
       <c r="Z879" s="5"/>
       <c r="AA879" s="5"/>
+      <c r="AB879" s="5"/>
     </row>
     <row r="880">
       <c r="A880" s="5"/>
@@ -26270,6 +27302,7 @@
       <c r="Y880" s="5"/>
       <c r="Z880" s="5"/>
       <c r="AA880" s="5"/>
+      <c r="AB880" s="5"/>
     </row>
     <row r="881">
       <c r="A881" s="5"/>
@@ -26299,6 +27332,7 @@
       <c r="Y881" s="5"/>
       <c r="Z881" s="5"/>
       <c r="AA881" s="5"/>
+      <c r="AB881" s="5"/>
     </row>
     <row r="882">
       <c r="A882" s="5"/>
@@ -26328,6 +27362,7 @@
       <c r="Y882" s="5"/>
       <c r="Z882" s="5"/>
       <c r="AA882" s="5"/>
+      <c r="AB882" s="5"/>
     </row>
     <row r="883">
       <c r="A883" s="5"/>
@@ -26357,6 +27392,7 @@
       <c r="Y883" s="5"/>
       <c r="Z883" s="5"/>
       <c r="AA883" s="5"/>
+      <c r="AB883" s="5"/>
     </row>
     <row r="884">
       <c r="A884" s="5"/>
@@ -26386,6 +27422,7 @@
       <c r="Y884" s="5"/>
       <c r="Z884" s="5"/>
       <c r="AA884" s="5"/>
+      <c r="AB884" s="5"/>
     </row>
     <row r="885">
       <c r="A885" s="5"/>
@@ -26415,6 +27452,7 @@
       <c r="Y885" s="5"/>
       <c r="Z885" s="5"/>
       <c r="AA885" s="5"/>
+      <c r="AB885" s="5"/>
     </row>
     <row r="886">
       <c r="A886" s="5"/>
@@ -26444,6 +27482,7 @@
       <c r="Y886" s="5"/>
       <c r="Z886" s="5"/>
       <c r="AA886" s="5"/>
+      <c r="AB886" s="5"/>
     </row>
     <row r="887">
       <c r="A887" s="5"/>
@@ -26473,6 +27512,7 @@
       <c r="Y887" s="5"/>
       <c r="Z887" s="5"/>
       <c r="AA887" s="5"/>
+      <c r="AB887" s="5"/>
     </row>
     <row r="888">
       <c r="A888" s="5"/>
@@ -26502,6 +27542,7 @@
       <c r="Y888" s="5"/>
       <c r="Z888" s="5"/>
       <c r="AA888" s="5"/>
+      <c r="AB888" s="5"/>
     </row>
     <row r="889">
       <c r="A889" s="5"/>
@@ -26531,6 +27572,7 @@
       <c r="Y889" s="5"/>
       <c r="Z889" s="5"/>
       <c r="AA889" s="5"/>
+      <c r="AB889" s="5"/>
     </row>
     <row r="890">
       <c r="A890" s="5"/>
@@ -26560,6 +27602,7 @@
       <c r="Y890" s="5"/>
       <c r="Z890" s="5"/>
       <c r="AA890" s="5"/>
+      <c r="AB890" s="5"/>
     </row>
     <row r="891">
       <c r="A891" s="5"/>
@@ -26589,6 +27632,7 @@
       <c r="Y891" s="5"/>
       <c r="Z891" s="5"/>
       <c r="AA891" s="5"/>
+      <c r="AB891" s="5"/>
     </row>
     <row r="892">
       <c r="A892" s="5"/>
@@ -26618,6 +27662,7 @@
       <c r="Y892" s="5"/>
       <c r="Z892" s="5"/>
       <c r="AA892" s="5"/>
+      <c r="AB892" s="5"/>
     </row>
     <row r="893">
       <c r="A893" s="5"/>
@@ -26647,6 +27692,7 @@
       <c r="Y893" s="5"/>
       <c r="Z893" s="5"/>
       <c r="AA893" s="5"/>
+      <c r="AB893" s="5"/>
     </row>
     <row r="894">
       <c r="A894" s="5"/>
@@ -26676,6 +27722,7 @@
       <c r="Y894" s="5"/>
       <c r="Z894" s="5"/>
       <c r="AA894" s="5"/>
+      <c r="AB894" s="5"/>
     </row>
     <row r="895">
       <c r="A895" s="5"/>
@@ -26705,6 +27752,7 @@
       <c r="Y895" s="5"/>
       <c r="Z895" s="5"/>
       <c r="AA895" s="5"/>
+      <c r="AB895" s="5"/>
     </row>
     <row r="896">
       <c r="A896" s="5"/>
@@ -26734,6 +27782,7 @@
       <c r="Y896" s="5"/>
       <c r="Z896" s="5"/>
       <c r="AA896" s="5"/>
+      <c r="AB896" s="5"/>
     </row>
     <row r="897">
       <c r="A897" s="5"/>
@@ -26763,6 +27812,7 @@
       <c r="Y897" s="5"/>
       <c r="Z897" s="5"/>
       <c r="AA897" s="5"/>
+      <c r="AB897" s="5"/>
     </row>
     <row r="898">
       <c r="A898" s="5"/>
@@ -26792,6 +27842,7 @@
       <c r="Y898" s="5"/>
       <c r="Z898" s="5"/>
       <c r="AA898" s="5"/>
+      <c r="AB898" s="5"/>
     </row>
     <row r="899">
       <c r="A899" s="5"/>
@@ -26821,6 +27872,7 @@
       <c r="Y899" s="5"/>
       <c r="Z899" s="5"/>
       <c r="AA899" s="5"/>
+      <c r="AB899" s="5"/>
     </row>
     <row r="900">
       <c r="A900" s="5"/>
@@ -26850,6 +27902,7 @@
       <c r="Y900" s="5"/>
       <c r="Z900" s="5"/>
       <c r="AA900" s="5"/>
+      <c r="AB900" s="5"/>
     </row>
     <row r="901">
       <c r="A901" s="5"/>
@@ -26879,6 +27932,7 @@
       <c r="Y901" s="5"/>
       <c r="Z901" s="5"/>
       <c r="AA901" s="5"/>
+      <c r="AB901" s="5"/>
     </row>
     <row r="902">
       <c r="A902" s="5"/>
@@ -26908,6 +27962,7 @@
       <c r="Y902" s="5"/>
       <c r="Z902" s="5"/>
       <c r="AA902" s="5"/>
+      <c r="AB902" s="5"/>
     </row>
     <row r="903">
       <c r="A903" s="5"/>
@@ -26937,6 +27992,7 @@
       <c r="Y903" s="5"/>
       <c r="Z903" s="5"/>
       <c r="AA903" s="5"/>
+      <c r="AB903" s="5"/>
     </row>
     <row r="904">
       <c r="A904" s="5"/>
@@ -26966,6 +28022,7 @@
       <c r="Y904" s="5"/>
       <c r="Z904" s="5"/>
       <c r="AA904" s="5"/>
+      <c r="AB904" s="5"/>
     </row>
     <row r="905">
       <c r="A905" s="5"/>
@@ -26995,6 +28052,7 @@
       <c r="Y905" s="5"/>
       <c r="Z905" s="5"/>
       <c r="AA905" s="5"/>
+      <c r="AB905" s="5"/>
     </row>
     <row r="906">
       <c r="A906" s="5"/>
@@ -27024,6 +28082,7 @@
       <c r="Y906" s="5"/>
       <c r="Z906" s="5"/>
       <c r="AA906" s="5"/>
+      <c r="AB906" s="5"/>
     </row>
     <row r="907">
       <c r="A907" s="5"/>
@@ -27053,6 +28112,7 @@
       <c r="Y907" s="5"/>
       <c r="Z907" s="5"/>
       <c r="AA907" s="5"/>
+      <c r="AB907" s="5"/>
     </row>
     <row r="908">
       <c r="A908" s="5"/>
@@ -27082,6 +28142,7 @@
       <c r="Y908" s="5"/>
       <c r="Z908" s="5"/>
       <c r="AA908" s="5"/>
+      <c r="AB908" s="5"/>
     </row>
     <row r="909">
       <c r="A909" s="5"/>
@@ -27111,6 +28172,7 @@
       <c r="Y909" s="5"/>
       <c r="Z909" s="5"/>
       <c r="AA909" s="5"/>
+      <c r="AB909" s="5"/>
     </row>
     <row r="910">
       <c r="A910" s="5"/>
@@ -27140,6 +28202,7 @@
       <c r="Y910" s="5"/>
       <c r="Z910" s="5"/>
       <c r="AA910" s="5"/>
+      <c r="AB910" s="5"/>
     </row>
     <row r="911">
       <c r="A911" s="5"/>
@@ -27169,6 +28232,7 @@
       <c r="Y911" s="5"/>
       <c r="Z911" s="5"/>
       <c r="AA911" s="5"/>
+      <c r="AB911" s="5"/>
     </row>
     <row r="912">
       <c r="A912" s="5"/>
@@ -27198,6 +28262,7 @@
       <c r="Y912" s="5"/>
       <c r="Z912" s="5"/>
       <c r="AA912" s="5"/>
+      <c r="AB912" s="5"/>
     </row>
     <row r="913">
       <c r="A913" s="5"/>
@@ -27227,6 +28292,7 @@
       <c r="Y913" s="5"/>
       <c r="Z913" s="5"/>
       <c r="AA913" s="5"/>
+      <c r="AB913" s="5"/>
     </row>
     <row r="914">
       <c r="A914" s="5"/>
@@ -27256,6 +28322,7 @@
       <c r="Y914" s="5"/>
       <c r="Z914" s="5"/>
       <c r="AA914" s="5"/>
+      <c r="AB914" s="5"/>
     </row>
     <row r="915">
       <c r="A915" s="5"/>
@@ -27285,6 +28352,7 @@
       <c r="Y915" s="5"/>
       <c r="Z915" s="5"/>
       <c r="AA915" s="5"/>
+      <c r="AB915" s="5"/>
     </row>
     <row r="916">
       <c r="A916" s="5"/>
@@ -27314,6 +28382,7 @@
       <c r="Y916" s="5"/>
       <c r="Z916" s="5"/>
       <c r="AA916" s="5"/>
+      <c r="AB916" s="5"/>
     </row>
     <row r="917">
       <c r="A917" s="5"/>
@@ -27343,6 +28412,7 @@
       <c r="Y917" s="5"/>
       <c r="Z917" s="5"/>
       <c r="AA917" s="5"/>
+      <c r="AB917" s="5"/>
     </row>
     <row r="918">
       <c r="A918" s="5"/>
@@ -27372,6 +28442,7 @@
       <c r="Y918" s="5"/>
       <c r="Z918" s="5"/>
       <c r="AA918" s="5"/>
+      <c r="AB918" s="5"/>
     </row>
     <row r="919">
       <c r="A919" s="5"/>
@@ -27401,6 +28472,7 @@
       <c r="Y919" s="5"/>
       <c r="Z919" s="5"/>
       <c r="AA919" s="5"/>
+      <c r="AB919" s="5"/>
     </row>
     <row r="920">
       <c r="A920" s="5"/>
@@ -27430,6 +28502,7 @@
       <c r="Y920" s="5"/>
       <c r="Z920" s="5"/>
       <c r="AA920" s="5"/>
+      <c r="AB920" s="5"/>
     </row>
     <row r="921">
       <c r="A921" s="5"/>
@@ -27459,6 +28532,7 @@
       <c r="Y921" s="5"/>
       <c r="Z921" s="5"/>
       <c r="AA921" s="5"/>
+      <c r="AB921" s="5"/>
     </row>
     <row r="922">
       <c r="A922" s="5"/>
@@ -27488,6 +28562,7 @@
       <c r="Y922" s="5"/>
       <c r="Z922" s="5"/>
       <c r="AA922" s="5"/>
+      <c r="AB922" s="5"/>
     </row>
     <row r="923">
       <c r="A923" s="5"/>
@@ -27517,6 +28592,7 @@
       <c r="Y923" s="5"/>
       <c r="Z923" s="5"/>
       <c r="AA923" s="5"/>
+      <c r="AB923" s="5"/>
     </row>
     <row r="924">
       <c r="A924" s="5"/>
@@ -27546,6 +28622,7 @@
       <c r="Y924" s="5"/>
       <c r="Z924" s="5"/>
       <c r="AA924" s="5"/>
+      <c r="AB924" s="5"/>
     </row>
     <row r="925">
       <c r="A925" s="5"/>
@@ -27575,6 +28652,7 @@
       <c r="Y925" s="5"/>
       <c r="Z925" s="5"/>
       <c r="AA925" s="5"/>
+      <c r="AB925" s="5"/>
     </row>
     <row r="926">
       <c r="A926" s="5"/>
@@ -27604,6 +28682,7 @@
       <c r="Y926" s="5"/>
       <c r="Z926" s="5"/>
       <c r="AA926" s="5"/>
+      <c r="AB926" s="5"/>
     </row>
     <row r="927">
       <c r="A927" s="5"/>
@@ -27633,6 +28712,7 @@
       <c r="Y927" s="5"/>
       <c r="Z927" s="5"/>
       <c r="AA927" s="5"/>
+      <c r="AB927" s="5"/>
     </row>
     <row r="928">
       <c r="A928" s="5"/>
@@ -27662,6 +28742,7 @@
       <c r="Y928" s="5"/>
       <c r="Z928" s="5"/>
       <c r="AA928" s="5"/>
+      <c r="AB928" s="5"/>
     </row>
     <row r="929">
       <c r="A929" s="5"/>
@@ -27691,6 +28772,7 @@
       <c r="Y929" s="5"/>
       <c r="Z929" s="5"/>
       <c r="AA929" s="5"/>
+      <c r="AB929" s="5"/>
     </row>
     <row r="930">
       <c r="A930" s="5"/>
@@ -27720,6 +28802,7 @@
       <c r="Y930" s="5"/>
       <c r="Z930" s="5"/>
       <c r="AA930" s="5"/>
+      <c r="AB930" s="5"/>
     </row>
     <row r="931">
       <c r="A931" s="5"/>
@@ -27749,6 +28832,7 @@
       <c r="Y931" s="5"/>
       <c r="Z931" s="5"/>
       <c r="AA931" s="5"/>
+      <c r="AB931" s="5"/>
     </row>
     <row r="932">
       <c r="A932" s="5"/>
@@ -27778,6 +28862,7 @@
       <c r="Y932" s="5"/>
       <c r="Z932" s="5"/>
       <c r="AA932" s="5"/>
+      <c r="AB932" s="5"/>
     </row>
     <row r="933">
       <c r="A933" s="5"/>
@@ -27807,6 +28892,7 @@
       <c r="Y933" s="5"/>
       <c r="Z933" s="5"/>
       <c r="AA933" s="5"/>
+      <c r="AB933" s="5"/>
     </row>
     <row r="934">
       <c r="A934" s="5"/>
@@ -27836,6 +28922,7 @@
       <c r="Y934" s="5"/>
       <c r="Z934" s="5"/>
       <c r="AA934" s="5"/>
+      <c r="AB934" s="5"/>
     </row>
     <row r="935">
       <c r="A935" s="5"/>
@@ -27865,6 +28952,7 @@
       <c r="Y935" s="5"/>
       <c r="Z935" s="5"/>
       <c r="AA935" s="5"/>
+      <c r="AB935" s="5"/>
     </row>
     <row r="936">
       <c r="A936" s="5"/>
@@ -27894,6 +28982,7 @@
       <c r="Y936" s="5"/>
       <c r="Z936" s="5"/>
       <c r="AA936" s="5"/>
+      <c r="AB936" s="5"/>
     </row>
     <row r="937">
       <c r="A937" s="5"/>
@@ -27923,6 +29012,7 @@
       <c r="Y937" s="5"/>
       <c r="Z937" s="5"/>
       <c r="AA937" s="5"/>
+      <c r="AB937" s="5"/>
     </row>
     <row r="938">
       <c r="A938" s="5"/>
@@ -27952,6 +29042,7 @@
       <c r="Y938" s="5"/>
       <c r="Z938" s="5"/>
       <c r="AA938" s="5"/>
+      <c r="AB938" s="5"/>
     </row>
     <row r="939">
       <c r="A939" s="5"/>
@@ -27981,6 +29072,7 @@
       <c r="Y939" s="5"/>
       <c r="Z939" s="5"/>
       <c r="AA939" s="5"/>
+      <c r="AB939" s="5"/>
     </row>
     <row r="940">
       <c r="A940" s="5"/>
@@ -28010,6 +29102,7 @@
       <c r="Y940" s="5"/>
       <c r="Z940" s="5"/>
       <c r="AA940" s="5"/>
+      <c r="AB940" s="5"/>
     </row>
     <row r="941">
       <c r="A941" s="5"/>
@@ -28039,6 +29132,7 @@
       <c r="Y941" s="5"/>
       <c r="Z941" s="5"/>
       <c r="AA941" s="5"/>
+      <c r="AB941" s="5"/>
     </row>
     <row r="942">
       <c r="A942" s="5"/>
@@ -28068,6 +29162,7 @@
       <c r="Y942" s="5"/>
       <c r="Z942" s="5"/>
       <c r="AA942" s="5"/>
+      <c r="AB942" s="5"/>
     </row>
     <row r="943">
       <c r="A943" s="5"/>
@@ -28097,6 +29192,7 @@
       <c r="Y943" s="5"/>
       <c r="Z943" s="5"/>
       <c r="AA943" s="5"/>
+      <c r="AB943" s="5"/>
     </row>
     <row r="944">
       <c r="A944" s="5"/>
@@ -28126,6 +29222,7 @@
       <c r="Y944" s="5"/>
       <c r="Z944" s="5"/>
       <c r="AA944" s="5"/>
+      <c r="AB944" s="5"/>
     </row>
     <row r="945">
       <c r="A945" s="5"/>
@@ -28155,6 +29252,7 @@
       <c r="Y945" s="5"/>
       <c r="Z945" s="5"/>
       <c r="AA945" s="5"/>
+      <c r="AB945" s="5"/>
     </row>
     <row r="946">
       <c r="A946" s="5"/>
@@ -28184,6 +29282,7 @@
       <c r="Y946" s="5"/>
       <c r="Z946" s="5"/>
       <c r="AA946" s="5"/>
+      <c r="AB946" s="5"/>
     </row>
     <row r="947">
       <c r="A947" s="5"/>
@@ -28213,6 +29312,7 @@
       <c r="Y947" s="5"/>
       <c r="Z947" s="5"/>
       <c r="AA947" s="5"/>
+      <c r="AB947" s="5"/>
     </row>
     <row r="948">
       <c r="A948" s="5"/>
@@ -28242,6 +29342,7 @@
       <c r="Y948" s="5"/>
       <c r="Z948" s="5"/>
       <c r="AA948" s="5"/>
+      <c r="AB948" s="5"/>
     </row>
     <row r="949">
       <c r="A949" s="5"/>
@@ -28271,6 +29372,7 @@
       <c r="Y949" s="5"/>
       <c r="Z949" s="5"/>
       <c r="AA949" s="5"/>
+      <c r="AB949" s="5"/>
     </row>
     <row r="950">
       <c r="A950" s="5"/>
@@ -28300,6 +29402,7 @@
       <c r="Y950" s="5"/>
       <c r="Z950" s="5"/>
       <c r="AA950" s="5"/>
+      <c r="AB950" s="5"/>
     </row>
     <row r="951">
       <c r="A951" s="5"/>
@@ -28329,6 +29432,7 @@
       <c r="Y951" s="5"/>
       <c r="Z951" s="5"/>
       <c r="AA951" s="5"/>
+      <c r="AB951" s="5"/>
     </row>
     <row r="952">
       <c r="A952" s="5"/>
@@ -28358,6 +29462,7 @@
       <c r="Y952" s="5"/>
       <c r="Z952" s="5"/>
       <c r="AA952" s="5"/>
+      <c r="AB952" s="5"/>
     </row>
     <row r="953">
       <c r="A953" s="5"/>
@@ -28387,6 +29492,7 @@
       <c r="Y953" s="5"/>
       <c r="Z953" s="5"/>
       <c r="AA953" s="5"/>
+      <c r="AB953" s="5"/>
     </row>
     <row r="954">
       <c r="A954" s="5"/>
@@ -28416,6 +29522,7 @@
       <c r="Y954" s="5"/>
       <c r="Z954" s="5"/>
       <c r="AA954" s="5"/>
+      <c r="AB954" s="5"/>
     </row>
     <row r="955">
       <c r="A955" s="5"/>
@@ -28445,6 +29552,7 @@
       <c r="Y955" s="5"/>
       <c r="Z955" s="5"/>
       <c r="AA955" s="5"/>
+      <c r="AB955" s="5"/>
     </row>
     <row r="956">
       <c r="A956" s="5"/>
@@ -28474,6 +29582,7 @@
       <c r="Y956" s="5"/>
       <c r="Z956" s="5"/>
       <c r="AA956" s="5"/>
+      <c r="AB956" s="5"/>
     </row>
     <row r="957">
       <c r="A957" s="5"/>
@@ -28503,6 +29612,7 @@
       <c r="Y957" s="5"/>
       <c r="Z957" s="5"/>
       <c r="AA957" s="5"/>
+      <c r="AB957" s="5"/>
     </row>
     <row r="958">
       <c r="A958" s="5"/>
@@ -28532,6 +29642,7 @@
       <c r="Y958" s="5"/>
       <c r="Z958" s="5"/>
       <c r="AA958" s="5"/>
+      <c r="AB958" s="5"/>
     </row>
     <row r="959">
       <c r="A959" s="5"/>
@@ -28561,6 +29672,7 @@
       <c r="Y959" s="5"/>
       <c r="Z959" s="5"/>
       <c r="AA959" s="5"/>
+      <c r="AB959" s="5"/>
     </row>
     <row r="960">
       <c r="A960" s="5"/>
@@ -28590,6 +29702,7 @@
       <c r="Y960" s="5"/>
       <c r="Z960" s="5"/>
       <c r="AA960" s="5"/>
+      <c r="AB960" s="5"/>
     </row>
     <row r="961">
       <c r="A961" s="5"/>
@@ -28619,6 +29732,7 @@
       <c r="Y961" s="5"/>
       <c r="Z961" s="5"/>
       <c r="AA961" s="5"/>
+      <c r="AB961" s="5"/>
     </row>
     <row r="962">
       <c r="A962" s="5"/>
@@ -28648,6 +29762,7 @@
       <c r="Y962" s="5"/>
       <c r="Z962" s="5"/>
       <c r="AA962" s="5"/>
+      <c r="AB962" s="5"/>
     </row>
     <row r="963">
       <c r="A963" s="5"/>
@@ -28677,6 +29792,7 @@
       <c r="Y963" s="5"/>
       <c r="Z963" s="5"/>
       <c r="AA963" s="5"/>
+      <c r="AB963" s="5"/>
     </row>
     <row r="964">
       <c r="A964" s="5"/>
@@ -28706,6 +29822,7 @@
       <c r="Y964" s="5"/>
       <c r="Z964" s="5"/>
       <c r="AA964" s="5"/>
+      <c r="AB964" s="5"/>
     </row>
     <row r="965">
       <c r="A965" s="5"/>
@@ -28735,6 +29852,7 @@
       <c r="Y965" s="5"/>
       <c r="Z965" s="5"/>
       <c r="AA965" s="5"/>
+      <c r="AB965" s="5"/>
     </row>
     <row r="966">
       <c r="A966" s="5"/>
@@ -28764,6 +29882,7 @@
       <c r="Y966" s="5"/>
       <c r="Z966" s="5"/>
       <c r="AA966" s="5"/>
+      <c r="AB966" s="5"/>
     </row>
     <row r="967">
       <c r="A967" s="5"/>
@@ -28793,6 +29912,7 @@
       <c r="Y967" s="5"/>
       <c r="Z967" s="5"/>
       <c r="AA967" s="5"/>
+      <c r="AB967" s="5"/>
     </row>
     <row r="968">
       <c r="A968" s="5"/>
@@ -28822,6 +29942,7 @@
       <c r="Y968" s="5"/>
       <c r="Z968" s="5"/>
       <c r="AA968" s="5"/>
+      <c r="AB968" s="5"/>
     </row>
     <row r="969">
       <c r="A969" s="5"/>
@@ -28851,6 +29972,7 @@
       <c r="Y969" s="5"/>
       <c r="Z969" s="5"/>
       <c r="AA969" s="5"/>
+      <c r="AB969" s="5"/>
     </row>
     <row r="970">
       <c r="A970" s="5"/>
@@ -28880,6 +30002,7 @@
       <c r="Y970" s="5"/>
       <c r="Z970" s="5"/>
       <c r="AA970" s="5"/>
+      <c r="AB970" s="5"/>
     </row>
     <row r="971">
       <c r="A971" s="5"/>
@@ -28909,6 +30032,7 @@
       <c r="Y971" s="5"/>
       <c r="Z971" s="5"/>
       <c r="AA971" s="5"/>
+      <c r="AB971" s="5"/>
     </row>
     <row r="972">
       <c r="A972" s="5"/>
@@ -28938,6 +30062,7 @@
       <c r="Y972" s="5"/>
       <c r="Z972" s="5"/>
       <c r="AA972" s="5"/>
+      <c r="AB972" s="5"/>
     </row>
     <row r="973">
       <c r="A973" s="5"/>
@@ -28967,6 +30092,7 @@
       <c r="Y973" s="5"/>
       <c r="Z973" s="5"/>
       <c r="AA973" s="5"/>
+      <c r="AB973" s="5"/>
     </row>
     <row r="974">
       <c r="A974" s="5"/>
@@ -28996,6 +30122,7 @@
       <c r="Y974" s="5"/>
       <c r="Z974" s="5"/>
       <c r="AA974" s="5"/>
+      <c r="AB974" s="5"/>
     </row>
     <row r="975">
       <c r="A975" s="5"/>
@@ -29025,6 +30152,7 @@
       <c r="Y975" s="5"/>
       <c r="Z975" s="5"/>
       <c r="AA975" s="5"/>
+      <c r="AB975" s="5"/>
     </row>
     <row r="976">
       <c r="A976" s="5"/>
@@ -29054,6 +30182,7 @@
       <c r="Y976" s="5"/>
       <c r="Z976" s="5"/>
       <c r="AA976" s="5"/>
+      <c r="AB976" s="5"/>
     </row>
     <row r="977">
       <c r="A977" s="5"/>
@@ -29083,6 +30212,7 @@
       <c r="Y977" s="5"/>
       <c r="Z977" s="5"/>
       <c r="AA977" s="5"/>
+      <c r="AB977" s="5"/>
     </row>
     <row r="978">
       <c r="A978" s="5"/>
@@ -29112,6 +30242,7 @@
       <c r="Y978" s="5"/>
       <c r="Z978" s="5"/>
       <c r="AA978" s="5"/>
+      <c r="AB978" s="5"/>
     </row>
     <row r="979">
       <c r="A979" s="5"/>
@@ -29141,6 +30272,7 @@
       <c r="Y979" s="5"/>
       <c r="Z979" s="5"/>
       <c r="AA979" s="5"/>
+      <c r="AB979" s="5"/>
     </row>
     <row r="980">
       <c r="A980" s="5"/>
@@ -29170,6 +30302,7 @@
       <c r="Y980" s="5"/>
       <c r="Z980" s="5"/>
       <c r="AA980" s="5"/>
+      <c r="AB980" s="5"/>
     </row>
     <row r="981">
       <c r="A981" s="5"/>
@@ -29199,6 +30332,7 @@
       <c r="Y981" s="5"/>
       <c r="Z981" s="5"/>
       <c r="AA981" s="5"/>
+      <c r="AB981" s="5"/>
     </row>
     <row r="982">
       <c r="A982" s="5"/>
@@ -29228,6 +30362,7 @@
       <c r="Y982" s="5"/>
       <c r="Z982" s="5"/>
       <c r="AA982" s="5"/>
+      <c r="AB982" s="5"/>
     </row>
     <row r="983">
       <c r="A983" s="5"/>
@@ -29257,6 +30392,7 @@
       <c r="Y983" s="5"/>
       <c r="Z983" s="5"/>
       <c r="AA983" s="5"/>
+      <c r="AB983" s="5"/>
     </row>
     <row r="984">
       <c r="A984" s="5"/>
@@ -29286,6 +30422,7 @@
       <c r="Y984" s="5"/>
       <c r="Z984" s="5"/>
       <c r="AA984" s="5"/>
+      <c r="AB984" s="5"/>
     </row>
     <row r="985">
       <c r="A985" s="5"/>
@@ -29315,6 +30452,7 @@
       <c r="Y985" s="5"/>
       <c r="Z985" s="5"/>
       <c r="AA985" s="5"/>
+      <c r="AB985" s="5"/>
     </row>
     <row r="986">
       <c r="A986" s="5"/>
@@ -29344,6 +30482,7 @@
       <c r="Y986" s="5"/>
       <c r="Z986" s="5"/>
       <c r="AA986" s="5"/>
+      <c r="AB986" s="5"/>
     </row>
     <row r="987">
       <c r="A987" s="5"/>
@@ -29373,6 +30512,7 @@
       <c r="Y987" s="5"/>
       <c r="Z987" s="5"/>
       <c r="AA987" s="5"/>
+      <c r="AB987" s="5"/>
     </row>
     <row r="988">
       <c r="A988" s="5"/>
@@ -29402,6 +30542,7 @@
       <c r="Y988" s="5"/>
       <c r="Z988" s="5"/>
       <c r="AA988" s="5"/>
+      <c r="AB988" s="5"/>
     </row>
     <row r="989">
       <c r="A989" s="5"/>
@@ -29431,6 +30572,7 @@
       <c r="Y989" s="5"/>
       <c r="Z989" s="5"/>
       <c r="AA989" s="5"/>
+      <c r="AB989" s="5"/>
     </row>
     <row r="990">
       <c r="A990" s="5"/>
@@ -29460,6 +30602,7 @@
       <c r="Y990" s="5"/>
       <c r="Z990" s="5"/>
       <c r="AA990" s="5"/>
+      <c r="AB990" s="5"/>
     </row>
     <row r="991">
       <c r="A991" s="5"/>
@@ -29489,6 +30632,7 @@
       <c r="Y991" s="5"/>
       <c r="Z991" s="5"/>
       <c r="AA991" s="5"/>
+      <c r="AB991" s="5"/>
     </row>
     <row r="992">
       <c r="A992" s="5"/>
@@ -29518,6 +30662,7 @@
       <c r="Y992" s="5"/>
       <c r="Z992" s="5"/>
       <c r="AA992" s="5"/>
+      <c r="AB992" s="5"/>
     </row>
     <row r="993">
       <c r="A993" s="5"/>
@@ -29547,6 +30692,7 @@
       <c r="Y993" s="5"/>
       <c r="Z993" s="5"/>
       <c r="AA993" s="5"/>
+      <c r="AB993" s="5"/>
     </row>
     <row r="994">
       <c r="A994" s="5"/>
@@ -29576,6 +30722,7 @@
       <c r="Y994" s="5"/>
       <c r="Z994" s="5"/>
       <c r="AA994" s="5"/>
+      <c r="AB994" s="5"/>
     </row>
     <row r="995">
       <c r="A995" s="5"/>
@@ -29605,6 +30752,7 @@
       <c r="Y995" s="5"/>
       <c r="Z995" s="5"/>
       <c r="AA995" s="5"/>
+      <c r="AB995" s="5"/>
     </row>
     <row r="996">
       <c r="A996" s="5"/>
@@ -29634,6 +30782,7 @@
       <c r="Y996" s="5"/>
       <c r="Z996" s="5"/>
       <c r="AA996" s="5"/>
+      <c r="AB996" s="5"/>
     </row>
     <row r="997">
       <c r="A997" s="5"/>
@@ -29663,6 +30812,7 @@
       <c r="Y997" s="5"/>
       <c r="Z997" s="5"/>
       <c r="AA997" s="5"/>
+      <c r="AB997" s="5"/>
     </row>
     <row r="998">
       <c r="A998" s="5"/>
@@ -29692,6 +30842,7 @@
       <c r="Y998" s="5"/>
       <c r="Z998" s="5"/>
       <c r="AA998" s="5"/>
+      <c r="AB998" s="5"/>
     </row>
     <row r="999">
       <c r="A999" s="5"/>
@@ -29721,6 +30872,7 @@
       <c r="Y999" s="5"/>
       <c r="Z999" s="5"/>
       <c r="AA999" s="5"/>
+      <c r="AB999" s="5"/>
     </row>
     <row r="1000">
       <c r="A1000" s="5"/>
@@ -29750,6 +30902,7 @@
       <c r="Y1000" s="5"/>
       <c r="Z1000" s="5"/>
       <c r="AA1000" s="5"/>
+      <c r="AB1000" s="5"/>
     </row>
     <row r="1001">
       <c r="A1001" s="5"/>
@@ -29779,39 +30932,13 @@
       <c r="Y1001" s="5"/>
       <c r="Z1001" s="5"/>
       <c r="AA1001" s="5"/>
-    </row>
-    <row r="1002">
-      <c r="A1002" s="5"/>
-      <c r="B1002" s="5"/>
-      <c r="C1002" s="5"/>
-      <c r="D1002" s="5"/>
-      <c r="E1002" s="5"/>
-      <c r="F1002" s="5"/>
-      <c r="G1002" s="5"/>
-      <c r="H1002" s="5"/>
-      <c r="I1002" s="5"/>
-      <c r="J1002" s="5"/>
-      <c r="K1002" s="5"/>
-      <c r="L1002" s="5"/>
-      <c r="M1002" s="5"/>
-      <c r="N1002" s="5"/>
-      <c r="O1002" s="5"/>
-      <c r="P1002" s="5"/>
-      <c r="Q1002" s="5"/>
-      <c r="R1002" s="5"/>
-      <c r="S1002" s="5"/>
-      <c r="T1002" s="5"/>
-      <c r="U1002" s="5"/>
-      <c r="V1002" s="5"/>
-      <c r="W1002" s="5"/>
-      <c r="X1002" s="5"/>
-      <c r="Y1002" s="5"/>
-      <c r="Z1002" s="5"/>
-      <c r="AA1002" s="5"/>
+      <c r="AB1001" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:J1"/>
+  <mergeCells count="3">
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -29838,20 +30965,20 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="7" t="s">
-        <v>12</v>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="7" t="s">
-        <v>16</v>
+      <c r="J1" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="4"/>
@@ -29867,36 +30994,36 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>11</v>
+      <c r="E2" s="7"/>
+      <c r="F2" s="6" t="s">
+        <v>7</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>11</v>
+      <c r="I2" s="7"/>
+      <c r="J2" s="6" t="s">
+        <v>7</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>11</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
@@ -29909,18 +31036,18 @@
       <c r="U2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
@@ -29932,32 +31059,32 @@
       <c r="U3" s="5"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>13</v>
+      <c r="A4" s="9" t="s">
+        <v>17</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>85.0</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>88.0</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>82.0</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="10">
+      <c r="E4" s="10"/>
+      <c r="F4" s="9">
         <v>85.0</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>88.0</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>82.0</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
@@ -29969,18 +31096,18 @@
       <c r="U4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -29992,8 +31119,8 @@
       <c r="U5" s="5"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="s">
-        <v>21</v>
+      <c r="A6" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="B6" s="12">
         <v>0.29</v>
@@ -30004,7 +31131,7 @@
       <c r="D6" s="12">
         <v>0.66</v>
       </c>
-      <c r="E6" s="13"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="12">
         <v>0.31</v>
       </c>
@@ -30014,7 +31141,7 @@
       <c r="H6" s="12">
         <v>0.78</v>
       </c>
-      <c r="I6" s="13"/>
+      <c r="I6" s="10"/>
       <c r="J6" s="12">
         <v>0.99</v>
       </c>
@@ -30035,18 +31162,18 @@
       <c r="U6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -30058,8 +31185,8 @@
       <c r="U7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="s">
-        <v>27</v>
+      <c r="A8" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="B8" s="12">
         <v>0.58</v>
@@ -30070,7 +31197,7 @@
       <c r="D8" s="12">
         <v>0.65</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="12">
         <v>0.75</v>
       </c>
@@ -30080,8 +31207,8 @@
       <c r="H8" s="12">
         <v>0.8</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="10">
+      <c r="I8" s="10"/>
+      <c r="J8" s="9">
         <v>90.0</v>
       </c>
       <c r="K8" s="12">
@@ -30101,18 +31228,18 @@
       <c r="U8" s="5"/>
     </row>
     <row r="9">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
@@ -30124,26 +31251,26 @@
       <c r="U9" s="5"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="s">
-        <v>32</v>
+      <c r="A10" s="9" t="s">
+        <v>28</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>80.0</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <v>60.0</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>70.0</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
@@ -30155,18 +31282,18 @@
       <c r="U10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
@@ -30178,32 +31305,32 @@
       <c r="U11" s="5"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="s">
-        <v>37</v>
+      <c r="A12" s="9" t="s">
+        <v>32</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>60.0</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <v>70.0</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>65.0</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="10">
+      <c r="E12" s="10"/>
+      <c r="F12" s="9">
         <v>70.0</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>75.0</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <v>75.0</v>
       </c>
-      <c r="I12" s="13"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
@@ -30215,18 +31342,18 @@
       <c r="U12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -30238,26 +31365,26 @@
       <c r="U13" s="5"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="s">
-        <v>42</v>
+      <c r="A14" s="9" t="s">
+        <v>33</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>6.0</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>12.0</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>5.0</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
@@ -30269,18 +31396,18 @@
       <c r="U14" s="5"/>
     </row>
     <row r="15">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -30292,26 +31419,26 @@
       <c r="U15" s="5"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="s">
-        <v>47</v>
+      <c r="A16" s="9" t="s">
+        <v>38</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>80.0</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>85.0</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>82.0</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -30323,18 +31450,18 @@
       <c r="U16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
